--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -557,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-501.1500000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.79726e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-66.955</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1585747846515243</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4599211563732</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.535480161012092</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.224837074583673</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19.9540243556174</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.81640921430224</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.023x + -29914.981</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.57799203963456e-11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3162.623821967788</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.00000000000012e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8167896763566419</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-373.1700000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.79278e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-69.04600000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3583572110792922</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.027572347266845</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.013596491228113</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.850155763239886</v>
+      </c>
+      <c r="J3" t="n">
+        <v>38.06553223342664</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.69713293948777</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.291x + -34761.029</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>169.2984843203908</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3196.958776527149</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.449986721646182e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.7991918328057676</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-347.73</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.79373e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-69.812</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02467248908296248</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.668285431119922</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.490639269406358</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.321809488782561</v>
+      </c>
+      <c r="J4" t="n">
+        <v>28.71178445525151</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.66424764890175</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.189x + -33591.477</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.156849441056458e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2970.216919520805</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000201e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8171991454006072</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-332.6300000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.79765e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-70.333</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.06178861788617579</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3865384615384614</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.310533610533601</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.830832570905755</v>
+      </c>
+      <c r="J5" t="n">
+        <v>24.39693656956412</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.54943589274184</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 12.848x + -32031.922</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>174.5331168529545</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3043.918106517487</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.432291297293793e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8012758228254919</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-316.79</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.80066e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-70.762</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1614345114345062</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5868978805394516</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.204821958456928</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.005304792926931</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24.90652750674552</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.60411717932806</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 13.008x + -31913.066</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>170.9042396417636</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2966.506574842459</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.428577322949221e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8013860969554942</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-289.71</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.8041e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-71.145</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8531630170316488</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9704063604239835</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.629460847240028</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.579338505512531</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31.67584235481791</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.87504135878514</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 13.866x + -33633.359</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.703271881903417e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2822.798465620636</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000050927e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8177443413666805</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-284.0700000000002</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.80841e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-71.486</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.09480519480518121</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.326387009472066</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.170400000000106</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.937499999999986</v>
+      </c>
+      <c r="J8" t="n">
+        <v>25.09660724327303</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.68327670184654</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 13.248x + -31559.418</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.229611816513598e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2780.688961265309</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000083773e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8179917421367228</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-265.8799999999997</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.81234e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-71.818</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3952029520295419</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4692307692307645</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.085580389329531</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.429180695847357</v>
+      </c>
+      <c r="J9" t="n">
+        <v>24.38145561030451</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.68809269322692</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 13.263x + -31152.413</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.282739444726501e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2741.026458025862</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000168214e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8182273988864641</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-259.8499999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.81622e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-72.07299999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5299310344827709</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5725067385444794</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.29827823691461</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.041313868613145</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24.49086342097672</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.75111752662106</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 13.460x + -31221.485</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>171.0881415868463</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2789.254748204574</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.459199413072242e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8012792039769343</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-258.9400000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.82048e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-72.35599999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1320736434108495</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7016742763137747</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.774792760313141</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.050101132663364</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20.90216401282332</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.35115376309354</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 12.298x + -27995.567</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.809456445001685e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2670.130623209288</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000014896e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8186774839590578</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +1192,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +1221,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-308.6999999999998</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.89568e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-69.714</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03984375000001497</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5672707889126211</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.284543125533713</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.780857009781086</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25.28013104938837</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.67769190834748</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 13.231x + -32276.242</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.062713675080443e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2817.482606988762</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000009562e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8197788815018751</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-281.5499999999997</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.92475e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-70.724</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.02307692307692821</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4259562841530169</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7268243243243059</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.796038151137158</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22.9483826203297</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.71322709819221</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.341x + -30869.332</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.199384125382961e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2696.651472895748</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000047e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8202425632635399</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-254.0499999999997</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.93395e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-71.063</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2838084378563289</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.033136792452822</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.841335131490256</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.479505872822919</v>
+      </c>
+      <c r="J4" t="n">
+        <v>33.65585865354063</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.17691980166539</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.965x + -34249.295</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>8.977309999750351e-11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2651.245768338757</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.00000000000035e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8203774656077029</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-252.1699999999996</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.94005e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-71.324</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2180272108843628</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5796391752577996</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.37511032656668</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.992538915727219</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26.78809752431617</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.99839542539505</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.295x + -32210.214</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.412983682853059e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2617.722928009755</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000002194e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8204699467478979</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-249.8099999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.94399e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-71.554</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2295081967213187</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.458184143222505</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.141674249317539</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.103157894736873</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23.59409525852557</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.87587358970984</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 13.869x + -30819.615</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.754991111739672e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2586.391296198517</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.00000000000004e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8206270444170378</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-242.8299999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.95007e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-71.795</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.09674418604650938</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9625835189311763</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.025788900979394</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.008090844570724</v>
+      </c>
+      <c r="J7" t="n">
+        <v>23.9431557052806</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.91292744449579</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 13.995x + -30711.920</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.754305017899591e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2552.541169396459</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000005444e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8208245912413163</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-222.6300000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.95551e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-72.07899999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3966819221968448</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7014734774066812</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.634000000000123</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.331633272616938</v>
+      </c>
+      <c r="J8" t="n">
+        <v>26.34623474102023</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.03553267229474</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 14.429x + -31356.984</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.503501385785679e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2520.051021445846</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000103e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8210531653555203</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-219.1199999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.96055e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-72.32299999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1770631067961296</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4623873873873711</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9205223880596185</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.228667225481966</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22.70337924811805</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.87061031206963</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 13.851x + -29651.049</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.103607156150456e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2488.499623189355</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8213020873958177</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-226.2200000000003</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.96625e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-72.483</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.07826289950623208</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9801000711540685</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.847263413633432</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.189965525357663</v>
+      </c>
+      <c r="J10" t="n">
+        <v>25.06692690148411</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.74332769620638</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 13.435x + -28365.293</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.69315635028907e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2458.740340453454</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8215601878843636</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-211.1599999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.9695e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-72.70699999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.03505402160863317</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5470223325061931</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.787132352941141</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.148451151707752</v>
+      </c>
+      <c r="J11" t="n">
+        <v>23.20462053068555</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.94015713521885</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 14.089x + -29499.889</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>7.469416570882947e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2430.19508284942</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8218355076552178</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-199.98</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.97248e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-72.90300000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2993224932249284</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.197248968363107</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.703867924528241</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.335793357933519</v>
+      </c>
+      <c r="J12" t="n">
+        <v>25.60634371002162</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.12324255767194</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 14.757x + -30652.092</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.227592549317984e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2402.334189525924</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000003668e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8221100891259403</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-194.4099999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.9763e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-73.08799999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4406885758998715</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7168107588857473</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.182897862232749</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.562611073137339</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25.87733918991289</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.20355099496464</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 15.070x + -30985.042</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.068240441306971e-07</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2375.18471007619</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000007576e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8224020485155823</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-186.3300000000002</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.98164e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-73.343</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.08323917137476962</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.121194029850707</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.175358422939039</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.782348993288685</v>
+      </c>
+      <c r="J14" t="n">
+        <v>21.16879016516664</v>
+      </c>
+      <c r="K14" t="n">
+        <v>85.87991980962975</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 13.882x + -28104.001</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>6.264119972202835e-10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2347.983299388562</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000001325e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8227032451695064</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-184.4400000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.9857e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-73.51000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5629906542055639</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6908163265305866</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.655577299412764</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.052464228934735</v>
+      </c>
+      <c r="J15" t="n">
+        <v>21.57941320890608</v>
+      </c>
+      <c r="K15" t="n">
+        <v>85.94789243767886</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 14.116x + -28294.576</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.648564380359053e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2321.447823498657</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8230266146558169</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-177.2199999999998</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.98769e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-73.767</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.07173978882687217</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.058668705439521</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.967504523694704</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.319502330522582</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>85.68494044969964</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 13.253x + -26179.976</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.444975292971956e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2295.454333830792</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000037474e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.823351715766147</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-166.29</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.99302e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-73.93899999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2994915254237248</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9693840579710565</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.020228671943679</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.754954321855337</v>
+      </c>
+      <c r="J17" t="n">
+        <v>18.44634920546769</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85.83022020495159</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 13.716x + -26857.777</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>7.284878717459521e-10</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2269.520303373984</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8236752203402323</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-177.0999999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.99637e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-74.099</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.07430476998689227</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.548035304556388</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.741602887747425</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.772421530108343</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6.325006490058035</v>
+      </c>
+      <c r="K18" t="n">
+        <v>85.55474785019742</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 12.863x + -24813.235</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.122146396175027e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2244.281534153596</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000082565e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8240364476399836</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-156.3399999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.99729e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-74.298</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5791304347824622</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.4662079510703839</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.067057761732905</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.14161237785019</v>
+      </c>
+      <c r="J19" t="n">
+        <v>18.10624525057016</v>
+      </c>
+      <c r="K19" t="n">
+        <v>85.89717706372096</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 13.941x + -26751.197</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.153696038650151e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2220.052834556127</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000071e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8243669625812434</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-158.1799999999998</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.00154e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-74.486</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1789824072844176</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9901773652783236</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.107320483577281</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.53429407337965</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>85.67983918752189</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 13.237x + -25046.523</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>5.228405024624928e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2195.472264591197</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000292e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8247232020220793</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-151.3799999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.00368e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-74.666</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3152446066921513</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8143617244498197</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.037116929129906</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.531062556991498</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>85.65409604666891</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 13.159x + -24639.744</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>5.819276857280407e-10</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2171.634071564724</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8250811738977637</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-126.6000000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.00741e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-74.914</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.102791878172398</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.687196467991009</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.624079320113237</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.724205544286647</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.651683256211446</v>
+      </c>
+      <c r="K22" t="n">
+        <v>85.60819168391087</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 13.020x + -24133.754</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>6.578424228709979e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2147.228739683565</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000655e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8254542221389155</v>
       </c>
     </row>
   </sheetData>
@@ -718,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,8 +2430,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -853,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-389.6800000000003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.76371e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-68.654</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.005752636625114716</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.643380109823051</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.375000000000025</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.381972149040257</v>
+      </c>
+      <c r="J2" t="n">
+        <v>27.04477161163654</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.39177638401414</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.407x + -33423.422</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.098250106241304e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3120.664929391704</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8167512048500183</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-315.9400000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.78267e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-70.33</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1473871733966776</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3840292275574305</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.20766283524897</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.817417556897355</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24.45472526078392</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.53496643231591</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.806x + -32428.984</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.31867104258221e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2965.022094740954</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000151e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8171428854042595</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-284.25</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.78277e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-70.899</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2782363977485984</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.041071428571386</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.655418719211857</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.335013162843247</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30.63640717090059</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.86922017233529</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.846x + -34518.215</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>177.1211480723434</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3039.279138324308</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.408723919991782e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8024963177946208</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-268.6699999999996</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.78542e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-71.29300000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1542452830188647</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3028279654359785</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.086224821312543</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.772313865358907</v>
+      </c>
+      <c r="J5" t="n">
+        <v>23.8411350464324</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.61970620755656</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 13.055x + -31987.110</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>176.2029875329841</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2981.14356315627</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.429785062539998e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8015259960473308</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-266.9300000000003</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.78356e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-71.545</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2835514018691813</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4578194816800418</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.412489795918334</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.250242587601068</v>
+      </c>
+      <c r="J6" t="n">
+        <v>25.26808171004656</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.75675250055059</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 13.478x + -32674.387</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.582852024490997e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2837.911472723138</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8173622034734879</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-243.8700000000003</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.78514e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-71.94199999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.007309941520472623</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7834932821497109</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.346691449814127</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.093251859723683</v>
+      </c>
+      <c r="J7" t="n">
+        <v>22.60055077831586</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.64471569966712</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 13.130x + -31411.495</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.027052330947454e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2802.796779623428</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.81748602223323</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-238.23</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.78715e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-72.16800000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5727735368956673</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6934306569342773</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.306414219474502</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.362458654906276</v>
+      </c>
+      <c r="J8" t="n">
+        <v>22.88644387318298</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.7339394940268</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 13.406x + -31723.446</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.015787469702198e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2768.876023266081</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000159084e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8176430666296741</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-244.6199999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.78614e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-72.40600000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2122302158273307</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8129737609328568</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.198596491228048</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.588855602156974</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.86297303891655</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.58268283310457</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 12.945x + -30185.322</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.414841070470384e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2735.507623836769</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000099752e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8178295304769163</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-227.29</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.78607e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-72.679</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.08494117647058347</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.203337306317007</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.133040078201236</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.468657599053973</v>
+      </c>
+      <c r="J10" t="n">
+        <v>22.12878298131901</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.77806666185957</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 13.546x + -31338.047</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.117614611909924e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2703.72269973288</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8180467454064364</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-229.8899999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.78627e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-72.91200000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.02690677966101727</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5146216768916433</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.000484652665529</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.329708431836253</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20.4161222957007</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.63242873926892</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 13.093x + -29864.520</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>9.363843093238253e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2671.904036300058</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8182950314756228</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-215.98</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.78455e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-73.172</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4276595744681494</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.067128712871187</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.82804659498199</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.061922714420343</v>
+      </c>
+      <c r="J12" t="n">
+        <v>21.07389383620736</v>
+      </c>
+      <c r="K12" t="n">
+        <v>85.80004939311935</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 13.618x + -30800.825</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>6.803671400167015e-10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2641.506310427568</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.818551472836228</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-207.9699999999998</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.78432e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-73.468</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2334498834498945</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8906143344709286</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.324122807017519</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.743734491315224</v>
+      </c>
+      <c r="J13" t="n">
+        <v>18.08763919586585</v>
+      </c>
+      <c r="K13" t="n">
+        <v>85.56015391330622</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 12.879x + -28701.885</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.552840944951873e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2611.438701930438</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000001204e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8188384935621639</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-216.5499999999997</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.78076e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-73.649</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.03001813298686253</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7603460783619607</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.857296409695922</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.309749567866873</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>85.60673631577249</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 13.016x + -28685.033</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.488659556647301e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2582.519623882753</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000183e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8191308488972497</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-211.6900000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.77901e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-73.889</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.08614955853766434</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7966535833294411</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.939720866532336</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.200588164529912</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>85.610437234266</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 13.027x + -28394.662</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>7.3046240432988e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2553.871728548393</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000013776e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8194319463068017</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-192.2400000000002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.77859e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-74.16</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1218475073313849</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.4649819494584939</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.209105560032239</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.74607754734008</v>
+      </c>
+      <c r="J16" t="n">
+        <v>17.64475831034795</v>
+      </c>
+      <c r="K16" t="n">
+        <v>85.66205234667723</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 13.183x + -28461.835</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.282230997996266e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2526.138178742537</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000003142e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8197395374908334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-186.0599999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.77748e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-74.419</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.242802325464425</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.040044628347885</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.32352018960071</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.295937500013407</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85.40347199469859</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 12.438x + -26483.935</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>5.574439715375114e-11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2499.201143920776</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8200444774305483</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-189.5700000000002</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.77596e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-74.56699999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.08028936669875121</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9018566444196355</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.891749737951876</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.479688990495477</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>85.5609320108414</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 12.881x + -27191.338</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>4.634196782120349e-10</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2472.918314070274</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000825e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8203547809949402</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-174.3699999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.77453e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-74.846</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2958323106436052</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8641788302522365</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.870715502156409</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.474297553205317</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>85.39634455312655</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 12.419x + -25897.572</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.82262901452101e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2446.808083731452</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000741e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.820672922691858</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-164.8799999999997</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.77162e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-75.05500000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3272425249169544</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.037594799566578</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.32446280991732</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.954877192982371</v>
+      </c>
+      <c r="J20" t="n">
+        <v>12.3728283624158</v>
+      </c>
+      <c r="K20" t="n">
+        <v>85.5448689275364</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 12.835x + -26556.738</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>5.361737835006235e-10</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2421.562315616129</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8209825486897392</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-163.4100000000003</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.77016e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-75.252</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3755122626338965</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.882693415982002</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.971470568481517</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.576407675697975</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>85.45268774548107</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 12.573x + -25706.558</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>7.639996898130592e-12</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2396.115690016146</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.821309181071586</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-156.95</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.77114e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-75.474</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2581038217365134</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7534271268454416</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.857111363532125</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.033373210900836</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>85.11598921882953</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 11.703x + -23581.447</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>9.386260832158776e-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2370.972297857967</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000001279e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8216299238500708</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +3668,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +3697,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-721.3899999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.79691e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-66.895</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2493913043478221</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.636128048780512</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.097439024390271</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.673099662162126</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12.09334511765336</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.72014836631793</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.087x + -22726.481</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>161.2417281774964</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2997.753554063162</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.988846993442448e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.7747497912492826</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-441.8000000000002</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.86279e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-71.098</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1537557943148126</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8639157227665247</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.760311059520085</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.887455335491913</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30.43281780639558</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.43516227096887</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.525x + -27597.763</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>6.944598466089181e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2541.080020887905</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000079e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8157461941399734</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-350.3499999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.8711e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-72.34999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2670658682634868</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9895588235294286</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.571052631579055</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.878855218855212</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23.49926292227236</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.00043112084253</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.302x + -30499.421</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.339634416928426e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2457.190193690232</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8158701634296962</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-332.4400000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.8701e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-72.92400000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.03813582830797662</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7716069131985591</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.809111047127211</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.518590983728823</v>
+      </c>
+      <c r="J5" t="n">
+        <v>36.55652458681441</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.85690537485016</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 13.805x + -28740.962</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.141607515479345e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2411.008026712254</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000068516e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.815882302457436</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-304.1600000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.87345e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-73.312</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5155109513330233</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.174309192244147</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.071469324360639</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.246148210642394</v>
+      </c>
+      <c r="J6" t="n">
+        <v>56.56221116205242</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.10034161816279</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.670x + -30139.688</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.784582872436847e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2370.845084032311</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000003383e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8158760916433044</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-284.8799999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.87595e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-73.68300000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5608120391205057</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.385744385124258</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.162864571541563</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.360447897224332</v>
+      </c>
+      <c r="J7" t="n">
+        <v>62.5869942657136</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.15477108984886</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 14.878x + -30131.405</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.78173516126112e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2335.636458354546</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000749e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8159179511372353</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-278.1100000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.87763e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-73.95699999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2277167335536202</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9674059784539646</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.888286174759087</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.85972035173991</v>
+      </c>
+      <c r="J8" t="n">
+        <v>43.05335073456732</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.08138355222933</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 14.599x + -29114.336</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.493521025855163e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2303.725336890074</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000021807e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8159718830446999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-266.3200000000002</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.87885e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-74.217</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5093014485010308</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.193291769396836</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.878421192391944</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.753185971985134</v>
+      </c>
+      <c r="J9" t="n">
+        <v>43.79316668483327</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.15446570425812</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 14.877x + -29316.099</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.349852838923336e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2273.865132145196</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8160623225976936</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-261.2200000000003</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.88043e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-74.425</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2047546648799991</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9014897860428804</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.022458593118618</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.887040077883444</v>
+      </c>
+      <c r="J10" t="n">
+        <v>45.01037156074624</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.19490023385163</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 15.035x + -29292.312</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.415840859719032e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2246.633628514866</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000001037e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8161684121207439</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-246.4200000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.88263e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-74.681</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3755920250787826</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.114197939153625</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.880712433186532</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.872744652156764</v>
+      </c>
+      <c r="J11" t="n">
+        <v>45.65998810141355</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.20519091257219</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 15.076x + -29049.927</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>7.662693213914232e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2221.753564947094</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000021e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8163150548366694</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +4230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +4334,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +4363,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-397.4200000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.80582e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-69.59</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1264993026499297</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3980237154150182</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.283583267561235</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.712387483926287</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22.9206481399476</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.48563307455248</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.666x + -31764.896</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.747300497441216e-11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2907.479074605734</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000113e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8187223477313514</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-310.4899999999998</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.82804e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-70.908</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05467914438501859</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4101302460202806</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.165629139072955</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.16544959128066</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25.86213396851568</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.77726979360258</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.544x + -32504.482</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>168.5195265035647</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2889.556619265637</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.445891583989431e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8020592143047403</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-281.9099999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.83893e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-71.398</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4491686460807748</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6135817307692117</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.560422163588374</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.95633251833736</v>
+      </c>
+      <c r="J4" t="n">
+        <v>25.61951024273065</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.79496131596672</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.601x + -31977.713</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>7.555493351899843e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2740.841542456011</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000084496e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.819043599687526</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-252.54</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.8475e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-71.702</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6595848595848331</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8671729957805677</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.824917817225479</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.584933222036676</v>
+      </c>
+      <c r="J5" t="n">
+        <v>31.08212197469907</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.00473210617741</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.318x + -33338.503</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.342753719515469e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2703.782377099914</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000074021e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8190909559437562</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-248.75</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.85466e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-71.956</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2981707317073275</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8932079414838812</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.68899613899624</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.345792222867111</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24.8488470947256</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.77433236462277</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 13.534x + -31008.477</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>176.4817727525122</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2746.685211094529</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.41996735244995e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8046711866808292</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-255.7900000000004</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.85812e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-72.122</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.01997663551402849</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5232771822358158</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7831899921814075</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.347557003257347</v>
+      </c>
+      <c r="J7" t="n">
+        <v>22.49218713525085</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.68211348543718</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 13.244x + -29947.165</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>178.0211361878237</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2726.024493861719</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.458498066863573e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8031980694926291</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-246.9299999999998</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.86224e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-72.40600000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1241647301518033</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5780800559709286</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.924408686613661</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.920031018385956</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19.77818342140005</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.4484269107667</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 12.562x + -27979.733</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.779085770779615e-11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2608.177857410929</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8196074959740213</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-230.6799999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.86793e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-72.616</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2288065843621437</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8352389878162678</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.176658860265418</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.426105810927893</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.8435048573684</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.60896831082496</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 13.023x + -28766.318</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.655100104717447e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2578.616719393352</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000029e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8198317936240599</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-222.1900000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.87002e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-72.83799999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2748043818466299</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.019710906701625</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.012768031189103</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.967671809256684</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20.71546828223053</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.65303013752521</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 13.155x + -28756.075</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.091953517026953e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2550.114354591583</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000534e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8201092857635204</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-206.27</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.87396e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-73.09699999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.08384527872582639</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4034090909090997</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.288996763754067</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.002663622526548</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18.8579425993542</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.536689265056</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 12.811x + -27684.937</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>6.62909506396634e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2522.540919444169</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8204279121052407</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-208.7700000000004</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.87648e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-73.24299999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5698811096433439</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5894862604539836</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.181950384944372</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.16427432216905</v>
+      </c>
+      <c r="J12" t="n">
+        <v>19.72323614897519</v>
+      </c>
+      <c r="K12" t="n">
+        <v>85.64876452444132</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 13.142x + -28123.710</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.987472430098682e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2493.047171116554</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8208081807839711</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-196.6599999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.88127e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-73.48999999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1976578411405386</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6303303303303726</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.209066427289134</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.942250673854441</v>
+      </c>
+      <c r="J13" t="n">
+        <v>17.88599935950926</v>
+      </c>
+      <c r="K13" t="n">
+        <v>85.52395524815631</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 12.774x + -26980.150</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.393343331997727e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2463.337570982736</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000125e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8211641342548746</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-184.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.88564e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-73.727</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1817958179581655</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9315989847716106</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.371781756180785</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.040674318507756</v>
+      </c>
+      <c r="J14" t="n">
+        <v>15.75115614220901</v>
+      </c>
+      <c r="K14" t="n">
+        <v>85.43447767524192</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 12.523x + -26126.307</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.434777164258078e-11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2434.584296388062</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8215384419511169</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-182.6100000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.88678e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-73.90300000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.07331730769230987</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.639267015706765</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.636890951276123</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.067287630402468</v>
+      </c>
+      <c r="J15" t="n">
+        <v>16.53200210997002</v>
+      </c>
+      <c r="K15" t="n">
+        <v>85.55302254198135</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 12.858x + -26558.870</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>9.684336146384152e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2405.335203949656</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000027e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8219147047866441</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-180.96</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.88925e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-74.06</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.7193661971831671</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.593678160919536</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.664784394250493</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.42921253175273</v>
+      </c>
+      <c r="J16" t="n">
+        <v>17.54275273248681</v>
+      </c>
+      <c r="K16" t="n">
+        <v>85.63416318064937</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 13.098x + -26767.354</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>5.807164635943636e-12</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2377.324128530602</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8222964029961314</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-168.0999999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.89484e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-74.298</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.450240384615369</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6442043222003655</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.584868421052649</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.898097826086989</v>
+      </c>
+      <c r="J17" t="n">
+        <v>14.24045460836506</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85.45889795763823</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 12.591x + -25383.439</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>5.054322738713438e-12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2348.931582503353</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8226889203609115</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-159.7199999999998</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.89727e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-74.51900000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3767942583731618</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.041881443298995</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9804347826086868</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.118482344102102</v>
+      </c>
+      <c r="J18" t="n">
+        <v>12.06014352843084</v>
+      </c>
+      <c r="K18" t="n">
+        <v>85.35343439223158</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 12.304x + -24497.487</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.866706578933825e-09</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2320.472602728526</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8231048157835914</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-163.6800000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.89987e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-74.694</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2563781606098836</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9969441452217283</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.804196397967004</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.553055431392509</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>85.22137184686588</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 11.962x + -23498.407</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.70225681349418e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2293.723643250007</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000010132e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8234896453865895</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-152.0199999999998</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.90312e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-74.93300000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2124016522732937</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8316712066353664</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.914456992646637</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.251959721728572</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.98757251495587</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 11.402x + -22083.133</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.210396138398304e-09</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2265.475399808963</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000019e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8238958024119492</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-145.5199999999998</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.9041e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-75.092</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.08507853403138531</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6179340028694011</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.316837782340924</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.586170212765991</v>
+      </c>
+      <c r="J21" t="n">
+        <v>9.096772206442481</v>
+      </c>
+      <c r="K21" t="n">
+        <v>85.29593044656765</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 12.153x + -23353.097</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>3.33699942704002e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2237.606985131801</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000001356e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8243226703090486</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-140.3800000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.90786e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-75.28</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2592079207920942</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.355447154471579</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.513070539419135</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.417086330935393</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.476094741698008</v>
+      </c>
+      <c r="K22" t="n">
+        <v>85.23316132345582</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 11.992x + -22753.885</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>7.239735727126652e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2209.97942875963</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000001243e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8247433108567596</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +5468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +5572,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +5601,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-743.5499999999997</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.76943e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-66.64400000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06619183285849521</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3431557653405256</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9255657492354911</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.760035842293836</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.92354205133403</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.5391984418617</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.831x + -22565.897</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.669308107439065e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2898.531356320102</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000001478e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8190025675869466</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-408.0100000000002</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.84077e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-71.477</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5417943107221553</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.908650875386144</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.306906614785914</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.807678018575794</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20.93809919373094</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.67727164542526</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.229x + -29408.654</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.03126867934202e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2556.597060659346</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000111e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8199216917217894</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-342.1700000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.85184e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-72.633</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07026064364732587</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9835590988326689</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.992073326552868</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.166481189186836</v>
+      </c>
+      <c r="J4" t="n">
+        <v>48.73356223004248</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.87851877562265</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.878x + -29583.934</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>9.061974822504213e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2467.008602312186</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000025e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8200960150288892</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-315.2600000000002</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.85759e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-73.092</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2245057921206386</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8789611587162565</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.10430061842461</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.15284312343381</v>
+      </c>
+      <c r="J5" t="n">
+        <v>55.26537244303667</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.96601860262649</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.180x + -29678.095</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.629535078081057e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2422.043207017894</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8201782845207977</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-286.7800000000002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.85986e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-73.459</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4232217573221217</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7375951293759425</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.80771812080537</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.372549019607845</v>
+      </c>
+      <c r="J6" t="n">
+        <v>26.50465078239117</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.1994198164175</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 15.053x + -31154.373</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.990938932229572e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2385.792369250469</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000008783e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8203024432975681</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-298.6299999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.86409e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-73.684</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.09798611861049893</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4928599440369619</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.230224277024809</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.409641476584216</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31.72474037547325</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.80287814285442</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 13.627x + -27596.067</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.129356743279167e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2351.902489905589</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8204542884825974</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-278.45</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.86455e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-73.949</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1530238873021293</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.886326692270619</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.231312423250098</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.317791200155269</v>
+      </c>
+      <c r="J8" t="n">
+        <v>63.18307913664914</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.16959384640222</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 14.936x + -30018.076</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.382791105745357e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2318.745722138486</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000131e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8206460909902948</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-262.24</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.86925e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-74.249</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4700819907729475</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.222272139091677</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.450071988481739</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.35708387435085</v>
+      </c>
+      <c r="J9" t="n">
+        <v>66.5235378490376</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.16231172024354</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 14.907x + -29550.904</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.719626855767721e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2286.064416655111</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8208424885399236</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-267.0100000000002</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.87132e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-74.467</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1082735514692771</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6130599531801963</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.216165621389492</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.212478445074232</v>
+      </c>
+      <c r="J10" t="n">
+        <v>33.15852937049793</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.92732160050741</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 14.045x + -27340.361</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.08760428912035e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2254.315818047912</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000032e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8210697152121067</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-261.51</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.87239e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-74.64400000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1918080706282584</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9398742325789154</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.887368634406233</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.88722959658035</v>
+      </c>
+      <c r="J11" t="n">
+        <v>45.16543240586272</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.17786898249233</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 14.968x + -28871.084</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.166191682446323e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2224.310126700585</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000001448e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8213032005508728</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +6134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +6238,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +6267,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-455.4699999999998</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.79463e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-68.84699999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.052718078381787</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2523162939297187</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9143913538111793</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.714469729497668</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20.17003580839866</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.22988672510775</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.984x + -30621.827</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.297076168366234e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2968.891507117198</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000048e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.818931396280973</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-348.3999999999996</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.80846e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-70.349</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.239685863874375</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8076923076923588</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.405833333333299</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.842429501084546</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30.04711987395344</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.89089795448947</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.920x + -34279.093</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.568459738348793e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2861.859134141609</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000018728e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8192054736333529</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-318.6399999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.81489e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-70.836</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.358931698774072</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9531034482758434</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.9277498202732</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.713193851409006</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31.82073888544717</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.98638690921051</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.252x + -34513.326</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>7.875781802845816e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2814.340182505431</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8193239749030816</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-311.6900000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.82214e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-71.131</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.006313834726083744</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.09443961772372357</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.704746835443164</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.138008342022833</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26.34472265192726</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.80482185543558</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 13.633x + -32476.831</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.447210733315941e-12</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2777.40156528471</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000003147e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8193876311862822</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-289.3399999999997</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.82776e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-71.455</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4205882352941485</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6770232558139498</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.184681460272017</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.542012195122005</v>
+      </c>
+      <c r="J6" t="n">
+        <v>26.09050407600991</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.81830792661792</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 13.677x + -32186.552</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.433992573529441e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2743.957567616646</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8194662589336773</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-285.75</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.83007e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-71.66500000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5443089430894275</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7620017714791728</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.31134485349353</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.018765311122019</v>
+      </c>
+      <c r="J7" t="n">
+        <v>26.45935074543551</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.87163150708022</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 13.855x + -32270.020</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>9.579990235952119e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2713.596310572661</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000156968e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8195668929104341</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-288.29</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.83257e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-71.86</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1043294614572391</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2450602409638383</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9137601177336271</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.766666666666765</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23.14263984714875</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.73117651278226</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 13.397x + -30808.799</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.218697654527602e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2685.741271748901</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000116112e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8196825558247631</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-272.5500000000002</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.83615e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-72.123</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1341726618704952</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.5833657587549134</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8235332043842873</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.072619047618872</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23.24097922922099</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.73842902141354</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 13.420x + -30546.624</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.479441224105351e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2658.180877920011</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.00000000000071e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8198505988660719</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-267.8299999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.83892e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-72.348</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.04703866229295919</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.57822411788636</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.69014541144829</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.130955516489549</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40.64421714725524</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.55946921631539</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 12.877x + -28941.911</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.380012355386828e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2631.183480824692</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000012889e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8200813779813744</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-257.5300000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.84195e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-72.509</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1166023166023121</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4661702127659471</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7657400972897708</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.706428138265575</v>
+      </c>
+      <c r="J11" t="n">
+        <v>23.50375382973382</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.80128589062012</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 13.622x + -30427.587</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>9.303005940359943e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2603.979594122613</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000039895e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.82035353547412</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-262.6900000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.84343e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-72.676</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.09966228016350101</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6827350666408089</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.814473566357984</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.068136902502828</v>
+      </c>
+      <c r="J12" t="n">
+        <v>44.04898659981232</v>
+      </c>
+      <c r="K12" t="n">
+        <v>85.69226677238517</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 13.276x + -29298.806</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.344160738297588e-12</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2577.717880925443</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000002961e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8206536807278236</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-255.5300000000002</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.84847e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-72.854</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1988684457684855</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6901797817919918</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.817762949331802</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.114139569909911</v>
+      </c>
+      <c r="J13" t="n">
+        <v>38.83173767432984</v>
+      </c>
+      <c r="K13" t="n">
+        <v>85.70841168783397</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 13.326x + -29107.365</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.60985710614627e-18</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2550.833724812115</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8209732842270187</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-235.0999999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.8497e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-73.113</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1670299727520248</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6840175953079207</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.3696721311475</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.669221484610854</v>
+      </c>
+      <c r="J14" t="n">
+        <v>23.42724663160913</v>
+      </c>
+      <c r="K14" t="n">
+        <v>85.85919159752454</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 13.813x + -29948.805</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.883939939052494e-10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2523.973641391239</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000010549e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8212867731213296</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-219.2999999999997</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.85395e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-73.31999999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.59573770491805</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.260698689956347</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.408502906976785</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.272149744753282</v>
+      </c>
+      <c r="J15" t="n">
+        <v>24.40595317391118</v>
+      </c>
+      <c r="K15" t="n">
+        <v>85.99574808611756</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 14.285x + -30744.115</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.502981915748685e-08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2497.596764095284</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000210954e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8216267671235367</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-217.9599999999996</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.85489e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-73.479</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.7989660265878692</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.107894736842106</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.118794098781233</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.396026490066222</v>
+      </c>
+      <c r="J16" t="n">
+        <v>25.13575999622183</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.03822384549272</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 14.439x + -30783.166</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>9.583345736296063e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2472.138018937787</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000263e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8219592530084373</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-223.75</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.85835e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-73.68000000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.09642591881024945</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6844444698887178</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.572339249421166</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.280361568212883</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.341780708683093</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85.66248540855653</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 13.184x + -27650.595</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.076491277200882e-10</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2446.151413445513</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8222949768213919</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-207.9099999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.8599e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-73.879</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1572799999999886</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.5832222222221741</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.723692992213523</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.044476534295995</v>
+      </c>
+      <c r="J18" t="n">
+        <v>21.33362090945453</v>
+      </c>
+      <c r="K18" t="n">
+        <v>85.81927658141153</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 13.680x + -28482.025</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.786965320502517e-09</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2420.467735693825</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000001139e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8226282779471028</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-217.26</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.8624e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-74.004</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1689432075045502</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8036175452845065</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.050087014551297</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.22571132296877</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>85.77189410797133</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 13.527x + -27841.277</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.728071149661126e-11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2395.345596222047</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000271e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8229619698113428</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-197.1199999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.86512e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-74.196</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5481786133959914</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.346587926509128</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.408416220352049</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.270756756756702</v>
+      </c>
+      <c r="J20" t="n">
+        <v>22.66434483128718</v>
+      </c>
+      <c r="K20" t="n">
+        <v>86.04079009269893</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 14.448x + -29578.208</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.151201381785353e-09</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2369.931667734592</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000026403e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8233047208738283</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-210.8499999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.86723e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-74.349</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.08731997254227876</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7459597266380356</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.679816162230556</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.617860072244097</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20.823838663639</v>
+      </c>
+      <c r="K21" t="n">
+        <v>85.61859359939417</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 13.052x + -26252.448</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>90.94930141049421</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2331.396859334923</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.277275645378917e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8104542054928779</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-193.4699999999998</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.87046e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-74.524</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6484098939929802</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.225826446280989</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.121831869510793</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.450340136054421</v>
+      </c>
+      <c r="J22" t="n">
+        <v>21.57798976706174</v>
+      </c>
+      <c r="K22" t="n">
+        <v>85.96295309951256</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 14.169x + -28367.557</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.338455413330206e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2319.952965833445</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000194e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8239873823820093</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +7372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +7476,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +7505,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-710.71</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.85436e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-66.83499999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1587344028520467</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.372055030094593</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.536466165413567</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.719089108910864</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.92425574979669</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.59616956072668</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.910x + -21553.656</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.039085601399273e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2726.946789323578</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.00000000000027e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8179473813783887</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-401.48</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.90819e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-71.625</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2134415720757781</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9083313515617871</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.690312500235393</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.942211281016333</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.51062267380237</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.60455708824557</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.010x + -27564.707</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.810395849991254e-11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2434.128637667324</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8187164122258088</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-327.4599999999998</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.9192e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-72.696</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5256211180124327</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5336371923427402</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.232642916321428</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.043287671232912</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24.6379385753511</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.13770616101534</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.812x + -30393.900</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>9.372927700212982e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2356.440625562518</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000119e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8187829017704485</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-303.99</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.92239e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-73.131</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.893478260869606</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6667852906287209</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.093794964028785</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.69147627416535</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26.13090271135829</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.27934440394502</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.378x + -31037.190</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.55874122150104e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2317.316779300467</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000024045e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8187899596608714</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-293.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.92703e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-73.474</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.256706660779095</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.783492099114218</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.896416443741846</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.612041911653753</v>
+      </c>
+      <c r="J6" t="n">
+        <v>40.49425355894642</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.05706977543211</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.508x + -28738.032</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.165904168561833e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2286.119522464697</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000247e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8188216991037657</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-278.8600000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.93103e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-73.74299999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1219316438417739</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9068713288654667</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.598494419119144</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.806322439044119</v>
+      </c>
+      <c r="J7" t="n">
+        <v>42.00928930268382</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.12476278051119</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 14.763x + -28895.870</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.74042746161858e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2256.056384785873</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000002347e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8189129950193168</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-262.6400000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.93365e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-74.008</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.569475682439224</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.100854321917947</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.229112833686433</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.32405448100505</v>
+      </c>
+      <c r="J8" t="n">
+        <v>65.72099417672497</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.31408704074593</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 15.523x + -30076.593</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.72685249777086e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2225.900919931732</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.819045124068046</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-256.4499999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.93899e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-74.246</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2948786390490279</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.439322231330101</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.772473864973404</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.792140412009485</v>
+      </c>
+      <c r="J9" t="n">
+        <v>44.71040105897736</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.21687968130527</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 15.123x + -28852.461</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.536564702534079e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2196.0039154832</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000428e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8192257747855003</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-245.7700000000002</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.94223e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-74.48699999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1554244740486372</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9036080809628981</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.82516860069548</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.909732626172684</v>
+      </c>
+      <c r="J10" t="n">
+        <v>45.22308275884836</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.27033952714685</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 15.340x + -28908.513</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.760263210525344e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2167.425630607172</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000014e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8194058511994442</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-249.0799999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.94502e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-74.619</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3150739563931069</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.230693413898665</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.83292160389022</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.859524294344061</v>
+      </c>
+      <c r="J11" t="n">
+        <v>47.58832023132853</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.34295633619254</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 15.646x + -29159.128</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.14325529618481e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2139.909577629029</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000067e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8195966819580668</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +8038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +8142,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +8171,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-395.9899999999998</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.86901e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-68.756</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8452688172042837</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.130451127819533</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.506652631578923</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.89554441659704</v>
+      </c>
+      <c r="J2" t="n">
+        <v>32.45630097322727</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.75811165242861</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 13.482x + -33774.863</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.846913323843916e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2877.138759700751</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000052073e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8195915288991009</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-312.2599999999998</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.88328e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-70.313</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08786359077231919</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8951197870453007</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.307405022537019</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.43805168986081</v>
+      </c>
+      <c r="J3" t="n">
+        <v>31.7470195809039</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.96653098710421</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.182x + -33888.873</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.405528003712421e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2768.959440272427</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000016458e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8198919491967519</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-289.2800000000002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.89304e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-70.745</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5565594059405854</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8714859437751142</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.107765451663998</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.709658371995007</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32.57799146563097</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.05187263551271</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.489x + -34009.825</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>7.964427138879586e-12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2720.638480053613</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000001424e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8199472184299055</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-272.3499999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.90045e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-71.039</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4780487804878008</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.297677119628248</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.570656370656512</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.725529995489418</v>
+      </c>
+      <c r="J5" t="n">
+        <v>33.71145553372613</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.1169377044325</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.733x + -34167.617</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>4.281344064035811e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2687.522056680972</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8199585031018202</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-266.0999999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.90706e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-71.28100000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.376683087027949</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5844011142061518</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.320980707395444</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.977024793388388</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27.14100763741779</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.95980606102954</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.158x + -32371.818</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.77543492875132e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2657.029005892974</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000001452e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8201147448924281</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-258.4899999999998</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.91195e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-71.50700000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.02975206611568673</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6553666312433682</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.529008264462782</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.04872462259245</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27.42504985033319</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.96482790941235</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 14.176x + -32071.228</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>178.7874322610375</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2685.114667925638</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.393666145335805e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.807392366587996</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-248.6100000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.91644e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-71.735</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.108153477218222</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7916395222583914</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.208626887131533</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.124903793293059</v>
+      </c>
+      <c r="J8" t="n">
+        <v>27.03386724380429</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.97733059189549</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 14.220x + -31831.516</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>180.7099134671621</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2664.709232403846</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.423279139325497e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8063722578768966</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-245.1900000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.91903e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-71.902</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.43898550724637</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9033542976940097</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.621252204585436</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.326309921962131</v>
+      </c>
+      <c r="J9" t="n">
+        <v>27.48694761056511</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.02870966900606</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 14.404x + -31951.224</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>181.480830455624</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2646.651785233375</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.456808227389621e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8050510101565322</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-250.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.92277e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-72.086</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.282306830907057</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.489424206815495</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.498723897911857</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.705124835742366</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24.1670412655428</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.87609696665561</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 13.870x + -30365.854</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>174.5742779311235</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2600.622594587256</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.390978337262408e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8083431445395306</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-230.0599999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.92693e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-72.29900000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4916387959865709</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9452571428571652</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.597463768115971</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.831385390428202</v>
+      </c>
+      <c r="J11" t="n">
+        <v>27.27324940408628</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.08516463464437</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 14.613x + -31778.105</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>6.872746667149741e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2519.116916451603</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000306e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8213885168837558</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-228.3900000000003</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.92978e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-72.48099999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2713201820940587</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.4846534653465558</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.502354920100994</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.246371882086255</v>
+      </c>
+      <c r="J12" t="n">
+        <v>28.03717184987267</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.11355201084075</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 14.720x + -31683.217</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>4.581051058942064e-12</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2491.604678133055</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.821746400329142</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-218.1699999999996</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.93443e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-72.721</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2613188976377858</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7026915113871813</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.775923970433069</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.111932479627581</v>
+      </c>
+      <c r="J13" t="n">
+        <v>26.67230853066723</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.08020508541409</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 14.594x + -31062.926</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.067583795970227e-12</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2464.038823681705</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8220720767545914</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-222.8499999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.93696e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-72.91500000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1490725338935988</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8085133703354108</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.866272757836868</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.114479101282501</v>
+      </c>
+      <c r="J14" t="n">
+        <v>24.40922486503461</v>
+      </c>
+      <c r="K14" t="n">
+        <v>85.74036323023644</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 13.426x + -28115.634</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.667103645306754e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2437.282706316727</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8224168114902716</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-218.6199999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.93967e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-73.128</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.01518986744462819</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.678282385233173</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.973038757060784</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.22473815192653</v>
+      </c>
+      <c r="J15" t="n">
+        <v>15.55229104313778</v>
+      </c>
+      <c r="K15" t="n">
+        <v>85.76039479724962</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 13.490x + -27958.581</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.156250906290475e-12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2410.525587010599</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8227550837375864</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-205.4299999999998</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.94321e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-73.27200000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8020634920634637</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6642659279778691</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.283890954151217</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.160100166944956</v>
+      </c>
+      <c r="J16" t="n">
+        <v>26.9927480182674</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.1750776523389</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 14.957x + -30875.338</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>8.470728801220286e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2384.055225509795</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000001024e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.823102309757364</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-198.6000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.9469e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-73.51600000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3678275290215436</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6925974025973791</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.779863013698621</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.184732214228679</v>
+      </c>
+      <c r="J17" t="n">
+        <v>22.38309758416112</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85.91530846486062</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 14.003x + -28487.343</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.230705697416968e-08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2357.918282023292</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000016e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8234458384755483</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-179.49</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.95083e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-73.755</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6151556156969546</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.826597938144306</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.099484536082316</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.103571428571493</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20.59133403708775</v>
+      </c>
+      <c r="K18" t="n">
+        <v>85.99763930489898</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 14.292x + -28816.333</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>6.194129678660083e-10</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2331.314977939496</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8238081950896849</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-189.1700000000003</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.95229e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-73.89</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3168289290681517</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.769346733668362</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.045982142857129</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.159871244635255</v>
+      </c>
+      <c r="J19" t="n">
+        <v>22.3757781550994</v>
+      </c>
+      <c r="K19" t="n">
+        <v>85.9876950211288</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 14.257x + -28409.744</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.19045633652048e-11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2306.018635037247</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8241829784722229</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-179.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.95609e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-74.08199999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1795811518324265</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.92220795892163</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.072660098522167</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.230877483443701</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20.90762961641318</v>
+      </c>
+      <c r="K20" t="n">
+        <v>85.92609497672279</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 14.040x + -27664.711</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>5.042093175659922e-11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2280.661471813982</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000146e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8245403951689554</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-182.6300000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.95864e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-74.238</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1758677685950436</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5471626733921927</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.832784810126508</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.898786653184994</v>
+      </c>
+      <c r="J21" t="n">
+        <v>21.33889786901714</v>
+      </c>
+      <c r="K21" t="n">
+        <v>85.96545586314856</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 14.178x + -27659.801</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.610994835102721e-08</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2255.78639408294</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000015152e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8249258958499351</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-170.4299999999998</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.96232e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-74.44199999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5528089887640059</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7835550181378867</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.27936320754709</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.108732612055497</v>
+      </c>
+      <c r="J22" t="n">
+        <v>20.18094444421598</v>
+      </c>
+      <c r="K22" t="n">
+        <v>85.93625423983973</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 14.076x + -27152.256</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.641316762978337e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2230.140017103029</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000507e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8253150783533207</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +9276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +9380,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +9409,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-672.26</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.08623e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-70.033</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2292389459308818</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6365809500997687</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.260119733770537</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.180883309527025</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.77405098758756</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.64983059297444</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.986x + -16149.241</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.18963506839997e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2000.054434608405</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000051e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8198449945424701</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-320.5600000000002</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.06994e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-75.041</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2092183721124184</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9281699756652059</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.50223840576859</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.613301752202911</v>
+      </c>
+      <c r="J3" t="n">
+        <v>27.31152456196506</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.27031403448062</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 15.340x + -24860.582</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>6.899639652387902e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1828.839227429705</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000072e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8203893547553976</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-262.3300000000002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.06951e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-75.95399999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3964381117348948</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7304300968449365</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.403468600234386</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.99856370185541</v>
+      </c>
+      <c r="J4" t="n">
+        <v>29.28887231560023</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.44820967343497</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.111x + -25272.296</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.295643239239275e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1778.897592392325</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000046e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8205170933880845</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-241.1200000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.07057e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-76.327</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4494401787887425</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9066330683554946</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.947524955194195</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.709318763503869</v>
+      </c>
+      <c r="J5" t="n">
+        <v>35.2496118355776</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.65293236683763</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 17.099x + -26428.632</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>7.339943731119014e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1748.353368977718</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000076e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8206349145994807</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-233.0799999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.07355e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-76.581</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3340135456659701</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7655314018124919</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.520592115291121</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.392265454942453</v>
+      </c>
+      <c r="J6" t="n">
+        <v>32.23071685783785</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.61506210747608</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 16.907x + -25695.896</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.06089984688109e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1720.612338470688</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000351e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8208233706467746</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-217.29</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.07609e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-76.857</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2901853472605054</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7902493135960845</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.64637931990596</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.880139346891258</v>
+      </c>
+      <c r="J7" t="n">
+        <v>38.47667886689877</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.74794040825911</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 17.599x + -26403.058</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.37158877233294e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1693.155492008821</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8210912061231181</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-217.1500000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.078e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.038</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5605050105711572</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.10255738947121</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.510043112611268</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.655289930090377</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.38393257394949</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.73482270002181</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 17.529x + -25876.916</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.830612224195562e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1666.728511405334</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000001403e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8213970356642882</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-205.1599999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.07998e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-77.306</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3681066542570877</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8223235490139518</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.660743489392434</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.335962776801288</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35.35974646188302</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.7597429707979</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 17.664x + -25678.132</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.284306897986913e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1640.36726593241</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8217390669474903</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-192.73</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.08297e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-77.503</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.7759056771935948</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.626484739626742</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.116182113421989</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.138261006813592</v>
+      </c>
+      <c r="J10" t="n">
+        <v>51.98874431911516</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.02495968943157</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 19.242x + -27710.362</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>140.6764401548427</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1567.082173047818</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.280368087482346e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8180991154307861</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-196.6299999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.0844e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-77.687</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3115963208114889</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.001607122153005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.200321061395096</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.353283726153484</v>
+      </c>
+      <c r="J11" t="n">
+        <v>71.85621553432904</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.77386829314423</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 17.741x + -25053.076</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.253218068662767e-07</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1593.111746086915</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.00000000000105e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8223684639019326</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -588,19 +588,19 @@
       <c r="K2" t="n">
         <v>84.81640921430224</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.023x + -29914.981</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-29914.98110711802</v>
       </c>
       <c r="Y2" t="n">
         <v>2.57799203963456e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>3162.623821967788</v>
+        <v>501.1500000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000012e-08</v>
@@ -640,19 +640,19 @@
       <c r="K3" t="n">
         <v>85.69713293948777</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.291x + -34761.029</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-34761.02860804056</v>
       </c>
       <c r="Y3" t="n">
         <v>169.2984843203908</v>
       </c>
       <c r="Z3" t="n">
-        <v>3196.958776527149</v>
+        <v>373.1700000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.449986721646182e-08</v>
@@ -692,19 +692,19 @@
       <c r="K4" t="n">
         <v>85.66424764890175</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.189x + -33591.477</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-33591.47731365899</v>
       </c>
       <c r="Y4" t="n">
         <v>1.156849441056458e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2970.216919520805</v>
+        <v>347.73</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000201e-08</v>
@@ -744,19 +744,19 @@
       <c r="K5" t="n">
         <v>85.54943589274184</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 12.848x + -32031.922</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-32031.92196320686</v>
       </c>
       <c r="Y5" t="n">
         <v>174.5331168529545</v>
       </c>
       <c r="Z5" t="n">
-        <v>3043.918106517487</v>
+        <v>332.6300000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.432291297293793e-08</v>
@@ -796,19 +796,19 @@
       <c r="K6" t="n">
         <v>85.60411717932806</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 13.008x + -31913.066</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-31913.06618704371</v>
       </c>
       <c r="Y6" t="n">
         <v>170.9042396417636</v>
       </c>
       <c r="Z6" t="n">
-        <v>2966.506574842459</v>
+        <v>316.79</v>
       </c>
       <c r="AA6" t="n">
         <v>1.428577322949221e-08</v>
@@ -848,19 +848,19 @@
       <c r="K7" t="n">
         <v>85.87504135878514</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 13.866x + -33633.359</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-33633.35851403059</v>
       </c>
       <c r="Y7" t="n">
         <v>1.703271881903417e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2822.798465620636</v>
+        <v>289.71</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000050927e-08</v>
@@ -900,19 +900,19 @@
       <c r="K8" t="n">
         <v>85.68327670184654</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 13.248x + -31559.418</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-31559.41778611071</v>
       </c>
       <c r="Y8" t="n">
         <v>6.229611816513598e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2780.688961265309</v>
+        <v>290.3000000000002</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000083773e-08</v>
@@ -952,19 +952,19 @@
       <c r="K9" t="n">
         <v>85.68809269322692</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 13.263x + -31152.413</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-31152.41284712239</v>
       </c>
       <c r="Y9" t="n">
         <v>1.282739444726501e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2741.026458025862</v>
+        <v>282.9399999999996</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000168214e-08</v>
@@ -1004,19 +1004,19 @@
       <c r="K10" t="n">
         <v>85.75111752662106</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 13.460x + -31221.485</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-31221.48532913067</v>
       </c>
       <c r="Y10" t="n">
         <v>171.0881415868463</v>
       </c>
       <c r="Z10" t="n">
-        <v>2789.254748204574</v>
+        <v>279.5799999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1.459199413072242e-08</v>
@@ -1056,19 +1056,19 @@
       <c r="K11" t="n">
         <v>85.35115376309354</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 12.298x + -27995.567</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-27995.56745854828</v>
       </c>
       <c r="Y11" t="n">
         <v>5.809456445001685e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2670.130623209288</v>
+        <v>287.8099999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000014896e-08</v>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1254,19 +1254,19 @@
       <c r="K2" t="n">
         <v>85.67769190834748</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 13.231x + -32276.242</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-32276.24153380185</v>
       </c>
       <c r="Y2" t="n">
         <v>2.062713675080443e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2817.482606988762</v>
+        <v>308.6999999999998</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000009562e-08</v>
@@ -1306,19 +1306,19 @@
       <c r="K3" t="n">
         <v>85.71322709819221</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.341x + -30869.332</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-30869.33157610318</v>
       </c>
       <c r="Y3" t="n">
         <v>2.199384125382961e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2696.651472895748</v>
+        <v>281.5499999999997</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000047e-08</v>
@@ -1358,19 +1358,19 @@
       <c r="K4" t="n">
         <v>86.17691980166539</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.965x + -34249.295</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-34249.29508316806</v>
       </c>
       <c r="Y4" t="n">
         <v>8.977309999750351e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>2651.245768338757</v>
+        <v>254.0499999999997</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000035e-08</v>
@@ -1410,19 +1410,19 @@
       <c r="K5" t="n">
         <v>85.99839542539505</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.295x + -32210.214</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-32210.21361267188</v>
       </c>
       <c r="Y5" t="n">
         <v>1.412983682853059e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2617.722928009755</v>
+        <v>254.3399999999997</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000002194e-08</v>
@@ -1462,19 +1462,19 @@
       <c r="K6" t="n">
         <v>85.87587358970984</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 13.869x + -30819.615</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-30819.6149635234</v>
       </c>
       <c r="Y6" t="n">
         <v>4.754991111739672e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2586.391296198517</v>
+        <v>254.6800000000003</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000000004e-08</v>
@@ -1514,19 +1514,19 @@
       <c r="K7" t="n">
         <v>85.91292744449579</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 13.995x + -30711.920</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-30711.9201904497</v>
       </c>
       <c r="Y7" t="n">
         <v>1.754305017899591e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>2552.541169396459</v>
+        <v>250.9200000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000005444e-08</v>
@@ -1566,19 +1566,19 @@
       <c r="K8" t="n">
         <v>86.03553267229474</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 14.429x + -31356.984</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-31356.98386594918</v>
       </c>
       <c r="Y8" t="n">
         <v>2.503501385785679e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2520.051021445846</v>
+        <v>242.4200000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000103e-08</v>
@@ -1618,19 +1618,19 @@
       <c r="K9" t="n">
         <v>85.87061031206963</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 13.851x + -29651.049</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-29651.04948460772</v>
       </c>
       <c r="Y9" t="n">
         <v>1.103607156150456e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2488.499623189355</v>
+        <v>244.5599999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000004e-08</v>
@@ -1670,19 +1670,19 @@
       <c r="K10" t="n">
         <v>85.74332769620638</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 13.435x + -28365.293</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-28365.29311611508</v>
       </c>
       <c r="Y10" t="n">
         <v>1.69315635028907e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2458.740340453454</v>
+        <v>249.9300000000003</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -1722,19 +1722,19 @@
       <c r="K11" t="n">
         <v>85.94015713521885</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 14.089x + -29499.889</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-29499.88895770364</v>
       </c>
       <c r="Y11" t="n">
         <v>7.469416570882947e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2430.19508284942</v>
+        <v>237.77</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000012e-08</v>
@@ -1774,19 +1774,19 @@
       <c r="K12" t="n">
         <v>86.12324255767194</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 14.757x + -30652.092</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-30652.09157851015</v>
       </c>
       <c r="Y12" t="n">
         <v>1.227592549317984e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>2402.334189525924</v>
+        <v>228.5300000000002</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000003668e-08</v>
@@ -1826,19 +1826,19 @@
       <c r="K13" t="n">
         <v>86.20355099496464</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 15.070x + -30985.042</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-30985.04205280727</v>
       </c>
       <c r="Y13" t="n">
         <v>1.068240441306971e-07</v>
       </c>
       <c r="Z13" t="n">
-        <v>2375.18471007619</v>
+        <v>222.96</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000007576e-08</v>
@@ -1878,19 +1878,19 @@
       <c r="K14" t="n">
         <v>85.87991980962975</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 13.882x + -28104.001</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-28104.00107703159</v>
       </c>
       <c r="Y14" t="n">
         <v>6.264119972202835e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>2347.983299388562</v>
+        <v>227.1699999999998</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000001325e-08</v>
@@ -1930,19 +1930,19 @@
       <c r="K15" t="n">
         <v>85.94789243767886</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 14.116x + -28294.576</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-28294.57574853358</v>
       </c>
       <c r="Y15" t="n">
         <v>2.648564380359053e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>2321.447823498657</v>
+        <v>224.5599999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000003e-08</v>
@@ -1982,19 +1982,19 @@
       <c r="K16" t="n">
         <v>85.68494044969964</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 13.253x + -26179.976</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-26179.97634280716</v>
       </c>
       <c r="Y16" t="n">
         <v>3.444975292971956e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>2295.454333830792</v>
+        <v>226.1099999999997</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000037474e-08</v>
@@ -2034,19 +2034,19 @@
       <c r="K17" t="n">
         <v>85.83022020495159</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 13.716x + -26857.777</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-26857.77674374761</v>
       </c>
       <c r="Y17" t="n">
         <v>7.284878717459521e-10</v>
       </c>
       <c r="Z17" t="n">
-        <v>2269.520303373984</v>
+        <v>217.5700000000002</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -2086,19 +2086,19 @@
       <c r="K18" t="n">
         <v>85.55474785019742</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 12.863x + -24813.235</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-24813.23486023556</v>
       </c>
       <c r="Y18" t="n">
         <v>3.122146396175027e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>2244.281534153596</v>
+        <v>227.8299999999999</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000082565e-08</v>
@@ -2138,19 +2138,19 @@
       <c r="K19" t="n">
         <v>85.89717706372096</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 13.941x + -26751.197</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-26751.19685487385</v>
       </c>
       <c r="Y19" t="n">
         <v>2.153696038650151e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>2220.052834556127</v>
+        <v>207.9799999999998</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000071e-08</v>
@@ -2190,19 +2190,19 @@
       <c r="K20" t="n">
         <v>85.67983918752189</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 13.237x + -25046.523</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-25046.5227868827</v>
       </c>
       <c r="Y20" t="n">
         <v>5.228405024624928e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>2195.472264591197</v>
+        <v>213.7199999999998</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000292e-08</v>
@@ -2242,19 +2242,19 @@
       <c r="K21" t="n">
         <v>85.65409604666891</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 13.159x + -24639.744</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-24639.74399748924</v>
       </c>
       <c r="Y21" t="n">
         <v>5.819276857280407e-10</v>
       </c>
       <c r="Z21" t="n">
-        <v>2171.634071564724</v>
+        <v>209.28</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -2294,19 +2294,19 @@
       <c r="K22" t="n">
         <v>85.60819168391087</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 13.020x + -24133.754</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-24133.75447069373</v>
       </c>
       <c r="Y22" t="n">
         <v>6.578424228709979e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>2147.228739683565</v>
+        <v>195.8400000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000655e-08</v>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2492,19 +2492,19 @@
       <c r="K2" t="n">
         <v>85.39177638401414</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.407x + -33423.422</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-33423.4216940086</v>
       </c>
       <c r="Y2" t="n">
         <v>3.098250106241304e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>3120.664929391704</v>
+        <v>389.6800000000003</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000042e-08</v>
@@ -2544,19 +2544,19 @@
       <c r="K3" t="n">
         <v>85.53496643231591</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.806x + -32428.984</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-32428.9839919529</v>
       </c>
       <c r="Y3" t="n">
         <v>1.31867104258221e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2965.022094740954</v>
+        <v>315.9400000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000151e-08</v>
@@ -2596,19 +2596,19 @@
       <c r="K4" t="n">
         <v>85.86922017233529</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.846x + -34518.215</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-34518.214625006</v>
       </c>
       <c r="Y4" t="n">
         <v>177.1211480723434</v>
       </c>
       <c r="Z4" t="n">
-        <v>3039.279138324308</v>
+        <v>286.3600000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.408723919991782e-08</v>
@@ -2648,19 +2648,19 @@
       <c r="K5" t="n">
         <v>85.61970620755656</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 13.055x + -31987.110</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-31987.10972683296</v>
       </c>
       <c r="Y5" t="n">
         <v>176.2029875329841</v>
       </c>
       <c r="Z5" t="n">
-        <v>2981.14356315627</v>
+        <v>288.9400000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.429785062539998e-08</v>
@@ -2700,19 +2700,19 @@
       <c r="K6" t="n">
         <v>85.75675250055059</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 13.478x + -32674.387</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-32674.38718010858</v>
       </c>
       <c r="Y6" t="n">
         <v>6.582852024490997e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>2837.911472723138</v>
+        <v>282.25</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000001e-08</v>
@@ -2752,19 +2752,19 @@
       <c r="K7" t="n">
         <v>85.64471569966712</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 13.130x + -31411.495</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-31411.49473469492</v>
       </c>
       <c r="Y7" t="n">
         <v>1.027052330947454e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2802.796779623428</v>
+        <v>279.8200000000002</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000002e-08</v>
@@ -2804,19 +2804,19 @@
       <c r="K8" t="n">
         <v>85.7339394940268</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 13.406x + -31723.446</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-31723.44635492421</v>
       </c>
       <c r="Y8" t="n">
         <v>1.015787469702198e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2768.876023266081</v>
+        <v>274.46</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000159084e-08</v>
@@ -2856,19 +2856,19 @@
       <c r="K9" t="n">
         <v>85.58268283310457</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 12.945x + -30185.322</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-30185.32181046786</v>
       </c>
       <c r="Y9" t="n">
         <v>1.414841070470384e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2735.507623836769</v>
+        <v>280.02</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000099752e-08</v>
@@ -2908,19 +2908,19 @@
       <c r="K10" t="n">
         <v>85.77806666185957</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 13.546x + -31338.047</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-31338.04713138255</v>
       </c>
       <c r="Y10" t="n">
         <v>2.117614611909924e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2703.72269973288</v>
+        <v>268.6600000000003</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -2960,19 +2960,19 @@
       <c r="K11" t="n">
         <v>85.63242873926892</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 13.093x + -29864.520</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-29864.52036155956</v>
       </c>
       <c r="Y11" t="n">
         <v>9.363843093238253e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2671.904036300058</v>
+        <v>273.1700000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000042e-08</v>
@@ -3012,19 +3012,19 @@
       <c r="K12" t="n">
         <v>85.80004939311935</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 13.618x + -30800.825</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-30800.82457272207</v>
       </c>
       <c r="Y12" t="n">
         <v>6.803671400167015e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>2641.506310427568</v>
+        <v>262.3699999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000008e-08</v>
@@ -3064,19 +3064,19 @@
       <c r="K13" t="n">
         <v>85.56015391330622</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 12.879x + -28701.885</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-28701.88478166432</v>
       </c>
       <c r="Y13" t="n">
         <v>2.552840944951873e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>2611.438701930438</v>
+        <v>264.5299999999997</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000001204e-08</v>
@@ -3116,19 +3116,19 @@
       <c r="K14" t="n">
         <v>85.60673631577249</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 13.016x + -28685.033</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-28685.03259873531</v>
       </c>
       <c r="Y14" t="n">
         <v>1.488659556647301e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>2582.519623882753</v>
+        <v>264.27</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000183e-08</v>
@@ -3168,19 +3168,19 @@
       <c r="K15" t="n">
         <v>85.610437234266</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 13.027x + -28394.662</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-28394.66167818223</v>
       </c>
       <c r="Y15" t="n">
         <v>7.3046240432988e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>2553.871728548393</v>
+        <v>262.4000000000001</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000013776e-08</v>
@@ -3220,19 +3220,19 @@
       <c r="K16" t="n">
         <v>85.66205234667723</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 13.183x + -28461.835</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-28461.83541249934</v>
       </c>
       <c r="Y16" t="n">
         <v>1.282230997996266e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>2526.138178742537</v>
+        <v>252.0800000000004</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000003142e-08</v>
@@ -3272,19 +3272,19 @@
       <c r="K17" t="n">
         <v>85.40347199469859</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 12.438x + -26483.935</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-26483.93509906495</v>
       </c>
       <c r="Y17" t="n">
         <v>5.574439715375114e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>2499.201143920776</v>
+        <v>253.9699999999998</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000002e-08</v>
@@ -3324,19 +3324,19 @@
       <c r="K18" t="n">
         <v>85.5609320108414</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 12.881x + -27191.338</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-27191.33839576717</v>
       </c>
       <c r="Y18" t="n">
         <v>4.634196782120349e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>2472.918314070274</v>
+        <v>251.3800000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000825e-08</v>
@@ -3376,19 +3376,19 @@
       <c r="K19" t="n">
         <v>85.39634455312655</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 12.419x + -25897.572</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-25897.57203092706</v>
       </c>
       <c r="Y19" t="n">
         <v>1.82262901452101e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>2446.808083731452</v>
+        <v>246.9200000000001</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000741e-08</v>
@@ -3428,19 +3428,19 @@
       <c r="K20" t="n">
         <v>85.5448689275364</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 12.835x + -26556.738</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-26556.73841351583</v>
       </c>
       <c r="Y20" t="n">
         <v>5.361737835006235e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>2421.562315616129</v>
+        <v>237.5899999999997</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000005e-08</v>
@@ -3480,19 +3480,19 @@
       <c r="K21" t="n">
         <v>85.45268774548107</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 12.573x + -25706.558</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-25706.5580828153</v>
       </c>
       <c r="Y21" t="n">
         <v>7.639996898130592e-12</v>
       </c>
       <c r="Z21" t="n">
-        <v>2396.115690016146</v>
+        <v>237.4700000000003</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -3532,19 +3532,19 @@
       <c r="K22" t="n">
         <v>85.11598921882953</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 11.703x + -23581.447</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-23581.44735841637</v>
       </c>
       <c r="Y22" t="n">
         <v>9.386260832158776e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>2370.972297857967</v>
+        <v>238.7299999999998</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000001279e-08</v>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -3730,19 +3730,19 @@
       <c r="K2" t="n">
         <v>83.72014836631793</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.087x + -22726.481</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-22726.48146502904</v>
       </c>
       <c r="Y2" t="n">
         <v>161.2417281774964</v>
       </c>
       <c r="Z2" t="n">
-        <v>2997.753554063162</v>
+        <v>721.3899999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1.988846993442448e-08</v>
@@ -3782,19 +3782,19 @@
       <c r="K3" t="n">
         <v>85.43516227096887</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.525x + -27597.763</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-27597.76330893855</v>
       </c>
       <c r="Y3" t="n">
         <v>6.944598466089181e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2541.080020887905</v>
+        <v>441.8000000000002</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000079e-08</v>
@@ -3834,19 +3834,19 @@
       <c r="K4" t="n">
         <v>86.00043112084253</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.302x + -30499.421</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-30499.42147381005</v>
       </c>
       <c r="Y4" t="n">
         <v>5.339634416928426e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2457.190193690232</v>
+        <v>350.3499999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -3886,19 +3886,19 @@
       <c r="K5" t="n">
         <v>85.85690537485016</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 13.805x + -28740.962</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-28740.96151745195</v>
       </c>
       <c r="Y5" t="n">
         <v>1.141607515479345e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2411.008026712254</v>
+        <v>332.4400000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000068516e-08</v>
@@ -3938,19 +3938,19 @@
       <c r="K6" t="n">
         <v>86.10034161816279</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.670x + -30139.688</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-30139.68816408904</v>
       </c>
       <c r="Y6" t="n">
         <v>1.784582872436847e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2370.845084032311</v>
+        <v>304.1600000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000003383e-08</v>
@@ -3990,19 +3990,19 @@
       <c r="K7" t="n">
         <v>86.15477108984886</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 14.878x + -30131.405</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-30131.40489930597</v>
       </c>
       <c r="Y7" t="n">
         <v>2.78173516126112e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2335.636458354546</v>
+        <v>284.8799999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000749e-08</v>
@@ -4042,19 +4042,19 @@
       <c r="K8" t="n">
         <v>86.08138355222933</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 14.599x + -29114.336</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-29114.33606285213</v>
       </c>
       <c r="Y8" t="n">
         <v>3.493521025855163e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2303.725336890074</v>
+        <v>278.1100000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000021807e-08</v>
@@ -4094,19 +4094,19 @@
       <c r="K9" t="n">
         <v>86.15446570425812</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 14.877x + -29316.099</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-29316.09885609434</v>
       </c>
       <c r="Y9" t="n">
         <v>1.349852838923336e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2273.865132145196</v>
+        <v>266.3200000000002</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -4146,19 +4146,19 @@
       <c r="K10" t="n">
         <v>86.19490023385163</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 15.035x + -29292.312</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-29292.31176746068</v>
       </c>
       <c r="Y10" t="n">
         <v>1.415840859719032e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2246.633628514866</v>
+        <v>261.2200000000003</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000001037e-08</v>
@@ -4198,19 +4198,19 @@
       <c r="K11" t="n">
         <v>86.20519091257219</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 15.076x + -29049.927</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-29049.92704982174</v>
       </c>
       <c r="Y11" t="n">
         <v>7.662693213914232e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2221.753564947094</v>
+        <v>246.4200000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000021e-08</v>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4396,19 +4396,19 @@
       <c r="K2" t="n">
         <v>85.48563307455248</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.666x + -31764.896</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-31764.89629019741</v>
       </c>
       <c r="Y2" t="n">
         <v>2.747300497441216e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>2907.479074605734</v>
+        <v>397.4200000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000113e-08</v>
@@ -4448,19 +4448,19 @@
       <c r="K3" t="n">
         <v>85.77726979360258</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.544x + -32504.482</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-32504.48179644905</v>
       </c>
       <c r="Y3" t="n">
         <v>168.5195265035647</v>
       </c>
       <c r="Z3" t="n">
-        <v>2889.556619265637</v>
+        <v>310.4899999999998</v>
       </c>
       <c r="AA3" t="n">
         <v>1.445891583989431e-08</v>
@@ -4500,19 +4500,19 @@
       <c r="K4" t="n">
         <v>85.79496131596672</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.601x + -31977.713</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-31977.71335055447</v>
       </c>
       <c r="Y4" t="n">
         <v>7.555493351899843e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2740.841542456011</v>
+        <v>281.9099999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000084496e-08</v>
@@ -4552,19 +4552,19 @@
       <c r="K5" t="n">
         <v>86.00473210617741</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.318x + -33338.503</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-33338.50338005289</v>
       </c>
       <c r="Y5" t="n">
         <v>1.342753719515469e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2703.782377099914</v>
+        <v>264.1599999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000074021e-08</v>
@@ -4604,19 +4604,19 @@
       <c r="K6" t="n">
         <v>85.77433236462277</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 13.534x + -31008.477</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-31008.47685392185</v>
       </c>
       <c r="Y6" t="n">
         <v>176.4817727525122</v>
       </c>
       <c r="Z6" t="n">
-        <v>2746.685211094529</v>
+        <v>270.25</v>
       </c>
       <c r="AA6" t="n">
         <v>1.41996735244995e-08</v>
@@ -4656,19 +4656,19 @@
       <c r="K7" t="n">
         <v>85.68211348543718</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 13.244x + -29947.165</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-29947.1649625958</v>
       </c>
       <c r="Y7" t="n">
         <v>178.0211361878237</v>
       </c>
       <c r="Z7" t="n">
-        <v>2726.024493861719</v>
+        <v>273.4000000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.458498066863573e-08</v>
@@ -4708,19 +4708,19 @@
       <c r="K8" t="n">
         <v>85.4484269107667</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 12.562x + -27979.733</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-27979.73269080841</v>
       </c>
       <c r="Y8" t="n">
         <v>2.779085770779615e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>2608.177857410929</v>
+        <v>275.5500000000002</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000017e-08</v>
@@ -4760,19 +4760,19 @@
       <c r="K9" t="n">
         <v>85.60896831082496</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 13.023x + -28766.318</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-28766.31773061886</v>
       </c>
       <c r="Y9" t="n">
         <v>3.655100104717447e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2578.616719393352</v>
+        <v>266.98</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000029e-08</v>
@@ -4812,19 +4812,19 @@
       <c r="K10" t="n">
         <v>85.65303013752521</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 13.155x + -28756.075</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-28756.07535024081</v>
       </c>
       <c r="Y10" t="n">
         <v>3.091953517026953e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2550.114354591583</v>
+        <v>261.2799999999997</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000534e-08</v>
@@ -4864,19 +4864,19 @@
       <c r="K11" t="n">
         <v>85.536689265056</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 12.811x + -27684.937</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-27684.93709289018</v>
       </c>
       <c r="Y11" t="n">
         <v>6.62909506396634e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2522.540919444169</v>
+        <v>256.46</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -4916,19 +4916,19 @@
       <c r="K12" t="n">
         <v>85.64876452444132</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 13.142x + -28123.710</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-28123.70963899793</v>
       </c>
       <c r="Y12" t="n">
         <v>1.987472430098682e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>2493.047171116554</v>
+        <v>255.0700000000002</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -4968,19 +4968,19 @@
       <c r="K13" t="n">
         <v>85.52395524815631</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 12.774x + -26980.150</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-26980.1496763315</v>
       </c>
       <c r="Y13" t="n">
         <v>2.393343331997727e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>2463.337570982736</v>
+        <v>251.73</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000125e-08</v>
@@ -5020,19 +5020,19 @@
       <c r="K14" t="n">
         <v>85.43447767524192</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 12.523x + -26126.307</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-26126.30703645421</v>
       </c>
       <c r="Y14" t="n">
         <v>1.434777164258078e-11</v>
       </c>
       <c r="Z14" t="n">
-        <v>2434.584296388062</v>
+        <v>246.9300000000003</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -5072,19 +5072,19 @@
       <c r="K15" t="n">
         <v>85.55302254198135</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 12.858x + -26558.870</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-26558.86995910022</v>
       </c>
       <c r="Y15" t="n">
         <v>9.684336146384152e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>2405.335203949656</v>
+        <v>242.5900000000001</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000027e-08</v>
@@ -5124,19 +5124,19 @@
       <c r="K16" t="n">
         <v>85.63416318064937</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 13.098x + -26767.354</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-26767.35432003055</v>
       </c>
       <c r="Y16" t="n">
         <v>5.807164635943636e-12</v>
       </c>
       <c r="Z16" t="n">
-        <v>2377.324128530602</v>
+        <v>236.6799999999998</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -5176,19 +5176,19 @@
       <c r="K17" t="n">
         <v>85.45889795763823</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 12.591x + -25383.439</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-25383.43886330936</v>
       </c>
       <c r="Y17" t="n">
         <v>5.054322738713438e-12</v>
       </c>
       <c r="Z17" t="n">
-        <v>2348.931582503353</v>
+        <v>234.2599999999998</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000006e-08</v>
@@ -5228,19 +5228,19 @@
       <c r="K18" t="n">
         <v>85.35343439223158</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 12.304x + -24497.487</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-24497.48739716551</v>
       </c>
       <c r="Y18" t="n">
         <v>2.866706578933825e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>2320.472602728526</v>
+        <v>231.8199999999997</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000008e-08</v>
@@ -5280,19 +5280,19 @@
       <c r="K19" t="n">
         <v>85.22137184686588</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 11.962x + -23498.407</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-23498.40669568294</v>
       </c>
       <c r="Y19" t="n">
         <v>1.70225681349418e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>2293.723643250007</v>
+        <v>234.7899999999997</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000010132e-08</v>
@@ -5332,19 +5332,19 @@
       <c r="K20" t="n">
         <v>84.98757251495587</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 11.402x + -22083.133</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-22083.13348589925</v>
       </c>
       <c r="Y20" t="n">
         <v>1.210396138398304e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>2265.475399808963</v>
+        <v>231.74</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000019e-08</v>
@@ -5384,19 +5384,19 @@
       <c r="K21" t="n">
         <v>85.29593044656765</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 12.153x + -23353.097</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-23353.09673975293</v>
       </c>
       <c r="Y21" t="n">
         <v>3.33699942704002e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>2237.606985131801</v>
+        <v>221.1400000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000001356e-08</v>
@@ -5436,19 +5436,19 @@
       <c r="K22" t="n">
         <v>85.23316132345582</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 11.992x + -22753.885</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-22753.88532271128</v>
       </c>
       <c r="Y22" t="n">
         <v>7.239735727126652e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>2209.97942875963</v>
+        <v>217.6900000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000001243e-08</v>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5634,19 +5634,19 @@
       <c r="K2" t="n">
         <v>83.5391984418617</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.831x + -22565.897</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-22565.89730244199</v>
       </c>
       <c r="Y2" t="n">
         <v>1.669308107439065e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2898.531356320102</v>
+        <v>743.5499999999997</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000001478e-08</v>
@@ -5686,19 +5686,19 @@
       <c r="K3" t="n">
         <v>85.67727164542526</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.229x + -29408.654</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-29408.65401258625</v>
       </c>
       <c r="Y3" t="n">
         <v>1.03126867934202e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2556.597060659346</v>
+        <v>408.0100000000002</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000111e-08</v>
@@ -5738,19 +5738,19 @@
       <c r="K4" t="n">
         <v>85.87851877562265</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.878x + -29583.934</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-29583.93365675751</v>
       </c>
       <c r="Y4" t="n">
         <v>9.061974822504213e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2467.008602312186</v>
+        <v>342.1700000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000025e-08</v>
@@ -5790,19 +5790,19 @@
       <c r="K5" t="n">
         <v>85.96601860262649</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.180x + -29678.095</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-29678.09452322549</v>
       </c>
       <c r="Y5" t="n">
         <v>2.629535078081057e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2422.043207017894</v>
+        <v>315.2600000000002</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -5842,19 +5842,19 @@
       <c r="K6" t="n">
         <v>86.1994198164175</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 15.053x + -31154.373</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-31154.37288865895</v>
       </c>
       <c r="Y6" t="n">
         <v>3.990938932229572e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2385.792369250469</v>
+        <v>286.7800000000002</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000008783e-08</v>
@@ -5894,19 +5894,19 @@
       <c r="K7" t="n">
         <v>85.80287814285442</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 13.627x + -27596.067</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-27596.06716754378</v>
       </c>
       <c r="Y7" t="n">
         <v>2.129356743279167e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2351.902489905589</v>
+        <v>298.6299999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000007e-08</v>
@@ -5946,19 +5946,19 @@
       <c r="K8" t="n">
         <v>86.16959384640222</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 14.936x + -30018.076</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-30018.07600164873</v>
       </c>
       <c r="Y8" t="n">
         <v>7.382791105745357e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2318.745722138486</v>
+        <v>278.45</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000131e-08</v>
@@ -5998,19 +5998,19 @@
       <c r="K9" t="n">
         <v>86.16231172024354</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 14.907x + -29550.904</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-29550.90375437156</v>
       </c>
       <c r="Y9" t="n">
         <v>1.719626855767721e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>2286.064416655111</v>
+        <v>262.24</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -6050,19 +6050,19 @@
       <c r="K10" t="n">
         <v>85.92732160050741</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 14.045x + -27340.361</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-27340.36124166657</v>
       </c>
       <c r="Y10" t="n">
         <v>3.08760428912035e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2254.315818047912</v>
+        <v>267.0100000000002</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000032e-08</v>
@@ -6102,19 +6102,19 @@
       <c r="K11" t="n">
         <v>86.17786898249233</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 14.968x + -28871.084</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-28871.0837201775</v>
       </c>
       <c r="Y11" t="n">
         <v>1.166191682446323e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2224.310126700585</v>
+        <v>261.51</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000001448e-08</v>
@@ -6240,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6300,19 +6300,19 @@
       <c r="K2" t="n">
         <v>85.22988672510775</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.984x + -30621.827</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-30621.82678766628</v>
       </c>
       <c r="Y2" t="n">
         <v>4.297076168366234e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>2968.891507117198</v>
+        <v>455.4699999999998</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000048e-08</v>
@@ -6352,19 +6352,19 @@
       <c r="K3" t="n">
         <v>85.89089795448947</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.920x + -34279.093</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-34279.09277141315</v>
       </c>
       <c r="Y3" t="n">
         <v>3.568459738348793e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2861.859134141609</v>
+        <v>348.3999999999996</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000018728e-08</v>
@@ -6404,19 +6404,19 @@
       <c r="K4" t="n">
         <v>85.98638690921051</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.252x + -34513.326</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-34513.32611334425</v>
       </c>
       <c r="Y4" t="n">
         <v>7.875781802845816e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2814.340182505431</v>
+        <v>318.6399999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000001e-08</v>
@@ -6456,19 +6456,19 @@
       <c r="K5" t="n">
         <v>85.80482185543558</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 13.633x + -32476.831</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-32476.83126192831</v>
       </c>
       <c r="Y5" t="n">
         <v>1.447210733315941e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>2777.40156528471</v>
+        <v>311.6900000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000003147e-08</v>
@@ -6508,19 +6508,19 @@
       <c r="K6" t="n">
         <v>85.81830792661792</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 13.677x + -32186.552</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-32186.55168588873</v>
       </c>
       <c r="Y6" t="n">
         <v>2.433992573529441e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>2743.957567616646</v>
+        <v>289.3399999999997</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000005e-08</v>
@@ -6560,19 +6560,19 @@
       <c r="K7" t="n">
         <v>85.87163150708022</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 13.855x + -32270.020</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-32270.01974311587</v>
       </c>
       <c r="Y7" t="n">
         <v>9.579990235952119e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>2713.596310572661</v>
+        <v>285.75</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000156968e-08</v>
@@ -6612,19 +6612,19 @@
       <c r="K8" t="n">
         <v>85.73117651278226</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 13.397x + -30808.799</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-30808.79912314165</v>
       </c>
       <c r="Y8" t="n">
         <v>1.218697654527602e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2685.741271748901</v>
+        <v>288.29</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000116112e-08</v>
@@ -6664,19 +6664,19 @@
       <c r="K9" t="n">
         <v>85.73842902141354</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 13.420x + -30546.624</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-30546.62388083949</v>
       </c>
       <c r="Y9" t="n">
         <v>1.479441224105351e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2658.180877920011</v>
+        <v>278.8700000000003</v>
       </c>
       <c r="AA9" t="n">
         <v>1.00000000000071e-08</v>
@@ -6716,19 +6716,19 @@
       <c r="K10" t="n">
         <v>85.55946921631539</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 12.877x + -28941.911</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-28941.91113499524</v>
       </c>
       <c r="Y10" t="n">
         <v>1.380012355386828e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2631.183480824692</v>
+        <v>280.8099999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000012889e-08</v>
@@ -6768,19 +6768,19 @@
       <c r="K11" t="n">
         <v>85.80128589062012</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 13.622x + -30427.587</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-30427.58664542211</v>
       </c>
       <c r="Y11" t="n">
         <v>9.303005940359943e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2603.979594122613</v>
+        <v>270.3899999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000039895e-08</v>
@@ -6820,19 +6820,19 @@
       <c r="K12" t="n">
         <v>85.69226677238517</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 13.276x + -29298.806</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-29298.80621146221</v>
       </c>
       <c r="Y12" t="n">
         <v>9.344160738297588e-12</v>
       </c>
       <c r="Z12" t="n">
-        <v>2577.717880925443</v>
+        <v>273.3499999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000002961e-08</v>
@@ -6872,19 +6872,19 @@
       <c r="K13" t="n">
         <v>85.70841168783397</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 13.326x + -29107.365</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-29107.36544144287</v>
       </c>
       <c r="Y13" t="n">
         <v>1.60985710614627e-18</v>
       </c>
       <c r="Z13" t="n">
-        <v>2550.833724812115</v>
+        <v>270.9000000000001</v>
       </c>
       <c r="AA13" t="n">
         <v>1e-08</v>
@@ -6924,19 +6924,19 @@
       <c r="K14" t="n">
         <v>85.85919159752454</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 13.813x + -29948.805</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-29948.80514446605</v>
       </c>
       <c r="Y14" t="n">
         <v>2.883939939052494e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>2523.973641391239</v>
+        <v>259.1499999999996</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000010549e-08</v>
@@ -6976,19 +6976,19 @@
       <c r="K15" t="n">
         <v>85.99574808611756</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 14.285x + -30744.115</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-30744.11453532423</v>
       </c>
       <c r="Y15" t="n">
         <v>1.502981915748685e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>2497.596764095284</v>
+        <v>251.8599999999997</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000210954e-08</v>
@@ -7028,19 +7028,19 @@
       <c r="K16" t="n">
         <v>86.03822384549272</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 14.439x + -30783.166</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-30783.16612355501</v>
       </c>
       <c r="Y16" t="n">
         <v>9.583345736296063e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>2472.138018937787</v>
+        <v>249.02</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000263e-08</v>
@@ -7080,19 +7080,19 @@
       <c r="K17" t="n">
         <v>85.66248540855653</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 13.184x + -27650.595</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-27650.59457274326</v>
       </c>
       <c r="Y17" t="n">
         <v>8.076491277200882e-10</v>
       </c>
       <c r="Z17" t="n">
-        <v>2446.151413445513</v>
+        <v>260.0900000000001</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000042e-08</v>
@@ -7132,19 +7132,19 @@
       <c r="K18" t="n">
         <v>85.81927658141153</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 13.680x + -28482.025</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-28482.02510896072</v>
       </c>
       <c r="Y18" t="n">
         <v>1.786965320502517e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>2420.467735693825</v>
+        <v>248.8600000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000001139e-08</v>
@@ -7184,19 +7184,19 @@
       <c r="K19" t="n">
         <v>85.77189410797133</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 13.527x + -27841.277</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-27841.27747218926</v>
       </c>
       <c r="Y19" t="n">
         <v>2.728071149661126e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>2395.345596222047</v>
+        <v>253.1699999999998</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000271e-08</v>
@@ -7236,19 +7236,19 @@
       <c r="K20" t="n">
         <v>86.04079009269893</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 14.448x + -29578.208</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-29578.20759198589</v>
       </c>
       <c r="Y20" t="n">
         <v>1.151201381785353e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>2369.931667734592</v>
+        <v>238.3699999999999</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000026403e-08</v>
@@ -7288,19 +7288,19 @@
       <c r="K21" t="n">
         <v>85.61859359939417</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 13.052x + -26252.448</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-26252.44812079285</v>
       </c>
       <c r="Y21" t="n">
         <v>90.94930141049421</v>
       </c>
       <c r="Z21" t="n">
-        <v>2331.396859334923</v>
+        <v>250.77</v>
       </c>
       <c r="AA21" t="n">
         <v>1.277275645378917e-08</v>
@@ -7340,19 +7340,19 @@
       <c r="K22" t="n">
         <v>85.96295309951256</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 14.169x + -28367.557</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-28367.55741277962</v>
       </c>
       <c r="Y22" t="n">
         <v>1.338455413330206e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>2319.952965833445</v>
+        <v>235.6599999999999</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000194e-08</v>
@@ -7478,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7538,19 +7538,19 @@
       <c r="K2" t="n">
         <v>83.59616956072668</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.910x + -21553.656</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-21553.65571513454</v>
       </c>
       <c r="Y2" t="n">
         <v>1.039085601399273e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2726.946789323578</v>
+        <v>710.71</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000027e-08</v>
@@ -7590,19 +7590,19 @@
       <c r="K3" t="n">
         <v>85.60455708824557</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.010x + -27564.707</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-27564.70733631978</v>
       </c>
       <c r="Y3" t="n">
         <v>1.810395849991254e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>2434.128637667324</v>
+        <v>401.48</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -7642,19 +7642,19 @@
       <c r="K4" t="n">
         <v>86.13770616101534</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.812x + -30393.900</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-30393.90042377313</v>
       </c>
       <c r="Y4" t="n">
         <v>9.372927700212982e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2356.440625562518</v>
+        <v>327.4599999999998</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000119e-08</v>
@@ -7694,19 +7694,19 @@
       <c r="K5" t="n">
         <v>86.27934440394502</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.378x + -31037.190</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-31037.18969553097</v>
       </c>
       <c r="Y5" t="n">
         <v>1.55874122150104e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2317.316779300467</v>
+        <v>303.99</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000024045e-08</v>
@@ -7746,19 +7746,19 @@
       <c r="K6" t="n">
         <v>86.05706977543211</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.508x + -28738.032</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-28738.03201182807</v>
       </c>
       <c r="Y6" t="n">
         <v>1.165904168561833e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2286.119522464697</v>
+        <v>293.5</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000247e-08</v>
@@ -7798,19 +7798,19 @@
       <c r="K7" t="n">
         <v>86.12476278051119</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 14.763x + -28895.870</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-28895.87027455024</v>
       </c>
       <c r="Y7" t="n">
         <v>2.74042746161858e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>2256.056384785873</v>
+        <v>278.8600000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000002347e-08</v>
@@ -7850,19 +7850,19 @@
       <c r="K8" t="n">
         <v>86.31408704074593</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 15.523x + -30076.593</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-30076.5926785157</v>
       </c>
       <c r="Y8" t="n">
         <v>9.72685249777086e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2225.900919931732</v>
+        <v>262.6400000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -7902,19 +7902,19 @@
       <c r="K9" t="n">
         <v>86.21687968130527</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 15.123x + -28852.461</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-28852.46110564734</v>
       </c>
       <c r="Y9" t="n">
         <v>1.536564702534079e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2196.0039154832</v>
+        <v>256.4499999999998</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000428e-08</v>
@@ -7954,19 +7954,19 @@
       <c r="K10" t="n">
         <v>86.27033952714685</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 15.340x + -28908.513</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-28908.51322135519</v>
       </c>
       <c r="Y10" t="n">
         <v>1.760263210525344e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2167.425630607172</v>
+        <v>245.7700000000002</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000014e-08</v>
@@ -8006,19 +8006,19 @@
       <c r="K11" t="n">
         <v>86.34295633619254</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 15.646x + -29159.128</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-29159.12776337244</v>
       </c>
       <c r="Y11" t="n">
         <v>2.14325529618481e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2139.909577629029</v>
+        <v>249.0799999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000067e-08</v>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -8204,19 +8204,19 @@
       <c r="K2" t="n">
         <v>85.75811165242861</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 13.482x + -33774.863</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-33774.86298556774</v>
       </c>
       <c r="Y2" t="n">
         <v>7.846913323843916e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>2877.138759700751</v>
+        <v>395.9899999999998</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000052073e-08</v>
@@ -8256,19 +8256,19 @@
       <c r="K3" t="n">
         <v>85.96653098710421</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.182x + -33888.873</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-33888.87326767434</v>
       </c>
       <c r="Y3" t="n">
         <v>5.405528003712421e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2768.959440272427</v>
+        <v>312.2599999999998</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000016458e-08</v>
@@ -8308,19 +8308,19 @@
       <c r="K4" t="n">
         <v>86.05187263551271</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.489x + -34009.825</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-34009.82532537974</v>
       </c>
       <c r="Y4" t="n">
         <v>7.964427138879586e-12</v>
       </c>
       <c r="Z4" t="n">
-        <v>2720.638480053613</v>
+        <v>289.2800000000002</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001424e-08</v>
@@ -8360,19 +8360,19 @@
       <c r="K5" t="n">
         <v>86.1169377044325</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.733x + -34167.617</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-34167.61706204643</v>
       </c>
       <c r="Y5" t="n">
         <v>4.281344064035811e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2687.522056680972</v>
+        <v>272.3499999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000001e-08</v>
@@ -8412,19 +8412,19 @@
       <c r="K6" t="n">
         <v>85.95980606102954</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.158x + -32371.818</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-32371.817969048</v>
       </c>
       <c r="Y6" t="n">
         <v>2.77543492875132e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2657.029005892974</v>
+        <v>266.0999999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001452e-08</v>
@@ -8464,19 +8464,19 @@
       <c r="K7" t="n">
         <v>85.96482790941235</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 14.176x + -32071.228</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-32071.22779888786</v>
       </c>
       <c r="Y7" t="n">
         <v>178.7874322610375</v>
       </c>
       <c r="Z7" t="n">
-        <v>2685.114667925638</v>
+        <v>258.7199999999998</v>
       </c>
       <c r="AA7" t="n">
         <v>1.393666145335805e-08</v>
@@ -8516,19 +8516,19 @@
       <c r="K8" t="n">
         <v>85.97733059189549</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 14.220x + -31831.516</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-31831.51642262445</v>
       </c>
       <c r="Y8" t="n">
         <v>180.7099134671621</v>
       </c>
       <c r="Z8" t="n">
-        <v>2664.709232403846</v>
+        <v>254.9499999999998</v>
       </c>
       <c r="AA8" t="n">
         <v>1.423279139325497e-08</v>
@@ -8568,19 +8568,19 @@
       <c r="K9" t="n">
         <v>86.02870966900606</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 14.404x + -31951.224</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-31951.22384277095</v>
       </c>
       <c r="Y9" t="n">
         <v>181.480830455624</v>
       </c>
       <c r="Z9" t="n">
-        <v>2646.651785233375</v>
+        <v>251.4900000000002</v>
       </c>
       <c r="AA9" t="n">
         <v>1.456808227389621e-08</v>
@@ -8620,19 +8620,19 @@
       <c r="K10" t="n">
         <v>85.87609696665561</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 13.870x + -30365.854</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-30365.85402702303</v>
       </c>
       <c r="Y10" t="n">
         <v>174.5742779311235</v>
       </c>
       <c r="Z10" t="n">
-        <v>2600.622594587256</v>
+        <v>256.9500000000003</v>
       </c>
       <c r="AA10" t="n">
         <v>1.390978337262408e-08</v>
@@ -8672,19 +8672,19 @@
       <c r="K11" t="n">
         <v>86.08516463464437</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 14.613x + -31778.105</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-31778.10502104715</v>
       </c>
       <c r="Y11" t="n">
         <v>6.872746667149741e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2519.116916451603</v>
+        <v>243.1700000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000306e-08</v>
@@ -8724,19 +8724,19 @@
       <c r="K12" t="n">
         <v>86.11355201084075</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 14.720x + -31683.217</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-31683.216587006</v>
       </c>
       <c r="Y12" t="n">
         <v>4.581051058942064e-12</v>
       </c>
       <c r="Z12" t="n">
-        <v>2491.604678133055</v>
+        <v>241.3200000000002</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -8776,19 +8776,19 @@
       <c r="K13" t="n">
         <v>86.08020508541409</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 14.594x + -31062.926</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-31062.92627946116</v>
       </c>
       <c r="Y13" t="n">
         <v>6.067583795970227e-12</v>
       </c>
       <c r="Z13" t="n">
-        <v>2464.038823681705</v>
+        <v>240.0899999999997</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000001e-08</v>
@@ -8828,19 +8828,19 @@
       <c r="K14" t="n">
         <v>85.74036323023644</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 13.426x + -28115.634</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-28115.63359985818</v>
       </c>
       <c r="Y14" t="n">
         <v>5.667103645306754e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>2437.282706316727</v>
+        <v>246.6600000000003</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000007e-08</v>
@@ -8880,19 +8880,19 @@
       <c r="K15" t="n">
         <v>85.76039479724962</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 13.490x + -27958.581</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-27958.58111479407</v>
       </c>
       <c r="Y15" t="n">
         <v>2.156250906290475e-12</v>
       </c>
       <c r="Z15" t="n">
-        <v>2410.525587010599</v>
+        <v>246.6500000000001</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -8932,19 +8932,19 @@
       <c r="K16" t="n">
         <v>86.1750776523389</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 14.957x + -30875.338</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-30875.33796739028</v>
       </c>
       <c r="Y16" t="n">
         <v>8.470728801220286e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>2384.055225509795</v>
+        <v>230.3899999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000001024e-08</v>
@@ -8984,19 +8984,19 @@
       <c r="K17" t="n">
         <v>85.91530846486062</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 14.003x + -28487.343</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-28487.34318003853</v>
       </c>
       <c r="Y17" t="n">
         <v>1.230705697416968e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>2357.918282023292</v>
+        <v>233.6099999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000016e-08</v>
@@ -9036,19 +9036,19 @@
       <c r="K18" t="n">
         <v>85.99763930489898</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 14.292x + -28816.333</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-28816.33325317343</v>
       </c>
       <c r="Y18" t="n">
         <v>6.194129678660083e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>2331.314977939496</v>
+        <v>223.9300000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -9088,19 +9088,19 @@
       <c r="K19" t="n">
         <v>85.9876950211288</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 14.257x + -28409.744</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-28409.74441714353</v>
       </c>
       <c r="Y19" t="n">
         <v>1.19045633652048e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>2306.018635037247</v>
+        <v>227.05</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -9140,19 +9140,19 @@
       <c r="K20" t="n">
         <v>85.92609497672279</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 14.040x + -27664.711</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-27664.71148502776</v>
       </c>
       <c r="Y20" t="n">
         <v>5.042093175659922e-11</v>
       </c>
       <c r="Z20" t="n">
-        <v>2280.661471813982</v>
+        <v>222.6499999999999</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000146e-08</v>
@@ -9192,19 +9192,19 @@
       <c r="K21" t="n">
         <v>85.96545586314856</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 14.178x + -27659.801</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-27659.80082951646</v>
       </c>
       <c r="Y21" t="n">
         <v>1.610994835102721e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>2255.78639408294</v>
+        <v>224.9299999999998</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000015152e-08</v>
@@ -9244,19 +9244,19 @@
       <c r="K22" t="n">
         <v>85.93625423983973</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 14.076x + -27152.256</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-27152.2559054583</v>
       </c>
       <c r="Y22" t="n">
         <v>1.641316762978337e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>2230.140017103029</v>
+        <v>216.4099999999999</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000507e-08</v>
@@ -9382,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -9442,19 +9442,19 @@
       <c r="K2" t="n">
         <v>83.64983059297444</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.986x + -16149.241</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-16149.2406227118</v>
       </c>
       <c r="Y2" t="n">
         <v>2.18963506839997e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2000.054434608405</v>
+        <v>672.26</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000051e-08</v>
@@ -9494,19 +9494,19 @@
       <c r="K3" t="n">
         <v>86.27031403448062</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 15.340x + -24860.582</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-24860.58184285437</v>
       </c>
       <c r="Y3" t="n">
         <v>6.899639652387902e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>1828.839227429705</v>
+        <v>320.5600000000002</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000072e-08</v>
@@ -9546,19 +9546,19 @@
       <c r="K4" t="n">
         <v>86.44820967343497</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.111x + -25272.296</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-25272.2961287095</v>
       </c>
       <c r="Y4" t="n">
         <v>3.295643239239275e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>1778.897592392325</v>
+        <v>262.3300000000002</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000046e-08</v>
@@ -9598,19 +9598,19 @@
       <c r="K5" t="n">
         <v>86.65293236683763</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 17.099x + -26428.632</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-26428.63204935795</v>
       </c>
       <c r="Y5" t="n">
         <v>7.339943731119014e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1748.353368977718</v>
+        <v>241.1200000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000076e-08</v>
@@ -9650,19 +9650,19 @@
       <c r="K6" t="n">
         <v>86.61506210747608</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 16.907x + -25695.896</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-25695.89624876585</v>
       </c>
       <c r="Y6" t="n">
         <v>1.06089984688109e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1720.612338470688</v>
+        <v>233.0799999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000351e-08</v>
@@ -9702,19 +9702,19 @@
       <c r="K7" t="n">
         <v>86.74794040825911</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 17.599x + -26403.058</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-26403.05827183233</v>
       </c>
       <c r="Y7" t="n">
         <v>1.37158877233294e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1693.155492008821</v>
+        <v>217.29</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000022e-08</v>
@@ -9754,19 +9754,19 @@
       <c r="K8" t="n">
         <v>86.73482270002181</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 17.529x + -25876.916</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-25876.91593827373</v>
       </c>
       <c r="Y8" t="n">
         <v>6.830612224195562e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>1666.728511405334</v>
+        <v>217.1500000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000001403e-08</v>
@@ -9806,19 +9806,19 @@
       <c r="K9" t="n">
         <v>86.7597429707979</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 17.664x + -25678.132</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-25678.13215329937</v>
       </c>
       <c r="Y9" t="n">
         <v>8.284306897986913e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>1640.36726593241</v>
+        <v>205.1599999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -9858,19 +9858,19 @@
       <c r="K10" t="n">
         <v>87.02495968943157</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 19.242x + -27710.362</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-27710.36230917755</v>
       </c>
       <c r="Y10" t="n">
         <v>140.6764401548427</v>
       </c>
       <c r="Z10" t="n">
-        <v>1567.082173047818</v>
+        <v>192.73</v>
       </c>
       <c r="AA10" t="n">
         <v>1.280368087482346e-08</v>
@@ -9910,19 +9910,19 @@
       <c r="K11" t="n">
         <v>86.77386829314423</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 17.741x + -25053.076</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-25053.07583818535</v>
       </c>
       <c r="Y11" t="n">
         <v>1.253218068662767e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>1593.111746086915</v>
+        <v>196.6299999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000105e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>84.81640921430224</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.023x + -29914.981</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.02312575118854</v>
       </c>
       <c r="X2" t="n">
         <v>-29914.98110711802</v>
@@ -600,7 +598,7 @@
         <v>2.57799203963456e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>501.1500000000001</v>
+        <v>3162.623821967788</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000012e-08</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>85.69713293948777</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.291x + -34761.029</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.29067903633629</v>
       </c>
       <c r="X3" t="n">
         <v>-34761.02860804056</v>
@@ -652,7 +648,7 @@
         <v>169.2984843203908</v>
       </c>
       <c r="Z3" t="n">
-        <v>373.1700000000001</v>
+        <v>3196.958776527149</v>
       </c>
       <c r="AA3" t="n">
         <v>1.449986721646182e-08</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>85.66424764890175</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.189x + -33591.477</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.18949202404524</v>
       </c>
       <c r="X4" t="n">
         <v>-33591.47731365899</v>
@@ -704,7 +698,7 @@
         <v>1.156849441056458e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>347.73</v>
+        <v>2970.216919520805</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000201e-08</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>85.54943589274184</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 12.848x + -32031.922</t>
-        </is>
+      <c r="W5" t="n">
+        <v>12.84792135780487</v>
       </c>
       <c r="X5" t="n">
         <v>-32031.92196320686</v>
@@ -756,7 +748,7 @@
         <v>174.5331168529545</v>
       </c>
       <c r="Z5" t="n">
-        <v>332.6300000000001</v>
+        <v>3043.918106517487</v>
       </c>
       <c r="AA5" t="n">
         <v>1.432291297293793e-08</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>85.60411717932806</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 13.008x + -31913.066</t>
-        </is>
+      <c r="W6" t="n">
+        <v>13.00837999458543</v>
       </c>
       <c r="X6" t="n">
         <v>-31913.06618704371</v>
@@ -808,7 +798,7 @@
         <v>170.9042396417636</v>
       </c>
       <c r="Z6" t="n">
-        <v>316.79</v>
+        <v>2966.506574842459</v>
       </c>
       <c r="AA6" t="n">
         <v>1.428577322949221e-08</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>85.87504135878514</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.866x + -33633.359</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.86601887606812</v>
       </c>
       <c r="X7" t="n">
         <v>-33633.35851403059</v>
@@ -860,7 +848,7 @@
         <v>1.703271881903417e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>289.71</v>
+        <v>2822.798465620636</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000050927e-08</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>85.68327670184654</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 13.248x + -31559.418</t>
-        </is>
+      <c r="W8" t="n">
+        <v>13.2478562366808</v>
       </c>
       <c r="X8" t="n">
         <v>-31559.41778611071</v>
@@ -912,7 +898,7 @@
         <v>6.229611816513598e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>290.3000000000002</v>
+        <v>2780.688961265309</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000083773e-08</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>85.68809269322692</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 13.263x + -31152.413</t>
-        </is>
+      <c r="W9" t="n">
+        <v>13.26270894555962</v>
       </c>
       <c r="X9" t="n">
         <v>-31152.41284712239</v>
@@ -964,7 +948,7 @@
         <v>1.282739444726501e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>282.9399999999996</v>
+        <v>2741.026458025862</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000168214e-08</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>85.75111752662106</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 13.460x + -31221.485</t>
-        </is>
+      <c r="W10" t="n">
+        <v>13.46017764347877</v>
       </c>
       <c r="X10" t="n">
         <v>-31221.48532913067</v>
@@ -1016,7 +998,7 @@
         <v>171.0881415868463</v>
       </c>
       <c r="Z10" t="n">
-        <v>279.5799999999999</v>
+        <v>2789.254748204574</v>
       </c>
       <c r="AA10" t="n">
         <v>1.459199413072242e-08</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>85.35115376309354</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 12.298x + -27995.567</t>
-        </is>
+      <c r="W11" t="n">
+        <v>12.29767327067961</v>
       </c>
       <c r="X11" t="n">
         <v>-27995.56745854828</v>
@@ -1068,7 +1048,7 @@
         <v>5.809456445001685e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>287.8099999999999</v>
+        <v>2670.130623209288</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000014896e-08</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>85.67769190834748</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 13.231x + -32276.242</t>
-        </is>
+      <c r="W2" t="n">
+        <v>13.23067387865224</v>
       </c>
       <c r="X2" t="n">
         <v>-32276.24153380185</v>
@@ -1266,7 +1244,7 @@
         <v>2.062713675080443e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>308.6999999999998</v>
+        <v>2817.482606988762</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000009562e-08</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>85.71322709819221</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.341x + -30869.332</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.34076500332833</v>
       </c>
       <c r="X3" t="n">
         <v>-30869.33157610318</v>
@@ -1318,7 +1294,7 @@
         <v>2.199384125382961e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>281.5499999999997</v>
+        <v>2696.651472895748</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000047e-08</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>86.17691980166539</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.965x + -34249.295</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.96456239221126</v>
       </c>
       <c r="X4" t="n">
         <v>-34249.29508316806</v>
@@ -1370,7 +1344,7 @@
         <v>8.977309999750351e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>254.0499999999997</v>
+        <v>2651.245768338757</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000035e-08</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>85.99839542539505</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.295x + -32210.214</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.29491325704733</v>
       </c>
       <c r="X5" t="n">
         <v>-32210.21361267188</v>
@@ -1422,7 +1394,7 @@
         <v>1.412983682853059e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>254.3399999999997</v>
+        <v>2617.722928009755</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000002194e-08</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>85.87587358970984</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 13.869x + -30819.615</t>
-        </is>
+      <c r="W6" t="n">
+        <v>13.86882667000138</v>
       </c>
       <c r="X6" t="n">
         <v>-30819.6149635234</v>
@@ -1474,7 +1444,7 @@
         <v>4.754991111739672e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>254.6800000000003</v>
+        <v>2586.391296198517</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000000004e-08</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>85.91292744449579</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.995x + -30711.920</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.99499638884589</v>
       </c>
       <c r="X7" t="n">
         <v>-30711.9201904497</v>
@@ -1526,7 +1494,7 @@
         <v>1.754305017899591e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>250.9200000000001</v>
+        <v>2552.541169396459</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000005444e-08</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>86.03553267229474</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 14.429x + -31356.984</t>
-        </is>
+      <c r="W8" t="n">
+        <v>14.42925563003187</v>
       </c>
       <c r="X8" t="n">
         <v>-31356.98386594918</v>
@@ -1578,7 +1544,7 @@
         <v>2.503501385785679e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>242.4200000000001</v>
+        <v>2520.051021445846</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000103e-08</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>85.87061031206963</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 13.851x + -29651.049</t>
-        </is>
+      <c r="W9" t="n">
+        <v>13.85108836176732</v>
       </c>
       <c r="X9" t="n">
         <v>-29651.04948460772</v>
@@ -1630,7 +1594,7 @@
         <v>1.103607156150456e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>244.5599999999999</v>
+        <v>2488.499623189355</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000004e-08</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>85.74332769620638</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 13.435x + -28365.293</t>
-        </is>
+      <c r="W10" t="n">
+        <v>13.43545451619287</v>
       </c>
       <c r="X10" t="n">
         <v>-28365.29311611508</v>
@@ -1682,7 +1644,7 @@
         <v>1.69315635028907e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>249.9300000000003</v>
+        <v>2458.740340453454</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>85.94015713521885</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 14.089x + -29499.889</t>
-        </is>
+      <c r="W11" t="n">
+        <v>14.08918005742417</v>
       </c>
       <c r="X11" t="n">
         <v>-29499.88895770364</v>
@@ -1734,7 +1694,7 @@
         <v>7.469416570882947e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>237.77</v>
+        <v>2430.19508284942</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000012e-08</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>86.12324255767194</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 14.757x + -30652.092</t>
-        </is>
+      <c r="W12" t="n">
+        <v>14.75674375911331</v>
       </c>
       <c r="X12" t="n">
         <v>-30652.09157851015</v>
@@ -1786,7 +1744,7 @@
         <v>1.227592549317984e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>228.5300000000002</v>
+        <v>2402.334189525924</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000003668e-08</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>86.20355099496464</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 15.070x + -30985.042</t>
-        </is>
+      <c r="W13" t="n">
+        <v>15.06984640200759</v>
       </c>
       <c r="X13" t="n">
         <v>-30985.04205280727</v>
@@ -1838,7 +1794,7 @@
         <v>1.068240441306971e-07</v>
       </c>
       <c r="Z13" t="n">
-        <v>222.96</v>
+        <v>2375.18471007619</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000007576e-08</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>85.87991980962975</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 13.882x + -28104.001</t>
-        </is>
+      <c r="W14" t="n">
+        <v>13.88249400714191</v>
       </c>
       <c r="X14" t="n">
         <v>-28104.00107703159</v>
@@ -1890,7 +1844,7 @@
         <v>6.264119972202835e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>227.1699999999998</v>
+        <v>2347.983299388562</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000001325e-08</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>85.94789243767886</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 14.116x + -28294.576</t>
-        </is>
+      <c r="W15" t="n">
+        <v>14.11616585849287</v>
       </c>
       <c r="X15" t="n">
         <v>-28294.57574853358</v>
@@ -1942,7 +1894,7 @@
         <v>2.648564380359053e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>224.5599999999999</v>
+        <v>2321.447823498657</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000003e-08</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>85.68494044969964</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 13.253x + -26179.976</t>
-        </is>
+      <c r="W16" t="n">
+        <v>13.25298355993706</v>
       </c>
       <c r="X16" t="n">
         <v>-26179.97634280716</v>
@@ -1994,7 +1944,7 @@
         <v>3.444975292971956e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>226.1099999999997</v>
+        <v>2295.454333830792</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000037474e-08</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>85.83022020495159</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 13.716x + -26857.777</t>
-        </is>
+      <c r="W17" t="n">
+        <v>13.716453327074</v>
       </c>
       <c r="X17" t="n">
         <v>-26857.77674374761</v>
@@ -2046,7 +1994,7 @@
         <v>7.284878717459521e-10</v>
       </c>
       <c r="Z17" t="n">
-        <v>217.5700000000002</v>
+        <v>2269.520303373984</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>85.55474785019742</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 12.863x + -24813.235</t>
-        </is>
+      <c r="W18" t="n">
+        <v>12.86333617437917</v>
       </c>
       <c r="X18" t="n">
         <v>-24813.23486023556</v>
@@ -2098,7 +2044,7 @@
         <v>3.122146396175027e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>227.8299999999999</v>
+        <v>2244.281534153596</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000082565e-08</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>85.89717706372096</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 13.941x + -26751.197</t>
-        </is>
+      <c r="W19" t="n">
+        <v>13.94108777677551</v>
       </c>
       <c r="X19" t="n">
         <v>-26751.19685487385</v>
@@ -2150,7 +2094,7 @@
         <v>2.153696038650151e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>207.9799999999998</v>
+        <v>2220.052834556127</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000071e-08</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>85.67983918752189</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 13.237x + -25046.523</t>
-        </is>
+      <c r="W20" t="n">
+        <v>13.23727502118751</v>
       </c>
       <c r="X20" t="n">
         <v>-25046.5227868827</v>
@@ -2202,7 +2144,7 @@
         <v>5.228405024624928e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>213.7199999999998</v>
+        <v>2195.472264591197</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000292e-08</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>85.65409604666891</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 13.159x + -24639.744</t>
-        </is>
+      <c r="W21" t="n">
+        <v>13.15856460221548</v>
       </c>
       <c r="X21" t="n">
         <v>-24639.74399748924</v>
@@ -2254,7 +2194,7 @@
         <v>5.819276857280407e-10</v>
       </c>
       <c r="Z21" t="n">
-        <v>209.28</v>
+        <v>2171.634071564724</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>85.60819168391087</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 13.020x + -24133.754</t>
-        </is>
+      <c r="W22" t="n">
+        <v>13.02049600043847</v>
       </c>
       <c r="X22" t="n">
         <v>-24133.75447069373</v>
@@ -2306,7 +2244,7 @@
         <v>6.578424228709979e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>195.8400000000001</v>
+        <v>2147.228739683565</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000655e-08</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>85.39177638401414</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.407x + -33423.422</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.40655543791352</v>
       </c>
       <c r="X2" t="n">
         <v>-33423.4216940086</v>
@@ -2504,7 +2440,7 @@
         <v>3.098250106241304e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>389.6800000000003</v>
+        <v>3120.664929391704</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000042e-08</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>85.53496643231591</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.806x + -32428.984</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.80611795201077</v>
       </c>
       <c r="X3" t="n">
         <v>-32428.9839919529</v>
@@ -2556,7 +2490,7 @@
         <v>1.31867104258221e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>315.9400000000001</v>
+        <v>2965.022094740954</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000151e-08</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>85.86922017233529</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.846x + -34518.215</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.84641084333695</v>
       </c>
       <c r="X4" t="n">
         <v>-34518.214625006</v>
@@ -2608,7 +2540,7 @@
         <v>177.1211480723434</v>
       </c>
       <c r="Z4" t="n">
-        <v>286.3600000000001</v>
+        <v>3039.279138324308</v>
       </c>
       <c r="AA4" t="n">
         <v>1.408723919991782e-08</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>85.61970620755656</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.055x + -31987.110</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.05485737165704</v>
       </c>
       <c r="X5" t="n">
         <v>-31987.10972683296</v>
@@ -2660,7 +2590,7 @@
         <v>176.2029875329841</v>
       </c>
       <c r="Z5" t="n">
-        <v>288.9400000000001</v>
+        <v>2981.14356315627</v>
       </c>
       <c r="AA5" t="n">
         <v>1.429785062539998e-08</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>85.75675250055059</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 13.478x + -32674.387</t>
-        </is>
+      <c r="W6" t="n">
+        <v>13.4781182305421</v>
       </c>
       <c r="X6" t="n">
         <v>-32674.38718010858</v>
@@ -2712,7 +2640,7 @@
         <v>6.582852024490997e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>282.25</v>
+        <v>2837.911472723138</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000001e-08</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>85.64471569966712</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.130x + -31411.495</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.13011476847629</v>
       </c>
       <c r="X7" t="n">
         <v>-31411.49473469492</v>
@@ -2764,7 +2690,7 @@
         <v>1.027052330947454e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>279.8200000000002</v>
+        <v>2802.796779623428</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000002e-08</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>85.7339394940268</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 13.406x + -31723.446</t>
-        </is>
+      <c r="W8" t="n">
+        <v>13.40577828343277</v>
       </c>
       <c r="X8" t="n">
         <v>-31723.44635492421</v>
@@ -2816,7 +2740,7 @@
         <v>1.015787469702198e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>274.46</v>
+        <v>2768.876023266081</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000159084e-08</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>85.58268283310457</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 12.945x + -30185.322</t>
-        </is>
+      <c r="W9" t="n">
+        <v>12.94500985761681</v>
       </c>
       <c r="X9" t="n">
         <v>-30185.32181046786</v>
@@ -2868,7 +2790,7 @@
         <v>1.414841070470384e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>280.02</v>
+        <v>2735.507623836769</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000099752e-08</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>85.77806666185957</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 13.546x + -31338.047</t>
-        </is>
+      <c r="W10" t="n">
+        <v>13.54641045978506</v>
       </c>
       <c r="X10" t="n">
         <v>-31338.04713138255</v>
@@ -2920,7 +2840,7 @@
         <v>2.117614611909924e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>268.6600000000003</v>
+        <v>2703.72269973288</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>85.63242873926892</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 13.093x + -29864.520</t>
-        </is>
+      <c r="W11" t="n">
+        <v>13.09303392757421</v>
       </c>
       <c r="X11" t="n">
         <v>-29864.52036155956</v>
@@ -2972,7 +2890,7 @@
         <v>9.363843093238253e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>273.1700000000001</v>
+        <v>2671.904036300058</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000042e-08</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>85.80004939311935</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 13.618x + -30800.825</t>
-        </is>
+      <c r="W12" t="n">
+        <v>13.61756961916917</v>
       </c>
       <c r="X12" t="n">
         <v>-30800.82457272207</v>
@@ -3024,7 +2940,7 @@
         <v>6.803671400167015e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>262.3699999999999</v>
+        <v>2641.506310427568</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000008e-08</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>85.56015391330622</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 12.879x + -28701.885</t>
-        </is>
+      <c r="W13" t="n">
+        <v>12.87906187229454</v>
       </c>
       <c r="X13" t="n">
         <v>-28701.88478166432</v>
@@ -3076,7 +2990,7 @@
         <v>2.552840944951873e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>264.5299999999997</v>
+        <v>2611.438701930438</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000001204e-08</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>85.60673631577249</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 13.016x + -28685.033</t>
-        </is>
+      <c r="W14" t="n">
+        <v>13.01616572166703</v>
       </c>
       <c r="X14" t="n">
         <v>-28685.03259873531</v>
@@ -3128,7 +3040,7 @@
         <v>1.488659556647301e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>264.27</v>
+        <v>2582.519623882753</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000183e-08</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>85.610437234266</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 13.027x + -28394.662</t>
-        </is>
+      <c r="W15" t="n">
+        <v>13.02718299671588</v>
       </c>
       <c r="X15" t="n">
         <v>-28394.66167818223</v>
@@ -3180,7 +3090,7 @@
         <v>7.3046240432988e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>262.4000000000001</v>
+        <v>2553.871728548393</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000013776e-08</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>85.66205234667723</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 13.183x + -28461.835</t>
-        </is>
+      <c r="W16" t="n">
+        <v>13.18279167020717</v>
       </c>
       <c r="X16" t="n">
         <v>-28461.83541249934</v>
@@ -3232,7 +3140,7 @@
         <v>1.282230997996266e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>252.0800000000004</v>
+        <v>2526.138178742537</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000003142e-08</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>85.40347199469859</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 12.438x + -26483.935</t>
-        </is>
+      <c r="W17" t="n">
+        <v>12.43825960549582</v>
       </c>
       <c r="X17" t="n">
         <v>-26483.93509906495</v>
@@ -3284,7 +3190,7 @@
         <v>5.574439715375114e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>253.9699999999998</v>
+        <v>2499.201143920776</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000002e-08</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>85.5609320108414</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 12.881x + -27191.338</t>
-        </is>
+      <c r="W18" t="n">
+        <v>12.8813284272303</v>
       </c>
       <c r="X18" t="n">
         <v>-27191.33839576717</v>
@@ -3336,7 +3240,7 @@
         <v>4.634196782120349e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>251.3800000000001</v>
+        <v>2472.918314070274</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000825e-08</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>85.39634455312655</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 12.419x + -25897.572</t>
-        </is>
+      <c r="W19" t="n">
+        <v>12.41891958525885</v>
       </c>
       <c r="X19" t="n">
         <v>-25897.57203092706</v>
@@ -3388,7 +3290,7 @@
         <v>1.82262901452101e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>246.9200000000001</v>
+        <v>2446.808083731452</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000741e-08</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>85.5448689275364</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 12.835x + -26556.738</t>
-        </is>
+      <c r="W20" t="n">
+        <v>12.83469776916752</v>
       </c>
       <c r="X20" t="n">
         <v>-26556.73841351583</v>
@@ -3440,7 +3340,7 @@
         <v>5.361737835006235e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>237.5899999999997</v>
+        <v>2421.562315616129</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000005e-08</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>85.45268774548107</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 12.573x + -25706.558</t>
-        </is>
+      <c r="W21" t="n">
+        <v>12.57345564903139</v>
       </c>
       <c r="X21" t="n">
         <v>-25706.5580828153</v>
@@ -3492,7 +3390,7 @@
         <v>7.639996898130592e-12</v>
       </c>
       <c r="Z21" t="n">
-        <v>237.4700000000003</v>
+        <v>2396.115690016146</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>85.11598921882953</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 11.703x + -23581.447</t>
-        </is>
+      <c r="W22" t="n">
+        <v>11.70286889378427</v>
       </c>
       <c r="X22" t="n">
         <v>-23581.44735841637</v>
@@ -3544,7 +3440,7 @@
         <v>9.386260832158776e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>238.7299999999998</v>
+        <v>2370.972297857967</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000001279e-08</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>83.72014836631793</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.087x + -22726.481</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.087183331123452</v>
       </c>
       <c r="X2" t="n">
         <v>-22726.48146502904</v>
@@ -3742,7 +3636,7 @@
         <v>161.2417281774964</v>
       </c>
       <c r="Z2" t="n">
-        <v>721.3899999999999</v>
+        <v>2997.753554063162</v>
       </c>
       <c r="AA2" t="n">
         <v>1.988846993442448e-08</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>85.43516227096887</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.525x + -27597.763</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.5249795278522</v>
       </c>
       <c r="X3" t="n">
         <v>-27597.76330893855</v>
@@ -3794,7 +3686,7 @@
         <v>6.944598466089181e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>441.8000000000002</v>
+        <v>2541.080020887905</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000079e-08</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>86.00043112084253</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.302x + -30499.421</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.30221277152701</v>
       </c>
       <c r="X4" t="n">
         <v>-30499.42147381005</v>
@@ -3846,7 +3736,7 @@
         <v>5.339634416928426e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>350.3499999999999</v>
+        <v>2457.190193690232</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>85.85690537485016</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.805x + -28740.962</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.80511105378638</v>
       </c>
       <c r="X5" t="n">
         <v>-28740.96151745195</v>
@@ -3898,7 +3786,7 @@
         <v>1.141607515479345e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>332.4400000000001</v>
+        <v>2411.008026712254</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000068516e-08</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>86.10034161816279</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.670x + -30139.688</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.66981819561738</v>
       </c>
       <c r="X6" t="n">
         <v>-30139.68816408904</v>
@@ -3950,7 +3836,7 @@
         <v>1.784582872436847e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>304.1600000000001</v>
+        <v>2370.845084032311</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000003383e-08</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>86.15477108984886</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 14.878x + -30131.405</t>
-        </is>
+      <c r="W7" t="n">
+        <v>14.87810863730701</v>
       </c>
       <c r="X7" t="n">
         <v>-30131.40489930597</v>
@@ -4002,7 +3886,7 @@
         <v>2.78173516126112e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>284.8799999999999</v>
+        <v>2335.636458354546</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000749e-08</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>86.08138355222933</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 14.599x + -29114.336</t>
-        </is>
+      <c r="W8" t="n">
+        <v>14.59862617537217</v>
       </c>
       <c r="X8" t="n">
         <v>-29114.33606285213</v>
@@ -4054,7 +3936,7 @@
         <v>3.493521025855163e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>278.1100000000001</v>
+        <v>2303.725336890074</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000021807e-08</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>86.15446570425812</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 14.877x + -29316.099</t>
-        </is>
+      <c r="W9" t="n">
+        <v>14.876923566069</v>
       </c>
       <c r="X9" t="n">
         <v>-29316.09885609434</v>
@@ -4106,7 +3986,7 @@
         <v>1.349852838923336e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>266.3200000000002</v>
+        <v>2273.865132145196</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>86.19490023385163</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 15.035x + -29292.312</t>
-        </is>
+      <c r="W10" t="n">
+        <v>15.03548503297851</v>
       </c>
       <c r="X10" t="n">
         <v>-29292.31176746068</v>
@@ -4158,7 +4036,7 @@
         <v>1.415840859719032e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>261.2200000000003</v>
+        <v>2246.633628514866</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000001037e-08</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>86.20519091257219</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 15.076x + -29049.927</t>
-        </is>
+      <c r="W11" t="n">
+        <v>15.07637789644078</v>
       </c>
       <c r="X11" t="n">
         <v>-29049.92704982174</v>
@@ -4210,7 +4086,7 @@
         <v>7.662693213914232e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>246.4200000000001</v>
+        <v>2221.753564947094</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000021e-08</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>85.48563307455248</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.666x + -31764.896</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.66560033411639</v>
       </c>
       <c r="X2" t="n">
         <v>-31764.89629019741</v>
@@ -4408,7 +4282,7 @@
         <v>2.747300497441216e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>397.4200000000001</v>
+        <v>2907.479074605734</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000113e-08</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>85.77726979360258</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.544x + -32504.482</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.54384484897848</v>
       </c>
       <c r="X3" t="n">
         <v>-32504.48179644905</v>
@@ -4460,7 +4332,7 @@
         <v>168.5195265035647</v>
       </c>
       <c r="Z3" t="n">
-        <v>310.4899999999998</v>
+        <v>2889.556619265637</v>
       </c>
       <c r="AA3" t="n">
         <v>1.445891583989431e-08</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>85.79496131596672</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.601x + -31977.713</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.60103321445857</v>
       </c>
       <c r="X4" t="n">
         <v>-31977.71335055447</v>
@@ -4512,7 +4382,7 @@
         <v>7.555493351899843e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>281.9099999999999</v>
+        <v>2740.841542456011</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000084496e-08</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>86.00473210617741</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.318x + -33338.503</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.31765949167264</v>
       </c>
       <c r="X5" t="n">
         <v>-33338.50338005289</v>
@@ -4564,7 +4432,7 @@
         <v>1.342753719515469e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>264.1599999999999</v>
+        <v>2703.782377099914</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000074021e-08</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>85.77433236462277</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 13.534x + -31008.477</t>
-        </is>
+      <c r="W6" t="n">
+        <v>13.53439579442333</v>
       </c>
       <c r="X6" t="n">
         <v>-31008.47685392185</v>
@@ -4616,7 +4482,7 @@
         <v>176.4817727525122</v>
       </c>
       <c r="Z6" t="n">
-        <v>270.25</v>
+        <v>2746.685211094529</v>
       </c>
       <c r="AA6" t="n">
         <v>1.41996735244995e-08</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>85.68211348543718</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.244x + -29947.165</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.24427378930981</v>
       </c>
       <c r="X7" t="n">
         <v>-29947.1649625958</v>
@@ -4668,7 +4532,7 @@
         <v>178.0211361878237</v>
       </c>
       <c r="Z7" t="n">
-        <v>273.4000000000001</v>
+        <v>2726.024493861719</v>
       </c>
       <c r="AA7" t="n">
         <v>1.458498066863573e-08</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>85.4484269107667</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 12.562x + -27979.733</t>
-        </is>
+      <c r="W8" t="n">
+        <v>12.56163574566255</v>
       </c>
       <c r="X8" t="n">
         <v>-27979.73269080841</v>
@@ -4720,7 +4582,7 @@
         <v>2.779085770779615e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>275.5500000000002</v>
+        <v>2608.177857410929</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000017e-08</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>85.60896831082496</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 13.023x + -28766.318</t>
-        </is>
+      <c r="W9" t="n">
+        <v>13.02280793584823</v>
       </c>
       <c r="X9" t="n">
         <v>-28766.31773061886</v>
@@ -4772,7 +4632,7 @@
         <v>3.655100104717447e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>266.98</v>
+        <v>2578.616719393352</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000029e-08</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>85.65303013752521</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 13.155x + -28756.075</t>
-        </is>
+      <c r="W10" t="n">
+        <v>13.15532561448664</v>
       </c>
       <c r="X10" t="n">
         <v>-28756.07535024081</v>
@@ -4824,7 +4682,7 @@
         <v>3.091953517026953e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>261.2799999999997</v>
+        <v>2550.114354591583</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000534e-08</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>85.536689265056</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 12.811x + -27684.937</t>
-        </is>
+      <c r="W11" t="n">
+        <v>12.81108116479109</v>
       </c>
       <c r="X11" t="n">
         <v>-27684.93709289018</v>
@@ -4876,7 +4732,7 @@
         <v>6.62909506396634e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>256.46</v>
+        <v>2522.540919444169</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>85.64876452444132</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 13.142x + -28123.710</t>
-        </is>
+      <c r="W12" t="n">
+        <v>13.14237950920491</v>
       </c>
       <c r="X12" t="n">
         <v>-28123.70963899793</v>
@@ -4928,7 +4782,7 @@
         <v>1.987472430098682e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>255.0700000000002</v>
+        <v>2493.047171116554</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>85.52395524815631</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 12.774x + -26980.150</t>
-        </is>
+      <c r="W13" t="n">
+        <v>12.77448650817274</v>
       </c>
       <c r="X13" t="n">
         <v>-26980.1496763315</v>
@@ -4980,7 +4832,7 @@
         <v>2.393343331997727e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>251.73</v>
+        <v>2463.337570982736</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000125e-08</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>85.43447767524192</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 12.523x + -26126.307</t>
-        </is>
+      <c r="W14" t="n">
+        <v>12.52309344730977</v>
       </c>
       <c r="X14" t="n">
         <v>-26126.30703645421</v>
@@ -5032,7 +4882,7 @@
         <v>1.434777164258078e-11</v>
       </c>
       <c r="Z14" t="n">
-        <v>246.9300000000003</v>
+        <v>2434.584296388062</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>85.55302254198135</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 12.858x + -26558.870</t>
-        </is>
+      <c r="W15" t="n">
+        <v>12.85832545716506</v>
       </c>
       <c r="X15" t="n">
         <v>-26558.86995910022</v>
@@ -5084,7 +4932,7 @@
         <v>9.684336146384152e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>242.5900000000001</v>
+        <v>2405.335203949656</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000027e-08</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>85.63416318064937</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 13.098x + -26767.354</t>
-        </is>
+      <c r="W16" t="n">
+        <v>13.09825567409449</v>
       </c>
       <c r="X16" t="n">
         <v>-26767.35432003055</v>
@@ -5136,7 +4982,7 @@
         <v>5.807164635943636e-12</v>
       </c>
       <c r="Z16" t="n">
-        <v>236.6799999999998</v>
+        <v>2377.324128530602</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>85.45889795763823</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 12.591x + -25383.439</t>
-        </is>
+      <c r="W17" t="n">
+        <v>12.59072292520358</v>
       </c>
       <c r="X17" t="n">
         <v>-25383.43886330936</v>
@@ -5188,7 +5032,7 @@
         <v>5.054322738713438e-12</v>
       </c>
       <c r="Z17" t="n">
-        <v>234.2599999999998</v>
+        <v>2348.931582503353</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000006e-08</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>85.35343439223158</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 12.304x + -24497.487</t>
-        </is>
+      <c r="W18" t="n">
+        <v>12.30373578560168</v>
       </c>
       <c r="X18" t="n">
         <v>-24497.48739716551</v>
@@ -5240,7 +5082,7 @@
         <v>2.866706578933825e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>231.8199999999997</v>
+        <v>2320.472602728526</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000008e-08</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>85.22137184686588</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 11.962x + -23498.407</t>
-        </is>
+      <c r="W19" t="n">
+        <v>11.96219201794371</v>
       </c>
       <c r="X19" t="n">
         <v>-23498.40669568294</v>
@@ -5292,7 +5132,7 @@
         <v>1.70225681349418e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>234.7899999999997</v>
+        <v>2293.723643250007</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000010132e-08</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>84.98757251495587</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 11.402x + -22083.133</t>
-        </is>
+      <c r="W20" t="n">
+        <v>11.40156880999661</v>
       </c>
       <c r="X20" t="n">
         <v>-22083.13348589925</v>
@@ -5344,7 +5182,7 @@
         <v>1.210396138398304e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>231.74</v>
+        <v>2265.475399808963</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000019e-08</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>85.29593044656765</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 12.153x + -23353.097</t>
-        </is>
+      <c r="W21" t="n">
+        <v>12.15266566885281</v>
       </c>
       <c r="X21" t="n">
         <v>-23353.09673975293</v>
@@ -5396,7 +5232,7 @@
         <v>3.33699942704002e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>221.1400000000001</v>
+        <v>2237.606985131801</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000001356e-08</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>85.23316132345582</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 11.992x + -22753.885</t>
-        </is>
+      <c r="W22" t="n">
+        <v>11.99191471404188</v>
       </c>
       <c r="X22" t="n">
         <v>-22753.88532271128</v>
@@ -5448,7 +5282,7 @@
         <v>7.239735727126652e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>217.6900000000001</v>
+        <v>2209.97942875963</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000001243e-08</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>83.5391984418617</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.831x + -22565.897</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.830596023209797</v>
       </c>
       <c r="X2" t="n">
         <v>-22565.89730244199</v>
@@ -5646,7 +5478,7 @@
         <v>1.669308107439065e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>743.5499999999997</v>
+        <v>2898.531356320102</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000001478e-08</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>85.67727164542526</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.229x + -29408.654</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.22938267682432</v>
       </c>
       <c r="X3" t="n">
         <v>-29408.65401258625</v>
@@ -5698,7 +5528,7 @@
         <v>1.03126867934202e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>408.0100000000002</v>
+        <v>2556.597060659346</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000111e-08</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>85.87851877562265</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.878x + -29583.934</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.87775855706153</v>
       </c>
       <c r="X4" t="n">
         <v>-29583.93365675751</v>
@@ -5750,7 +5578,7 @@
         <v>9.061974822504213e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>342.1700000000001</v>
+        <v>2467.008602312186</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000025e-08</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>85.96601860262649</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.180x + -29678.095</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.17980651531481</v>
       </c>
       <c r="X5" t="n">
         <v>-29678.09452322549</v>
@@ -5802,7 +5628,7 @@
         <v>2.629535078081057e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>315.2600000000002</v>
+        <v>2422.043207017894</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>86.1994198164175</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.053x + -31154.373</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.05341761510953</v>
       </c>
       <c r="X6" t="n">
         <v>-31154.37288865895</v>
@@ -5854,7 +5678,7 @@
         <v>3.990938932229572e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>286.7800000000002</v>
+        <v>2385.792369250469</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000008783e-08</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>85.80287814285442</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.627x + -27596.067</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.62678045159084</v>
       </c>
       <c r="X7" t="n">
         <v>-27596.06716754378</v>
@@ -5906,7 +5728,7 @@
         <v>2.129356743279167e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>298.6299999999999</v>
+        <v>2351.902489905589</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000007e-08</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>86.16959384640222</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 14.936x + -30018.076</t>
-        </is>
+      <c r="W8" t="n">
+        <v>14.93585627042165</v>
       </c>
       <c r="X8" t="n">
         <v>-30018.07600164873</v>
@@ -5958,7 +5778,7 @@
         <v>7.382791105745357e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>278.45</v>
+        <v>2318.745722138486</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000131e-08</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>86.16231172024354</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 14.907x + -29550.904</t>
-        </is>
+      <c r="W9" t="n">
+        <v>14.90743034316741</v>
       </c>
       <c r="X9" t="n">
         <v>-29550.90375437156</v>
@@ -6010,7 +5828,7 @@
         <v>1.719626855767721e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>262.24</v>
+        <v>2286.064416655111</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>85.92732160050741</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 14.045x + -27340.361</t>
-        </is>
+      <c r="W10" t="n">
+        <v>14.04462710262912</v>
       </c>
       <c r="X10" t="n">
         <v>-27340.36124166657</v>
@@ -6062,7 +5878,7 @@
         <v>3.08760428912035e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>267.0100000000002</v>
+        <v>2254.315818047912</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000032e-08</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>86.17786898249233</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 14.968x + -28871.084</t>
-        </is>
+      <c r="W11" t="n">
+        <v>14.96828971563667</v>
       </c>
       <c r="X11" t="n">
         <v>-28871.0837201775</v>
@@ -6114,7 +5928,7 @@
         <v>1.166191682446323e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>261.51</v>
+        <v>2224.310126700585</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000001448e-08</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>85.22988672510775</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.984x + -30621.827</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.9836443529929</v>
       </c>
       <c r="X2" t="n">
         <v>-30621.82678766628</v>
@@ -6312,7 +6124,7 @@
         <v>4.297076168366234e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>455.4699999999998</v>
+        <v>2968.891507117198</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000048e-08</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>85.89089795448947</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.920x + -34279.093</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.91971137817118</v>
       </c>
       <c r="X3" t="n">
         <v>-34279.09277141315</v>
@@ -6364,7 +6174,7 @@
         <v>3.568459738348793e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>348.3999999999996</v>
+        <v>2861.859134141609</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000018728e-08</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>85.98638690921051</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.252x + -34513.326</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.25200403193947</v>
       </c>
       <c r="X4" t="n">
         <v>-34513.32611334425</v>
@@ -6416,7 +6224,7 @@
         <v>7.875781802845816e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>318.6399999999999</v>
+        <v>2814.340182505431</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000001e-08</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>85.80482185543558</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.633x + -32476.831</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.63311665764747</v>
       </c>
       <c r="X5" t="n">
         <v>-32476.83126192831</v>
@@ -6468,7 +6274,7 @@
         <v>1.447210733315941e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>311.6900000000001</v>
+        <v>2777.40156528471</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000003147e-08</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>85.81830792661792</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 13.677x + -32186.552</t>
-        </is>
+      <c r="W6" t="n">
+        <v>13.67724111399948</v>
       </c>
       <c r="X6" t="n">
         <v>-32186.55168588873</v>
@@ -6520,7 +6324,7 @@
         <v>2.433992573529441e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>289.3399999999997</v>
+        <v>2743.957567616646</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000005e-08</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>85.87163150708022</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.855x + -32270.020</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.85452646480459</v>
       </c>
       <c r="X7" t="n">
         <v>-32270.01974311587</v>
@@ -6572,7 +6374,7 @@
         <v>9.579990235952119e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>285.75</v>
+        <v>2713.596310572661</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000156968e-08</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>85.73117651278226</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 13.397x + -30808.799</t>
-        </is>
+      <c r="W8" t="n">
+        <v>13.3970692776507</v>
       </c>
       <c r="X8" t="n">
         <v>-30808.79912314165</v>
@@ -6624,7 +6424,7 @@
         <v>1.218697654527602e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>288.29</v>
+        <v>2685.741271748901</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000116112e-08</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>85.73842902141354</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 13.420x + -30546.624</t>
-        </is>
+      <c r="W9" t="n">
+        <v>13.41995345661399</v>
       </c>
       <c r="X9" t="n">
         <v>-30546.62388083949</v>
@@ -6676,7 +6474,7 @@
         <v>1.479441224105351e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>278.8700000000003</v>
+        <v>2658.180877920011</v>
       </c>
       <c r="AA9" t="n">
         <v>1.00000000000071e-08</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>85.55946921631539</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 12.877x + -28941.911</t>
-        </is>
+      <c r="W10" t="n">
+        <v>12.8770680436661</v>
       </c>
       <c r="X10" t="n">
         <v>-28941.91113499524</v>
@@ -6728,7 +6524,7 @@
         <v>1.380012355386828e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>280.8099999999999</v>
+        <v>2631.183480824692</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000012889e-08</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>85.80128589062012</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 13.622x + -30427.587</t>
-        </is>
+      <c r="W11" t="n">
+        <v>13.62159431595203</v>
       </c>
       <c r="X11" t="n">
         <v>-30427.58664542211</v>
@@ -6780,7 +6574,7 @@
         <v>9.303005940359943e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>270.3899999999999</v>
+        <v>2603.979594122613</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000039895e-08</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>85.69226677238517</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 13.276x + -29298.806</t>
-        </is>
+      <c r="W12" t="n">
+        <v>13.27560878633282</v>
       </c>
       <c r="X12" t="n">
         <v>-29298.80621146221</v>
@@ -6832,7 +6624,7 @@
         <v>9.344160738297588e-12</v>
       </c>
       <c r="Z12" t="n">
-        <v>273.3499999999999</v>
+        <v>2577.717880925443</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000002961e-08</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>85.70841168783397</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 13.326x + -29107.365</t>
-        </is>
+      <c r="W13" t="n">
+        <v>13.3257398529347</v>
       </c>
       <c r="X13" t="n">
         <v>-29107.36544144287</v>
@@ -6884,7 +6674,7 @@
         <v>1.60985710614627e-18</v>
       </c>
       <c r="Z13" t="n">
-        <v>270.9000000000001</v>
+        <v>2550.833724812115</v>
       </c>
       <c r="AA13" t="n">
         <v>1e-08</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>85.85919159752454</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 13.813x + -29948.805</t>
-        </is>
+      <c r="W14" t="n">
+        <v>13.81275975747213</v>
       </c>
       <c r="X14" t="n">
         <v>-29948.80514446605</v>
@@ -6936,7 +6724,7 @@
         <v>2.883939939052494e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>259.1499999999996</v>
+        <v>2523.973641391239</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000010549e-08</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>85.99574808611756</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 14.285x + -30744.115</t>
-        </is>
+      <c r="W15" t="n">
+        <v>14.28543161867493</v>
       </c>
       <c r="X15" t="n">
         <v>-30744.11453532423</v>
@@ -6988,7 +6774,7 @@
         <v>1.502981915748685e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>251.8599999999997</v>
+        <v>2497.596764095284</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000210954e-08</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>86.03822384549272</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 14.439x + -30783.166</t>
-        </is>
+      <c r="W16" t="n">
+        <v>14.43908854381331</v>
       </c>
       <c r="X16" t="n">
         <v>-30783.16612355501</v>
@@ -7040,7 +6824,7 @@
         <v>9.583345736296063e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>249.02</v>
+        <v>2472.138018937787</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000263e-08</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>85.66248540855653</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 13.184x + -27650.595</t>
-        </is>
+      <c r="W17" t="n">
+        <v>13.1841128965781</v>
       </c>
       <c r="X17" t="n">
         <v>-27650.59457274326</v>
@@ -7092,7 +6874,7 @@
         <v>8.076491277200882e-10</v>
       </c>
       <c r="Z17" t="n">
-        <v>260.0900000000001</v>
+        <v>2446.151413445513</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000042e-08</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>85.81927658141153</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 13.680x + -28482.025</t>
-        </is>
+      <c r="W18" t="n">
+        <v>13.68042134931388</v>
       </c>
       <c r="X18" t="n">
         <v>-28482.02510896072</v>
@@ -7144,7 +6924,7 @@
         <v>1.786965320502517e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>248.8600000000001</v>
+        <v>2420.467735693825</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000001139e-08</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>85.77189410797133</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 13.527x + -27841.277</t>
-        </is>
+      <c r="W19" t="n">
+        <v>13.52656242009697</v>
       </c>
       <c r="X19" t="n">
         <v>-27841.27747218926</v>
@@ -7196,7 +6974,7 @@
         <v>2.728071149661126e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>253.1699999999998</v>
+        <v>2395.345596222047</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000271e-08</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>86.04079009269893</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 14.448x + -29578.208</t>
-        </is>
+      <c r="W20" t="n">
+        <v>14.44847743851758</v>
       </c>
       <c r="X20" t="n">
         <v>-29578.20759198589</v>
@@ -7248,7 +7024,7 @@
         <v>1.151201381785353e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>238.3699999999999</v>
+        <v>2369.931667734592</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000026403e-08</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>85.61859359939417</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 13.052x + -26252.448</t>
-        </is>
+      <c r="W21" t="n">
+        <v>13.05152928534863</v>
       </c>
       <c r="X21" t="n">
         <v>-26252.44812079285</v>
@@ -7300,7 +7074,7 @@
         <v>90.94930141049421</v>
       </c>
       <c r="Z21" t="n">
-        <v>250.77</v>
+        <v>2331.396859334923</v>
       </c>
       <c r="AA21" t="n">
         <v>1.277275645378917e-08</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>85.96295309951256</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 14.169x + -28367.557</t>
-        </is>
+      <c r="W22" t="n">
+        <v>14.16900350035914</v>
       </c>
       <c r="X22" t="n">
         <v>-28367.55741277962</v>
@@ -7352,7 +7124,7 @@
         <v>1.338455413330206e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>235.6599999999999</v>
+        <v>2319.952965833445</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000194e-08</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>83.59616956072668</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.910x + -21553.656</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.909823609083137</v>
       </c>
       <c r="X2" t="n">
         <v>-21553.65571513454</v>
@@ -7550,7 +7320,7 @@
         <v>1.039085601399273e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>710.71</v>
+        <v>2726.946789323578</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000027e-08</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>85.60455708824557</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.010x + -27564.707</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.00968703455139</v>
       </c>
       <c r="X3" t="n">
         <v>-27564.70733631978</v>
@@ -7602,7 +7370,7 @@
         <v>1.810395849991254e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>401.48</v>
+        <v>2434.128637667324</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>86.13770616101534</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.812x + -30393.900</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.81217384871999</v>
       </c>
       <c r="X4" t="n">
         <v>-30393.90042377313</v>
@@ -7654,7 +7420,7 @@
         <v>9.372927700212982e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>327.4599999999998</v>
+        <v>2356.440625562518</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000119e-08</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>86.27934440394502</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.378x + -31037.190</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.37772536549441</v>
       </c>
       <c r="X5" t="n">
         <v>-31037.18969553097</v>
@@ -7706,7 +7470,7 @@
         <v>1.55874122150104e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>303.99</v>
+        <v>2317.316779300467</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000024045e-08</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>86.05706977543211</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.508x + -28738.032</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.5083226583154</v>
       </c>
       <c r="X6" t="n">
         <v>-28738.03201182807</v>
@@ -7758,7 +7520,7 @@
         <v>1.165904168561833e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>293.5</v>
+        <v>2286.119522464697</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000247e-08</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>86.12476278051119</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 14.763x + -28895.870</t>
-        </is>
+      <c r="W7" t="n">
+        <v>14.7625504079541</v>
       </c>
       <c r="X7" t="n">
         <v>-28895.87027455024</v>
@@ -7810,7 +7570,7 @@
         <v>2.74042746161858e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>278.8600000000001</v>
+        <v>2256.056384785873</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000002347e-08</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>86.31408704074593</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 15.523x + -30076.593</t>
-        </is>
+      <c r="W8" t="n">
+        <v>15.52307893630385</v>
       </c>
       <c r="X8" t="n">
         <v>-30076.5926785157</v>
@@ -7862,7 +7620,7 @@
         <v>9.72685249777086e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>262.6400000000001</v>
+        <v>2225.900919931732</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>86.21687968130527</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 15.123x + -28852.461</t>
-        </is>
+      <c r="W9" t="n">
+        <v>15.12309592243104</v>
       </c>
       <c r="X9" t="n">
         <v>-28852.46110564734</v>
@@ -7914,7 +7670,7 @@
         <v>1.536564702534079e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>256.4499999999998</v>
+        <v>2196.0039154832</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000428e-08</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>86.27033952714685</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 15.340x + -28908.513</t>
-        </is>
+      <c r="W10" t="n">
+        <v>15.34049274003198</v>
       </c>
       <c r="X10" t="n">
         <v>-28908.51322135519</v>
@@ -7966,7 +7720,7 @@
         <v>1.760263210525344e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>245.7700000000002</v>
+        <v>2167.425630607172</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000014e-08</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>86.34295633619254</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 15.646x + -29159.128</t>
-        </is>
+      <c r="W11" t="n">
+        <v>15.64595805765012</v>
       </c>
       <c r="X11" t="n">
         <v>-29159.12776337244</v>
@@ -8018,7 +7770,7 @@
         <v>2.14325529618481e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>249.0799999999999</v>
+        <v>2139.909577629029</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000067e-08</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>85.75811165242861</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 13.482x + -33774.863</t>
-        </is>
+      <c r="W2" t="n">
+        <v>13.48245260975388</v>
       </c>
       <c r="X2" t="n">
         <v>-33774.86298556774</v>
@@ -8216,7 +7966,7 @@
         <v>7.846913323843916e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>395.9899999999998</v>
+        <v>2877.138759700751</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000052073e-08</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>85.96653098710421</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.182x + -33888.873</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.18161378770432</v>
       </c>
       <c r="X3" t="n">
         <v>-33888.87326767434</v>
@@ -8268,7 +8016,7 @@
         <v>5.405528003712421e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>312.2599999999998</v>
+        <v>2768.959440272427</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000016458e-08</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>86.05187263551271</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.489x + -34009.825</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.48916407533497</v>
       </c>
       <c r="X4" t="n">
         <v>-34009.82532537974</v>
@@ -8320,7 +8066,7 @@
         <v>7.964427138879586e-12</v>
       </c>
       <c r="Z4" t="n">
-        <v>289.2800000000002</v>
+        <v>2720.638480053613</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001424e-08</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>86.1169377044325</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.733x + -34167.617</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.73271017374215</v>
       </c>
       <c r="X5" t="n">
         <v>-34167.61706204643</v>
@@ -8372,7 +8116,7 @@
         <v>4.281344064035811e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>272.3499999999999</v>
+        <v>2687.522056680972</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000001e-08</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>85.95980606102954</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.158x + -32371.818</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.15793017516788</v>
       </c>
       <c r="X6" t="n">
         <v>-32371.817969048</v>
@@ -8424,7 +8166,7 @@
         <v>2.77543492875132e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>266.0999999999999</v>
+        <v>2657.029005892974</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001452e-08</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>85.96482790941235</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 14.176x + -32071.228</t>
-        </is>
+      <c r="W7" t="n">
+        <v>14.17560849540062</v>
       </c>
       <c r="X7" t="n">
         <v>-32071.22779888786</v>
@@ -8476,7 +8216,7 @@
         <v>178.7874322610375</v>
       </c>
       <c r="Z7" t="n">
-        <v>258.7199999999998</v>
+        <v>2685.114667925638</v>
       </c>
       <c r="AA7" t="n">
         <v>1.393666145335805e-08</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>85.97733059189549</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 14.220x + -31831.516</t>
-        </is>
+      <c r="W8" t="n">
+        <v>14.21981288039699</v>
       </c>
       <c r="X8" t="n">
         <v>-31831.51642262445</v>
@@ -8528,7 +8266,7 @@
         <v>180.7099134671621</v>
       </c>
       <c r="Z8" t="n">
-        <v>254.9499999999998</v>
+        <v>2664.709232403846</v>
       </c>
       <c r="AA8" t="n">
         <v>1.423279139325497e-08</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>86.02870966900606</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 14.404x + -31951.224</t>
-        </is>
+      <c r="W9" t="n">
+        <v>14.40438561075018</v>
       </c>
       <c r="X9" t="n">
         <v>-31951.22384277095</v>
@@ -8580,7 +8316,7 @@
         <v>181.480830455624</v>
       </c>
       <c r="Z9" t="n">
-        <v>251.4900000000002</v>
+        <v>2646.651785233375</v>
       </c>
       <c r="AA9" t="n">
         <v>1.456808227389621e-08</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>85.87609696665561</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 13.870x + -30365.854</t>
-        </is>
+      <c r="W10" t="n">
+        <v>13.8695804952709</v>
       </c>
       <c r="X10" t="n">
         <v>-30365.85402702303</v>
@@ -8632,7 +8366,7 @@
         <v>174.5742779311235</v>
       </c>
       <c r="Z10" t="n">
-        <v>256.9500000000003</v>
+        <v>2600.622594587256</v>
       </c>
       <c r="AA10" t="n">
         <v>1.390978337262408e-08</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>86.08516463464437</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 14.613x + -31778.105</t>
-        </is>
+      <c r="W11" t="n">
+        <v>14.61277007336968</v>
       </c>
       <c r="X11" t="n">
         <v>-31778.10502104715</v>
@@ -8684,7 +8416,7 @@
         <v>6.872746667149741e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>243.1700000000001</v>
+        <v>2519.116916451603</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000306e-08</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>86.11355201084075</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 14.720x + -31683.217</t>
-        </is>
+      <c r="W12" t="n">
+        <v>14.71983631726206</v>
       </c>
       <c r="X12" t="n">
         <v>-31683.216587006</v>
@@ -8736,7 +8466,7 @@
         <v>4.581051058942064e-12</v>
       </c>
       <c r="Z12" t="n">
-        <v>241.3200000000002</v>
+        <v>2491.604678133055</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>86.08020508541409</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 14.594x + -31062.926</t>
-        </is>
+      <c r="W13" t="n">
+        <v>14.59422345255162</v>
       </c>
       <c r="X13" t="n">
         <v>-31062.92627946116</v>
@@ -8788,7 +8516,7 @@
         <v>6.067583795970227e-12</v>
       </c>
       <c r="Z13" t="n">
-        <v>240.0899999999997</v>
+        <v>2464.038823681705</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000001e-08</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>85.74036323023644</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 13.426x + -28115.634</t>
-        </is>
+      <c r="W14" t="n">
+        <v>13.42606969415648</v>
       </c>
       <c r="X14" t="n">
         <v>-28115.63359985818</v>
@@ -8840,7 +8566,7 @@
         <v>5.667103645306754e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>246.6600000000003</v>
+        <v>2437.282706316727</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000007e-08</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>85.76039479724962</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 13.490x + -27958.581</t>
-        </is>
+      <c r="W15" t="n">
+        <v>13.48973987606593</v>
       </c>
       <c r="X15" t="n">
         <v>-27958.58111479407</v>
@@ -8892,7 +8616,7 @@
         <v>2.156250906290475e-12</v>
       </c>
       <c r="Z15" t="n">
-        <v>246.6500000000001</v>
+        <v>2410.525587010599</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>86.1750776523389</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 14.957x + -30875.338</t>
-        </is>
+      <c r="W16" t="n">
+        <v>14.95733375595929</v>
       </c>
       <c r="X16" t="n">
         <v>-30875.33796739028</v>
@@ -8944,7 +8666,7 @@
         <v>8.470728801220286e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>230.3899999999999</v>
+        <v>2384.055225509795</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000001024e-08</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>85.91530846486062</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 14.003x + -28487.343</t>
-        </is>
+      <c r="W17" t="n">
+        <v>14.00318198743088</v>
       </c>
       <c r="X17" t="n">
         <v>-28487.34318003853</v>
@@ -8996,7 +8716,7 @@
         <v>1.230705697416968e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>233.6099999999999</v>
+        <v>2357.918282023292</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000016e-08</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>85.99763930489898</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 14.292x + -28816.333</t>
-        </is>
+      <c r="W18" t="n">
+        <v>14.29220387887353</v>
       </c>
       <c r="X18" t="n">
         <v>-28816.33325317343</v>
@@ -9048,7 +8766,7 @@
         <v>6.194129678660083e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>223.9300000000001</v>
+        <v>2331.314977939496</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>85.9876950211288</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 14.257x + -28409.744</t>
-        </is>
+      <c r="W19" t="n">
+        <v>14.25666577523855</v>
       </c>
       <c r="X19" t="n">
         <v>-28409.74441714353</v>
@@ -9100,7 +8816,7 @@
         <v>1.19045633652048e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>227.05</v>
+        <v>2306.018635037247</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>85.92609497672279</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 14.040x + -27664.711</t>
-        </is>
+      <c r="W20" t="n">
+        <v>14.04038408555592</v>
       </c>
       <c r="X20" t="n">
         <v>-27664.71148502776</v>
@@ -9152,7 +8866,7 @@
         <v>5.042093175659922e-11</v>
       </c>
       <c r="Z20" t="n">
-        <v>222.6499999999999</v>
+        <v>2280.661471813982</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000146e-08</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>85.96545586314856</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 14.178x + -27659.801</t>
-        </is>
+      <c r="W21" t="n">
+        <v>14.17782215982208</v>
       </c>
       <c r="X21" t="n">
         <v>-27659.80082951646</v>
@@ -9204,7 +8916,7 @@
         <v>1.610994835102721e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>224.9299999999998</v>
+        <v>2255.78639408294</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000015152e-08</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>85.93625423983973</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 14.076x + -27152.256</t>
-        </is>
+      <c r="W22" t="n">
+        <v>14.07560313162577</v>
       </c>
       <c r="X22" t="n">
         <v>-27152.2559054583</v>
@@ -9256,7 +8966,7 @@
         <v>1.641316762978337e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>216.4099999999999</v>
+        <v>2230.140017103029</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000507e-08</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>83.64983059297444</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.986x + -16149.241</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.985742616147581</v>
       </c>
       <c r="X2" t="n">
         <v>-16149.2406227118</v>
@@ -9454,7 +9162,7 @@
         <v>2.18963506839997e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>672.26</v>
+        <v>2000.054434608405</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000051e-08</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>86.27031403448062</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 15.340x + -24860.582</t>
-        </is>
+      <c r="W3" t="n">
+        <v>15.34038758989648</v>
       </c>
       <c r="X3" t="n">
         <v>-24860.58184285437</v>
@@ -9506,7 +9212,7 @@
         <v>6.899639652387902e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>320.5600000000002</v>
+        <v>1828.839227429705</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000072e-08</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>86.44820967343497</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.111x + -25272.296</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.1108520209959</v>
       </c>
       <c r="X4" t="n">
         <v>-25272.2961287095</v>
@@ -9558,7 +9262,7 @@
         <v>3.295643239239275e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>262.3300000000002</v>
+        <v>1778.897592392325</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000046e-08</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>86.65293236683763</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 17.099x + -26428.632</t>
-        </is>
+      <c r="W5" t="n">
+        <v>17.09872501700414</v>
       </c>
       <c r="X5" t="n">
         <v>-26428.63204935795</v>
@@ -9610,7 +9312,7 @@
         <v>7.339943731119014e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>241.1200000000001</v>
+        <v>1748.353368977718</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000076e-08</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>86.61506210747608</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.907x + -25695.896</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.90698825500108</v>
       </c>
       <c r="X6" t="n">
         <v>-25695.89624876585</v>
@@ -9662,7 +9362,7 @@
         <v>1.06089984688109e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>233.0799999999999</v>
+        <v>1720.612338470688</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000351e-08</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>86.74794040825911</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 17.599x + -26403.058</t>
-        </is>
+      <c r="W7" t="n">
+        <v>17.59938175690651</v>
       </c>
       <c r="X7" t="n">
         <v>-26403.05827183233</v>
@@ -9714,7 +9412,7 @@
         <v>1.37158877233294e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>217.29</v>
+        <v>1693.155492008821</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000022e-08</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>86.73482270002181</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 17.529x + -25876.916</t>
-        </is>
+      <c r="W8" t="n">
+        <v>17.52852461314235</v>
       </c>
       <c r="X8" t="n">
         <v>-25876.91593827373</v>
@@ -9766,7 +9462,7 @@
         <v>6.830612224195562e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>217.1500000000001</v>
+        <v>1666.728511405334</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000001403e-08</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>86.7597429707979</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.664x + -25678.132</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.66362474277963</v>
       </c>
       <c r="X9" t="n">
         <v>-25678.13215329937</v>
@@ -9818,7 +9512,7 @@
         <v>8.284306897986913e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>205.1599999999999</v>
+        <v>1640.36726593241</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>87.02495968943157</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 19.242x + -27710.362</t>
-        </is>
+      <c r="W10" t="n">
+        <v>19.24151340323605</v>
       </c>
       <c r="X10" t="n">
         <v>-27710.36230917755</v>
@@ -9870,7 +9562,7 @@
         <v>140.6764401548427</v>
       </c>
       <c r="Z10" t="n">
-        <v>192.73</v>
+        <v>1567.082173047818</v>
       </c>
       <c r="AA10" t="n">
         <v>1.280368087482346e-08</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>86.77386829314423</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 17.741x + -25053.076</t>
-        </is>
+      <c r="W11" t="n">
+        <v>17.7411280920849</v>
       </c>
       <c r="X11" t="n">
         <v>-25053.07583818535</v>
@@ -9922,7 +9612,7 @@
         <v>1.253218068662767e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>196.6299999999999</v>
+        <v>1593.111746086915</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000105e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-501.1500000000001</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-373.1700000000001</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-347.73</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-332.6300000000001</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-316.79</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-289.71</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-284.0700000000002</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-265.8799999999997</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-259.8499999999999</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-258.9400000000001</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-721.3899999999999</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-441.8000000000002</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-350.3499999999999</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-332.4400000000001</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-304.1600000000001</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-284.8799999999999</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-278.1100000000001</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-266.3200000000002</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-261.2200000000003</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-246.4200000000001</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-743.5499999999997</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-408.0100000000002</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-342.1700000000001</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-315.2600000000002</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-286.7800000000002</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-298.6299999999999</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-278.45</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-262.24</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-267.0100000000002</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-261.51</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-710.71</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-401.48</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-327.4599999999998</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-303.99</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-293.5</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-278.8600000000001</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-262.6400000000001</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-256.4499999999998</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-245.7700000000002</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-249.0799999999999</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-672.26</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-320.5600000000002</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-262.3300000000002</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-241.1200000000001</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-233.0799999999999</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-217.29</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-217.1500000000001</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-205.1599999999999</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-192.73</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-196.6299999999999</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-501.1500000000001</v>
+        <v>2319.272</v>
       </c>
       <c r="D2" t="n">
         <v>1.79726e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-373.1700000000001</v>
+        <v>2218.411</v>
       </c>
       <c r="D3" t="n">
         <v>1.79278e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-347.73</v>
+        <v>2150.1</v>
       </c>
       <c r="D4" t="n">
         <v>1.79373e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-332.6300000000001</v>
+        <v>2094.711</v>
       </c>
       <c r="D5" t="n">
         <v>1.79765e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-316.79</v>
+        <v>2051.908</v>
       </c>
       <c r="D6" t="n">
         <v>1.80066e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-289.71</v>
+        <v>2025.09</v>
       </c>
       <c r="D7" t="n">
         <v>1.8041e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-284.0700000000002</v>
+        <v>1982.399</v>
       </c>
       <c r="D8" t="n">
         <v>1.80841e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-265.8799999999997</v>
+        <v>1952.526</v>
       </c>
       <c r="D9" t="n">
         <v>1.81234e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-259.8499999999999</v>
+        <v>1920.287</v>
       </c>
       <c r="D10" t="n">
         <v>1.81622e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-258.9400000000001</v>
+        <v>1877.408</v>
       </c>
       <c r="D11" t="n">
         <v>1.82048e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-308.6999999999998</v>
+        <v>2049.569</v>
       </c>
       <c r="D2" t="n">
         <v>1.89568e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-281.5499999999997</v>
+        <v>1921.625</v>
       </c>
       <c r="D3" t="n">
         <v>1.92475e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-254.0499999999997</v>
+        <v>1896.133</v>
       </c>
       <c r="D4" t="n">
         <v>1.93395e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-252.1699999999996</v>
+        <v>1858.729</v>
       </c>
       <c r="D5" t="n">
         <v>1.94005e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-249.8099999999999</v>
+        <v>1829.222</v>
       </c>
       <c r="D6" t="n">
         <v>1.94399e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-242.8299999999999</v>
+        <v>1799.899</v>
       </c>
       <c r="D7" t="n">
         <v>1.95007e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-222.6300000000001</v>
+        <v>1778.92</v>
       </c>
       <c r="D8" t="n">
         <v>1.95551e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-219.1199999999999</v>
+        <v>1747.645</v>
       </c>
       <c r="D9" t="n">
         <v>1.96055e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-226.2200000000003</v>
+        <v>1715.609</v>
       </c>
       <c r="D10" t="n">
         <v>1.96625e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-211.1599999999999</v>
+        <v>1700.874</v>
       </c>
       <c r="D11" t="n">
         <v>1.9695e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-199.98</v>
+        <v>1684.541</v>
       </c>
       <c r="D12" t="n">
         <v>1.97248e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-194.4099999999999</v>
+        <v>1664.2</v>
       </c>
       <c r="D13" t="n">
         <v>1.9763e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-186.3300000000002</v>
+        <v>1637.12</v>
       </c>
       <c r="D14" t="n">
         <v>1.98164e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-184.4400000000001</v>
+        <v>1614.806</v>
       </c>
       <c r="D15" t="n">
         <v>1.9857e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-177.2199999999998</v>
+        <v>1590.964</v>
       </c>
       <c r="D16" t="n">
         <v>1.98769e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-166.29</v>
+        <v>1575.338</v>
       </c>
       <c r="D17" t="n">
         <v>1.99302e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-177.0999999999999</v>
+        <v>1542.203</v>
       </c>
       <c r="D18" t="n">
         <v>1.99637e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-156.3399999999999</v>
+        <v>1538.817</v>
       </c>
       <c r="D19" t="n">
         <v>1.99729e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-158.1799999999998</v>
+        <v>1514.049</v>
       </c>
       <c r="D20" t="n">
         <v>2.00154e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-151.3799999999999</v>
+        <v>1496.498</v>
       </c>
       <c r="D21" t="n">
         <v>2.00368e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-126.6000000000001</v>
+        <v>1488.396</v>
       </c>
       <c r="D22" t="n">
         <v>2.00741e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-389.6800000000003</v>
+        <v>2296.259</v>
       </c>
       <c r="D2" t="n">
         <v>1.76371e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-315.9400000000001</v>
+        <v>2135.695</v>
       </c>
       <c r="D3" t="n">
         <v>1.78267e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-284.25</v>
+        <v>2095.379</v>
       </c>
       <c r="D4" t="n">
         <v>1.78277e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-268.6699999999996</v>
+        <v>2056.981</v>
       </c>
       <c r="D5" t="n">
         <v>1.78542e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-266.9300000000003</v>
+        <v>2028.168</v>
       </c>
       <c r="D6" t="n">
         <v>1.78356e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-243.8700000000003</v>
+        <v>1997.313</v>
       </c>
       <c r="D7" t="n">
         <v>1.78514e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-238.23</v>
+        <v>1970.152</v>
       </c>
       <c r="D8" t="n">
         <v>1.78715e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-244.6199999999999</v>
+        <v>1933.798</v>
       </c>
       <c r="D9" t="n">
         <v>1.78614e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-227.29</v>
+        <v>1916.056</v>
       </c>
       <c r="D10" t="n">
         <v>1.78607e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-229.8899999999999</v>
+        <v>1882.6</v>
       </c>
       <c r="D11" t="n">
         <v>1.78627e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-215.98</v>
+        <v>1863.725</v>
       </c>
       <c r="D12" t="n">
         <v>1.78455e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-207.9699999999998</v>
+        <v>1834.568</v>
       </c>
       <c r="D13" t="n">
         <v>1.78432e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-216.5499999999997</v>
+        <v>1806.722</v>
       </c>
       <c r="D14" t="n">
         <v>1.78076e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-211.6900000000001</v>
+        <v>1782.123</v>
       </c>
       <c r="D15" t="n">
         <v>1.77901e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-192.2400000000002</v>
+        <v>1766.725</v>
       </c>
       <c r="D16" t="n">
         <v>1.77859e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-186.0599999999999</v>
+        <v>1739.261</v>
       </c>
       <c r="D17" t="n">
         <v>1.77748e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-189.5700000000002</v>
+        <v>1719.156</v>
       </c>
       <c r="D18" t="n">
         <v>1.77596e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-174.3699999999999</v>
+        <v>1697.681</v>
       </c>
       <c r="D19" t="n">
         <v>1.77453e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-164.8799999999997</v>
+        <v>1683.348</v>
       </c>
       <c r="D20" t="n">
         <v>1.77162e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-163.4100000000003</v>
+        <v>1659.877</v>
       </c>
       <c r="D21" t="n">
         <v>1.77016e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-156.95</v>
+        <v>1635.382</v>
       </c>
       <c r="D22" t="n">
         <v>1.77114e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-721.3899999999999</v>
+        <v>2055.368</v>
       </c>
       <c r="D2" t="n">
         <v>1.79691e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-441.8000000000002</v>
+        <v>1749.25</v>
       </c>
       <c r="D3" t="n">
         <v>1.86279e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-350.3499999999999</v>
+        <v>1674.421</v>
       </c>
       <c r="D4" t="n">
         <v>1.8711e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-332.4400000000001</v>
+        <v>1620.014</v>
       </c>
       <c r="D5" t="n">
         <v>1.8701e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-304.1600000000001</v>
+        <v>1592.746</v>
       </c>
       <c r="D6" t="n">
         <v>1.87345e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-284.8799999999999</v>
+        <v>1560.177</v>
       </c>
       <c r="D7" t="n">
         <v>1.87595e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-278.1100000000001</v>
+        <v>1527.535</v>
       </c>
       <c r="D8" t="n">
         <v>1.87763e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-266.3200000000002</v>
+        <v>1503.321</v>
       </c>
       <c r="D9" t="n">
         <v>1.87885e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-261.2200000000003</v>
+        <v>1479.373</v>
       </c>
       <c r="D10" t="n">
         <v>1.88043e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-246.4200000000001</v>
+        <v>1458.328</v>
       </c>
       <c r="D11" t="n">
         <v>1.88263e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-397.4200000000001</v>
+        <v>2109.609</v>
       </c>
       <c r="D2" t="n">
         <v>1.80582e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-310.4899999999998</v>
+        <v>2004.165</v>
       </c>
       <c r="D3" t="n">
         <v>1.82804e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-281.9099999999999</v>
+        <v>1954.573</v>
       </c>
       <c r="D4" t="n">
         <v>1.83893e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-252.54</v>
+        <v>1932.932</v>
       </c>
       <c r="D5" t="n">
         <v>1.8475e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-248.75</v>
+        <v>1894.38</v>
       </c>
       <c r="D6" t="n">
         <v>1.85466e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-255.7900000000004</v>
+        <v>1862.599</v>
       </c>
       <c r="D7" t="n">
         <v>1.85812e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-246.9299999999998</v>
+        <v>1829.782</v>
       </c>
       <c r="D8" t="n">
         <v>1.86224e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-230.6799999999998</v>
+        <v>1813.049</v>
       </c>
       <c r="D9" t="n">
         <v>1.86793e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-222.1900000000001</v>
+        <v>1791.775</v>
       </c>
       <c r="D10" t="n">
         <v>1.87002e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-206.27</v>
+        <v>1771.164</v>
       </c>
       <c r="D11" t="n">
         <v>1.87396e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-208.7700000000004</v>
+        <v>1747.663</v>
       </c>
       <c r="D12" t="n">
         <v>1.87648e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-196.6599999999999</v>
+        <v>1724.264</v>
       </c>
       <c r="D13" t="n">
         <v>1.88127e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-184.5</v>
+        <v>1700.635</v>
       </c>
       <c r="D14" t="n">
         <v>1.88564e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-182.6100000000001</v>
+        <v>1679.72</v>
       </c>
       <c r="D15" t="n">
         <v>1.88678e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-180.96</v>
+        <v>1659.648</v>
       </c>
       <c r="D16" t="n">
         <v>1.88925e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-168.0999999999999</v>
+        <v>1637.082</v>
       </c>
       <c r="D17" t="n">
         <v>1.89484e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-159.7199999999998</v>
+        <v>1615.956</v>
       </c>
       <c r="D18" t="n">
         <v>1.89727e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-163.6800000000001</v>
+        <v>1587.141</v>
       </c>
       <c r="D19" t="n">
         <v>1.89987e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-152.0199999999998</v>
+        <v>1565.966</v>
       </c>
       <c r="D20" t="n">
         <v>1.90312e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-145.5199999999998</v>
+        <v>1552.813</v>
       </c>
       <c r="D21" t="n">
         <v>1.9041e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-140.3800000000001</v>
+        <v>1529.684</v>
       </c>
       <c r="D22" t="n">
         <v>1.90786e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-743.5499999999997</v>
+        <v>2145.244</v>
       </c>
       <c r="D2" t="n">
         <v>1.76943e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-408.0100000000002</v>
+        <v>1804.357</v>
       </c>
       <c r="D3" t="n">
         <v>1.84077e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-342.1700000000001</v>
+        <v>1710.582</v>
       </c>
       <c r="D4" t="n">
         <v>1.85184e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-315.2600000000002</v>
+        <v>1671.218</v>
       </c>
       <c r="D5" t="n">
         <v>1.85759e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-286.7800000000002</v>
+        <v>1648.205</v>
       </c>
       <c r="D6" t="n">
         <v>1.85986e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-298.6299999999999</v>
+        <v>1600.842</v>
       </c>
       <c r="D7" t="n">
         <v>1.86409e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-278.45</v>
+        <v>1586.441</v>
       </c>
       <c r="D8" t="n">
         <v>1.86455e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-262.24</v>
+        <v>1557.725</v>
       </c>
       <c r="D9" t="n">
         <v>1.86925e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-267.0100000000002</v>
+        <v>1522.092</v>
       </c>
       <c r="D10" t="n">
         <v>1.87132e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-261.51</v>
+        <v>1502.414</v>
       </c>
       <c r="D11" t="n">
         <v>1.87239e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-455.4699999999998</v>
+        <v>2164.259</v>
       </c>
       <c r="D2" t="n">
         <v>1.79463e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-348.3999999999996</v>
+        <v>2069.956</v>
       </c>
       <c r="D3" t="n">
         <v>1.80846e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-318.6399999999999</v>
+        <v>2029.286</v>
       </c>
       <c r="D4" t="n">
         <v>1.81489e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-311.6900000000001</v>
+        <v>1988.22</v>
       </c>
       <c r="D5" t="n">
         <v>1.82214e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-289.3399999999997</v>
+        <v>1961.517</v>
       </c>
       <c r="D6" t="n">
         <v>1.82776e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-285.75</v>
+        <v>1934.235</v>
       </c>
       <c r="D7" t="n">
         <v>1.83007e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-288.29</v>
+        <v>1902.703</v>
       </c>
       <c r="D8" t="n">
         <v>1.83257e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-272.5500000000002</v>
+        <v>1881.206</v>
       </c>
       <c r="D9" t="n">
         <v>1.83615e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-267.8299999999999</v>
+        <v>1854.214</v>
       </c>
       <c r="D10" t="n">
         <v>1.83892e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-257.5300000000002</v>
+        <v>1841.019</v>
       </c>
       <c r="D11" t="n">
         <v>1.84195e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-262.6900000000001</v>
+        <v>1813.612</v>
       </c>
       <c r="D12" t="n">
         <v>1.84343e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-255.5300000000002</v>
+        <v>1791.995</v>
       </c>
       <c r="D13" t="n">
         <v>1.84847e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-235.0999999999999</v>
+        <v>1779.061</v>
       </c>
       <c r="D14" t="n">
         <v>1.8497e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-219.2999999999997</v>
+        <v>1763.477</v>
       </c>
       <c r="D15" t="n">
         <v>1.85395e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-217.9599999999996</v>
+        <v>1743.803</v>
       </c>
       <c r="D16" t="n">
         <v>1.85489e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-223.75</v>
+        <v>1708.144</v>
       </c>
       <c r="D17" t="n">
         <v>1.85835e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-207.9099999999999</v>
+        <v>1697.884</v>
       </c>
       <c r="D18" t="n">
         <v>1.8599e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-217.26</v>
+        <v>1670.326</v>
       </c>
       <c r="D19" t="n">
         <v>1.8624e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-197.1199999999999</v>
+        <v>1662.175</v>
       </c>
       <c r="D20" t="n">
         <v>1.86512e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-210.8499999999999</v>
+        <v>1626.797</v>
       </c>
       <c r="D21" t="n">
         <v>1.86723e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-193.4699999999998</v>
+        <v>1619.644</v>
       </c>
       <c r="D22" t="n">
         <v>1.87046e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-710.71</v>
+        <v>1988.348</v>
       </c>
       <c r="D2" t="n">
         <v>1.85436e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-401.48</v>
+        <v>1682.077</v>
       </c>
       <c r="D3" t="n">
         <v>1.90819e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-327.4599999999998</v>
+        <v>1611.404</v>
       </c>
       <c r="D4" t="n">
         <v>1.9192e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-303.99</v>
+        <v>1575.579</v>
       </c>
       <c r="D5" t="n">
         <v>1.92239e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-293.5</v>
+        <v>1536.597</v>
       </c>
       <c r="D6" t="n">
         <v>1.92703e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-278.8600000000001</v>
+        <v>1512.392</v>
       </c>
       <c r="D7" t="n">
         <v>1.93103e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-262.6400000000001</v>
+        <v>1492.181</v>
       </c>
       <c r="D8" t="n">
         <v>1.93365e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-256.4499999999998</v>
+        <v>1461.894</v>
       </c>
       <c r="D9" t="n">
         <v>1.93899e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-245.7700000000002</v>
+        <v>1439.08</v>
       </c>
       <c r="D10" t="n">
         <v>1.94223e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-249.0799999999999</v>
+        <v>1414.254</v>
       </c>
       <c r="D11" t="n">
         <v>1.94502e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-395.9899999999998</v>
+        <v>2111.898</v>
       </c>
       <c r="D2" t="n">
         <v>1.86901e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-312.2599999999998</v>
+        <v>1997.472</v>
       </c>
       <c r="D3" t="n">
         <v>1.88328e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-289.2800000000002</v>
+        <v>1954.439</v>
       </c>
       <c r="D4" t="n">
         <v>1.89304e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-272.3499999999999</v>
+        <v>1925.279</v>
       </c>
       <c r="D5" t="n">
         <v>1.90045e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-266.0999999999999</v>
+        <v>1893.883</v>
       </c>
       <c r="D6" t="n">
         <v>1.90706e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-258.4899999999998</v>
+        <v>1868.608</v>
       </c>
       <c r="D7" t="n">
         <v>1.91195e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-248.6100000000001</v>
+        <v>1845.438</v>
       </c>
       <c r="D8" t="n">
         <v>1.91644e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-245.1900000000001</v>
+        <v>1825.197</v>
       </c>
       <c r="D9" t="n">
         <v>1.91903e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-250.5</v>
+        <v>1794.576</v>
       </c>
       <c r="D10" t="n">
         <v>1.92277e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-230.0599999999999</v>
+        <v>1784.815</v>
       </c>
       <c r="D11" t="n">
         <v>1.92693e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-228.3900000000003</v>
+        <v>1762.292</v>
       </c>
       <c r="D12" t="n">
         <v>1.92978e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-218.1699999999996</v>
+        <v>1738.861</v>
       </c>
       <c r="D13" t="n">
         <v>1.93443e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-222.8499999999999</v>
+        <v>1708.564</v>
       </c>
       <c r="D14" t="n">
         <v>1.93696e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-218.6199999999999</v>
+        <v>1684.266</v>
       </c>
       <c r="D15" t="n">
         <v>1.93967e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-205.4299999999998</v>
+        <v>1676.935</v>
       </c>
       <c r="D16" t="n">
         <v>1.94321e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-198.6000000000001</v>
+        <v>1649.18</v>
       </c>
       <c r="D17" t="n">
         <v>1.9469e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-179.49</v>
+        <v>1637.094</v>
       </c>
       <c r="D18" t="n">
         <v>1.95083e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-189.1700000000003</v>
+        <v>1609.313</v>
       </c>
       <c r="D19" t="n">
         <v>1.95229e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-179.8</v>
+        <v>1592</v>
       </c>
       <c r="D20" t="n">
         <v>1.95609e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-182.6300000000001</v>
+        <v>1567.873</v>
       </c>
       <c r="D21" t="n">
         <v>1.95864e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-170.4299999999998</v>
+        <v>1556.609</v>
       </c>
       <c r="D22" t="n">
         <v>1.96232e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-672.26</v>
+        <v>1325.072</v>
       </c>
       <c r="D2" t="n">
         <v>2.08623e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-320.5600000000002</v>
+        <v>1141.581</v>
       </c>
       <c r="D3" t="n">
         <v>2.06994e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-262.3300000000002</v>
+        <v>1090.47</v>
       </c>
       <c r="D4" t="n">
         <v>2.06951e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-241.1200000000001</v>
+        <v>1065.158</v>
       </c>
       <c r="D5" t="n">
         <v>2.07057e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-233.0799999999999</v>
+        <v>1038.614</v>
       </c>
       <c r="D6" t="n">
         <v>2.07355e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-217.29</v>
+        <v>1023.88</v>
       </c>
       <c r="D7" t="n">
         <v>2.07609e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-217.1500000000001</v>
+        <v>1003.1</v>
       </c>
       <c r="D8" t="n">
         <v>2.078e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-205.1599999999999</v>
+        <v>978.5730000000001</v>
       </c>
       <c r="D9" t="n">
         <v>2.07998e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-192.73</v>
+        <v>966.352</v>
       </c>
       <c r="D10" t="n">
         <v>2.08297e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-196.6299999999999</v>
+        <v>940.7620000000001</v>
       </c>
       <c r="D11" t="n">
         <v>2.0844e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>2319.272</v>
       </c>
+      <c r="C2" t="n">
+        <v>2765.25339923485</v>
+      </c>
       <c r="D2" t="n">
         <v>1.79726e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>2218.411</v>
       </c>
+      <c r="C3" t="n">
+        <v>2650.622563497349</v>
+      </c>
       <c r="D3" t="n">
         <v>1.79278e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>2150.1</v>
       </c>
+      <c r="C4" t="n">
+        <v>2586.037259708128</v>
+      </c>
       <c r="D4" t="n">
         <v>1.79373e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>2094.711</v>
       </c>
+      <c r="C5" t="n">
+        <v>2535.159229752001</v>
+      </c>
       <c r="D5" t="n">
         <v>1.79765e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>2051.908</v>
       </c>
+      <c r="C6" t="n">
+        <v>2497.098894081099</v>
+      </c>
       <c r="D6" t="n">
         <v>1.80066e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>2025.09</v>
       </c>
+      <c r="C7" t="n">
+        <v>2466.804762772409</v>
+      </c>
       <c r="D7" t="n">
         <v>1.8041e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>1982.399</v>
       </c>
+      <c r="C8" t="n">
+        <v>2429.809241504423</v>
+      </c>
       <c r="D8" t="n">
         <v>1.80841e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>1952.526</v>
       </c>
+      <c r="C9" t="n">
+        <v>2398.159385734003</v>
+      </c>
       <c r="D9" t="n">
         <v>1.81234e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>1920.287</v>
       </c>
+      <c r="C10" t="n">
+        <v>2366.659126029585</v>
+      </c>
       <c r="D10" t="n">
         <v>1.81622e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>1877.408</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2329.062851415299</v>
       </c>
       <c r="D11" t="n">
         <v>1.82048e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>2049.569</v>
       </c>
+      <c r="C2" t="n">
+        <v>2502.457019276659</v>
+      </c>
       <c r="D2" t="n">
         <v>1.89568e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>1921.625</v>
       </c>
+      <c r="C3" t="n">
+        <v>2353.262974834514</v>
+      </c>
       <c r="D3" t="n">
         <v>1.92475e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>1896.133</v>
       </c>
+      <c r="C4" t="n">
+        <v>2319.334081953533</v>
+      </c>
       <c r="D4" t="n">
         <v>1.93395e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>1858.729</v>
       </c>
+      <c r="C5" t="n">
+        <v>2285.841974392742</v>
+      </c>
       <c r="D5" t="n">
         <v>1.94005e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>1829.222</v>
       </c>
+      <c r="C6" t="n">
+        <v>2261.227465319625</v>
+      </c>
       <c r="D6" t="n">
         <v>1.94399e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>1799.899</v>
       </c>
+      <c r="C7" t="n">
+        <v>2232.109885448911</v>
+      </c>
       <c r="D7" t="n">
         <v>1.95007e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>1778.92</v>
       </c>
+      <c r="C8" t="n">
+        <v>2210.12024384711</v>
+      </c>
       <c r="D8" t="n">
         <v>1.95551e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>1747.645</v>
       </c>
+      <c r="C9" t="n">
+        <v>2180.05996833487</v>
+      </c>
       <c r="D9" t="n">
         <v>1.96055e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>1715.609</v>
       </c>
+      <c r="C10" t="n">
+        <v>2154.481310829325</v>
+      </c>
       <c r="D10" t="n">
         <v>1.96625e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>1700.874</v>
       </c>
+      <c r="C11" t="n">
+        <v>2135.370643899865</v>
+      </c>
       <c r="D11" t="n">
         <v>1.9695e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>1684.541</v>
       </c>
+      <c r="C12" t="n">
+        <v>2116.652863858062</v>
+      </c>
       <c r="D12" t="n">
         <v>1.97248e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>1664.2</v>
       </c>
+      <c r="C13" t="n">
+        <v>2093.313739543561</v>
+      </c>
       <c r="D13" t="n">
         <v>1.9763e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>1637.12</v>
       </c>
+      <c r="C14" t="n">
+        <v>2068.743970203242</v>
+      </c>
       <c r="D14" t="n">
         <v>1.98164e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>1614.806</v>
       </c>
+      <c r="C15" t="n">
+        <v>2046.403633786304</v>
+      </c>
       <c r="D15" t="n">
         <v>1.9857e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>1590.964</v>
       </c>
+      <c r="C16" t="n">
+        <v>2023.749407709066</v>
+      </c>
       <c r="D16" t="n">
         <v>1.98769e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>1575.338</v>
       </c>
+      <c r="C17" t="n">
+        <v>2005.738477473314</v>
+      </c>
       <c r="D17" t="n">
         <v>1.99302e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>1542.203</v>
       </c>
+      <c r="C18" t="n">
+        <v>1979.022110820506</v>
+      </c>
       <c r="D18" t="n">
         <v>1.99637e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>1538.817</v>
       </c>
+      <c r="C19" t="n">
+        <v>1967.140914746095</v>
+      </c>
       <c r="D19" t="n">
         <v>1.99729e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>1514.049</v>
       </c>
+      <c r="C20" t="n">
+        <v>1943.173117955198</v>
+      </c>
       <c r="D20" t="n">
         <v>2.00154e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>1496.498</v>
       </c>
+      <c r="C21" t="n">
+        <v>1925.721806707736</v>
+      </c>
       <c r="D21" t="n">
         <v>2.00368e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>1488.396</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1915.514230814465</v>
       </c>
       <c r="D22" t="n">
         <v>2.00741e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>2296.259</v>
       </c>
+      <c r="C2" t="n">
+        <v>2767.481619554566</v>
+      </c>
       <c r="D2" t="n">
         <v>1.76371e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>2135.695</v>
       </c>
+      <c r="C3" t="n">
+        <v>2582.399292919124</v>
+      </c>
       <c r="D3" t="n">
         <v>1.78267e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>2095.379</v>
       </c>
+      <c r="C4" t="n">
+        <v>2535.981933143532</v>
+      </c>
       <c r="D4" t="n">
         <v>1.78277e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>2056.981</v>
       </c>
+      <c r="C5" t="n">
+        <v>2499.49506100792</v>
+      </c>
       <c r="D5" t="n">
         <v>1.78542e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>2028.168</v>
       </c>
+      <c r="C6" t="n">
+        <v>2472.089158229961</v>
+      </c>
       <c r="D6" t="n">
         <v>1.78356e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>1997.313</v>
       </c>
+      <c r="C7" t="n">
+        <v>2444.476983435881</v>
+      </c>
       <c r="D7" t="n">
         <v>1.78514e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>1970.152</v>
       </c>
+      <c r="C8" t="n">
+        <v>2417.530860315659</v>
+      </c>
       <c r="D8" t="n">
         <v>1.78715e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>1933.798</v>
       </c>
+      <c r="C9" t="n">
+        <v>2387.038078666194</v>
+      </c>
       <c r="D9" t="n">
         <v>1.78614e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>1916.056</v>
       </c>
+      <c r="C10" t="n">
+        <v>2366.946448651923</v>
+      </c>
       <c r="D10" t="n">
         <v>1.78607e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>1882.6</v>
       </c>
+      <c r="C11" t="n">
+        <v>2334.931188423901</v>
+      </c>
       <c r="D11" t="n">
         <v>1.78627e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>1863.725</v>
       </c>
+      <c r="C12" t="n">
+        <v>2316.328382264959</v>
+      </c>
       <c r="D12" t="n">
         <v>1.78455e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>1834.568</v>
       </c>
+      <c r="C13" t="n">
+        <v>2288.008128823943</v>
+      </c>
       <c r="D13" t="n">
         <v>1.78432e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>1806.722</v>
       </c>
+      <c r="C14" t="n">
+        <v>2261.961931595813</v>
+      </c>
       <c r="D14" t="n">
         <v>1.78076e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>1782.123</v>
       </c>
+      <c r="C15" t="n">
+        <v>2236.594265495209</v>
+      </c>
       <c r="D15" t="n">
         <v>1.77901e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>1766.725</v>
       </c>
+      <c r="C16" t="n">
+        <v>2222.257767649715</v>
+      </c>
       <c r="D16" t="n">
         <v>1.77859e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>1739.261</v>
       </c>
+      <c r="C17" t="n">
+        <v>2195.071520239685</v>
+      </c>
       <c r="D17" t="n">
         <v>1.77748e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>1719.156</v>
       </c>
+      <c r="C18" t="n">
+        <v>2173.805933216641</v>
+      </c>
       <c r="D18" t="n">
         <v>1.77596e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>1697.681</v>
       </c>
+      <c r="C19" t="n">
+        <v>2153.698610262876</v>
+      </c>
       <c r="D19" t="n">
         <v>1.77453e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>1683.348</v>
       </c>
+      <c r="C20" t="n">
+        <v>2137.701149432174</v>
+      </c>
       <c r="D20" t="n">
         <v>1.77162e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>1659.877</v>
       </c>
+      <c r="C21" t="n">
+        <v>2113.079460492747</v>
+      </c>
       <c r="D21" t="n">
         <v>1.77016e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>1635.382</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2089.876805188434</v>
       </c>
       <c r="D22" t="n">
         <v>1.77114e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>2055.368</v>
       </c>
+      <c r="C2" t="n">
+        <v>2652.611683478858</v>
+      </c>
       <c r="D2" t="n">
         <v>1.79691e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>1749.25</v>
       </c>
+      <c r="C3" t="n">
+        <v>2264.066556795311</v>
+      </c>
       <c r="D3" t="n">
         <v>1.86279e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>1674.421</v>
       </c>
+      <c r="C4" t="n">
+        <v>2179.190813969196</v>
+      </c>
       <c r="D4" t="n">
         <v>1.8711e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>1620.014</v>
       </c>
+      <c r="C5" t="n">
+        <v>2127.643999852218</v>
+      </c>
       <c r="D5" t="n">
         <v>1.8701e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>1592.746</v>
       </c>
+      <c r="C6" t="n">
+        <v>2103.036253573521</v>
+      </c>
       <c r="D6" t="n">
         <v>1.87345e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>1560.177</v>
       </c>
+      <c r="C7" t="n">
+        <v>2073.687472824779</v>
+      </c>
       <c r="D7" t="n">
         <v>1.87595e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>1527.535</v>
       </c>
+      <c r="C8" t="n">
+        <v>2044.473473153196</v>
+      </c>
       <c r="D8" t="n">
         <v>1.87763e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>1503.321</v>
       </c>
+      <c r="C9" t="n">
+        <v>2020.465082799839</v>
+      </c>
       <c r="D9" t="n">
         <v>1.87885e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>1479.373</v>
       </c>
+      <c r="C10" t="n">
+        <v>1999.617652474425</v>
+      </c>
       <c r="D10" t="n">
         <v>1.88043e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>1458.328</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1978.833045984886</v>
       </c>
       <c r="D11" t="n">
         <v>1.88263e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>2109.609</v>
       </c>
+      <c r="C2" t="n">
+        <v>2566.457828555054</v>
+      </c>
       <c r="D2" t="n">
         <v>1.80582e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>2004.165</v>
       </c>
+      <c r="C3" t="n">
+        <v>2441.970338644355</v>
+      </c>
       <c r="D3" t="n">
         <v>1.82804e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>1954.573</v>
       </c>
+      <c r="C4" t="n">
+        <v>2393.271221472365</v>
+      </c>
       <c r="D4" t="n">
         <v>1.83893e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>1932.932</v>
       </c>
+      <c r="C5" t="n">
+        <v>2368.29517136367</v>
+      </c>
       <c r="D5" t="n">
         <v>1.8475e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>1894.38</v>
       </c>
+      <c r="C6" t="n">
+        <v>2337.283902193636</v>
+      </c>
       <c r="D6" t="n">
         <v>1.85466e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>1862.599</v>
       </c>
+      <c r="C7" t="n">
+        <v>2306.377750178047</v>
+      </c>
       <c r="D7" t="n">
         <v>1.85812e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>1829.782</v>
       </c>
+      <c r="C8" t="n">
+        <v>2276.92218542719</v>
+      </c>
       <c r="D8" t="n">
         <v>1.86224e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>1813.049</v>
       </c>
+      <c r="C9" t="n">
+        <v>2258.937578484088</v>
+      </c>
       <c r="D9" t="n">
         <v>1.86793e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>1791.775</v>
       </c>
+      <c r="C10" t="n">
+        <v>2236.002473812734</v>
+      </c>
       <c r="D10" t="n">
         <v>1.87002e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>1771.164</v>
       </c>
+      <c r="C11" t="n">
+        <v>2212.324578166099</v>
+      </c>
       <c r="D11" t="n">
         <v>1.87396e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>1747.663</v>
       </c>
+      <c r="C12" t="n">
+        <v>2191.949889980789</v>
+      </c>
       <c r="D12" t="n">
         <v>1.87648e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>1724.264</v>
       </c>
+      <c r="C13" t="n">
+        <v>2166.857486197992</v>
+      </c>
       <c r="D13" t="n">
         <v>1.88127e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>1700.635</v>
       </c>
+      <c r="C14" t="n">
+        <v>2146.104086115552</v>
+      </c>
       <c r="D14" t="n">
         <v>1.88564e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>1679.72</v>
       </c>
+      <c r="C15" t="n">
+        <v>2121.846854622285</v>
+      </c>
       <c r="D15" t="n">
         <v>1.88678e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>1659.648</v>
       </c>
+      <c r="C16" t="n">
+        <v>2098.258564823981</v>
+      </c>
       <c r="D16" t="n">
         <v>1.88925e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>1637.082</v>
       </c>
+      <c r="C17" t="n">
+        <v>2076.771142898563</v>
+      </c>
       <c r="D17" t="n">
         <v>1.89484e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>1615.956</v>
       </c>
+      <c r="C18" t="n">
+        <v>2055.027266979027</v>
+      </c>
       <c r="D18" t="n">
         <v>1.89727e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>1587.141</v>
       </c>
+      <c r="C19" t="n">
+        <v>2028.656706785446</v>
+      </c>
       <c r="D19" t="n">
         <v>1.89987e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>1565.966</v>
       </c>
+      <c r="C20" t="n">
+        <v>2005.845559730371</v>
+      </c>
       <c r="D20" t="n">
         <v>1.90312e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>1552.813</v>
       </c>
+      <c r="C21" t="n">
+        <v>1989.903047368714</v>
+      </c>
       <c r="D21" t="n">
         <v>1.9041e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>1529.684</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1966.252372203238</v>
       </c>
       <c r="D22" t="n">
         <v>1.90786e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>2145.244</v>
       </c>
+      <c r="C2" t="n">
+        <v>2717.564994895205</v>
+      </c>
       <c r="D2" t="n">
         <v>1.76943e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>1804.357</v>
       </c>
+      <c r="C3" t="n">
+        <v>2283.147365066457</v>
+      </c>
       <c r="D3" t="n">
         <v>1.84077e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>1710.582</v>
       </c>
+      <c r="C4" t="n">
+        <v>2177.390011964691</v>
+      </c>
       <c r="D4" t="n">
         <v>1.85184e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>1671.218</v>
       </c>
+      <c r="C5" t="n">
+        <v>2138.222782543589</v>
+      </c>
       <c r="D5" t="n">
         <v>1.85759e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>1648.205</v>
       </c>
+      <c r="C6" t="n">
+        <v>2112.526259575811</v>
+      </c>
       <c r="D6" t="n">
         <v>1.85986e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>1600.842</v>
       </c>
+      <c r="C7" t="n">
+        <v>2073.77550909039</v>
+      </c>
       <c r="D7" t="n">
         <v>1.86409e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>1586.441</v>
       </c>
+      <c r="C8" t="n">
+        <v>2055.369711888345</v>
+      </c>
       <c r="D8" t="n">
         <v>1.86455e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>1557.725</v>
       </c>
+      <c r="C9" t="n">
+        <v>2029.460098808713</v>
+      </c>
       <c r="D9" t="n">
         <v>1.86925e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>1522.092</v>
       </c>
+      <c r="C10" t="n">
+        <v>1996.123038045879</v>
+      </c>
       <c r="D10" t="n">
         <v>1.87132e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>1502.414</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1977.252821410763</v>
       </c>
       <c r="D11" t="n">
         <v>1.87239e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>2164.259</v>
       </c>
+      <c r="C2" t="n">
+        <v>2615.042423759553</v>
+      </c>
       <c r="D2" t="n">
         <v>1.79463e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>2069.956</v>
       </c>
+      <c r="C3" t="n">
+        <v>2500.482359148224</v>
+      </c>
       <c r="D3" t="n">
         <v>1.80846e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>2029.286</v>
       </c>
+      <c r="C4" t="n">
+        <v>2455.973236641828</v>
+      </c>
       <c r="D4" t="n">
         <v>1.81489e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>1988.22</v>
       </c>
+      <c r="C5" t="n">
+        <v>2420.142799335162</v>
+      </c>
       <c r="D5" t="n">
         <v>1.82214e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>1961.517</v>
       </c>
+      <c r="C6" t="n">
+        <v>2394.114206196847</v>
+      </c>
       <c r="D6" t="n">
         <v>1.82776e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>1934.235</v>
       </c>
+      <c r="C7" t="n">
+        <v>2369.692124176571</v>
+      </c>
       <c r="D7" t="n">
         <v>1.83007e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>1902.703</v>
       </c>
+      <c r="C8" t="n">
+        <v>2344.196598059812</v>
+      </c>
       <c r="D8" t="n">
         <v>1.83257e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>1881.206</v>
       </c>
+      <c r="C9" t="n">
+        <v>2320.817710551393</v>
+      </c>
       <c r="D9" t="n">
         <v>1.83615e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>1854.214</v>
       </c>
+      <c r="C10" t="n">
+        <v>2296.210351620853</v>
+      </c>
       <c r="D10" t="n">
         <v>1.83892e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>1841.019</v>
       </c>
+      <c r="C11" t="n">
+        <v>2277.764147138912</v>
+      </c>
       <c r="D11" t="n">
         <v>1.84195e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>1813.612</v>
       </c>
+      <c r="C12" t="n">
+        <v>2252.857224841983</v>
+      </c>
       <c r="D12" t="n">
         <v>1.84343e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>1791.995</v>
       </c>
+      <c r="C13" t="n">
+        <v>2232.85959785229</v>
+      </c>
       <c r="D13" t="n">
         <v>1.84847e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>1779.061</v>
       </c>
+      <c r="C14" t="n">
+        <v>2215.694125556464</v>
+      </c>
       <c r="D14" t="n">
         <v>1.8497e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>1763.477</v>
       </c>
+      <c r="C15" t="n">
+        <v>2199.651920674664</v>
+      </c>
       <c r="D15" t="n">
         <v>1.85395e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>1743.803</v>
       </c>
+      <c r="C16" t="n">
+        <v>2178.858437222986</v>
+      </c>
       <c r="D16" t="n">
         <v>1.85489e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>1708.144</v>
       </c>
+      <c r="C17" t="n">
+        <v>2149.082797839986</v>
+      </c>
       <c r="D17" t="n">
         <v>1.85835e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>1697.884</v>
       </c>
+      <c r="C18" t="n">
+        <v>2133.928302754755</v>
+      </c>
       <c r="D18" t="n">
         <v>1.8599e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>1670.326</v>
       </c>
+      <c r="C19" t="n">
+        <v>2109.304827429291</v>
+      </c>
       <c r="D19" t="n">
         <v>1.8624e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>1662.175</v>
       </c>
+      <c r="C20" t="n">
+        <v>2097.502806155587</v>
+      </c>
       <c r="D20" t="n">
         <v>1.86512e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>1626.797</v>
       </c>
+      <c r="C21" t="n">
+        <v>2067.010977353736</v>
+      </c>
       <c r="D21" t="n">
         <v>1.86723e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>1619.644</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2053.956968870594</v>
       </c>
       <c r="D22" t="n">
         <v>1.87046e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>1988.348</v>
       </c>
+      <c r="C2" t="n">
+        <v>2573.669666254917</v>
+      </c>
       <c r="D2" t="n">
         <v>1.85436e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>1682.077</v>
       </c>
+      <c r="C3" t="n">
+        <v>2180.447701705977</v>
+      </c>
       <c r="D3" t="n">
         <v>1.90819e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>1611.404</v>
       </c>
+      <c r="C4" t="n">
+        <v>2097.904199290637</v>
+      </c>
       <c r="D4" t="n">
         <v>1.9192e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>1575.579</v>
       </c>
+      <c r="C5" t="n">
+        <v>2060.821523868785</v>
+      </c>
       <c r="D5" t="n">
         <v>1.92239e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>1536.597</v>
       </c>
+      <c r="C6" t="n">
+        <v>2026.643513510091</v>
+      </c>
       <c r="D6" t="n">
         <v>1.92703e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>1512.392</v>
       </c>
+      <c r="C7" t="n">
+        <v>2002.8456779642</v>
+      </c>
       <c r="D7" t="n">
         <v>1.93103e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>1492.181</v>
       </c>
+      <c r="C8" t="n">
+        <v>1982.807418110533</v>
+      </c>
       <c r="D8" t="n">
         <v>1.93365e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>1461.894</v>
       </c>
+      <c r="C9" t="n">
+        <v>1954.761999520421</v>
+      </c>
       <c r="D9" t="n">
         <v>1.93899e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>1439.08</v>
       </c>
+      <c r="C10" t="n">
+        <v>1932.488133411392</v>
+      </c>
       <c r="D10" t="n">
         <v>1.94223e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>1414.254</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1911.035482429834</v>
       </c>
       <c r="D11" t="n">
         <v>1.94502e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>2111.898</v>
       </c>
+      <c r="C2" t="n">
+        <v>2552.961407012211</v>
+      </c>
       <c r="D2" t="n">
         <v>1.86901e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>1997.472</v>
       </c>
+      <c r="C3" t="n">
+        <v>2422.94721975489</v>
+      </c>
       <c r="D3" t="n">
         <v>1.88328e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>1954.439</v>
       </c>
+      <c r="C4" t="n">
+        <v>2379.479700091805</v>
+      </c>
       <c r="D4" t="n">
         <v>1.89304e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>1925.279</v>
       </c>
+      <c r="C5" t="n">
+        <v>2352.812711962656</v>
+      </c>
       <c r="D5" t="n">
         <v>1.90045e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>1893.883</v>
       </c>
+      <c r="C6" t="n">
+        <v>2322.693735038906</v>
+      </c>
       <c r="D6" t="n">
         <v>1.90706e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>1868.608</v>
       </c>
+      <c r="C7" t="n">
+        <v>2299.839082145288</v>
+      </c>
       <c r="D7" t="n">
         <v>1.91195e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>1845.438</v>
       </c>
+      <c r="C8" t="n">
+        <v>2276.625361202926</v>
+      </c>
       <c r="D8" t="n">
         <v>1.91644e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>1825.197</v>
       </c>
+      <c r="C9" t="n">
+        <v>2256.442935487167</v>
+      </c>
       <c r="D9" t="n">
         <v>1.91903e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>1794.576</v>
       </c>
+      <c r="C10" t="n">
+        <v>2230.130208420808</v>
+      </c>
       <c r="D10" t="n">
         <v>1.92277e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>1784.815</v>
       </c>
+      <c r="C11" t="n">
+        <v>2213.006685241706</v>
+      </c>
       <c r="D11" t="n">
         <v>1.92693e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>1762.292</v>
       </c>
+      <c r="C12" t="n">
+        <v>2192.234469119241</v>
+      </c>
       <c r="D12" t="n">
         <v>1.92978e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>1738.861</v>
       </c>
+      <c r="C13" t="n">
+        <v>2168.935354564524</v>
+      </c>
       <c r="D13" t="n">
         <v>1.93443e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>1708.564</v>
       </c>
+      <c r="C14" t="n">
+        <v>2139.255264570246</v>
+      </c>
       <c r="D14" t="n">
         <v>1.93696e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>1684.266</v>
       </c>
+      <c r="C15" t="n">
+        <v>2117.327598724976</v>
+      </c>
       <c r="D15" t="n">
         <v>1.93967e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>1676.935</v>
       </c>
+      <c r="C16" t="n">
+        <v>2105.778789208036</v>
+      </c>
       <c r="D16" t="n">
         <v>1.94321e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>1649.18</v>
       </c>
+      <c r="C17" t="n">
+        <v>2080.932645665826</v>
+      </c>
       <c r="D17" t="n">
         <v>1.9469e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>1637.094</v>
       </c>
+      <c r="C18" t="n">
+        <v>2065.938413596574</v>
+      </c>
       <c r="D18" t="n">
         <v>1.95083e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>1609.313</v>
       </c>
+      <c r="C19" t="n">
+        <v>2037.999750898706</v>
+      </c>
       <c r="D19" t="n">
         <v>1.95229e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>1592</v>
       </c>
+      <c r="C20" t="n">
+        <v>2020.000788266332</v>
+      </c>
       <c r="D20" t="n">
         <v>1.95609e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>1567.873</v>
       </c>
+      <c r="C21" t="n">
+        <v>1997.820756043844</v>
+      </c>
       <c r="D21" t="n">
         <v>1.95864e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>1556.609</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1979.764543724677</v>
       </c>
       <c r="D22" t="n">
         <v>1.96232e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>1325.072</v>
       </c>
+      <c r="C2" t="n">
+        <v>1956.931832287007</v>
+      </c>
       <c r="D2" t="n">
         <v>2.08623e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>1141.581</v>
       </c>
+      <c r="C3" t="n">
+        <v>1685.654169874066</v>
+      </c>
       <c r="D3" t="n">
         <v>2.06994e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>1090.47</v>
       </c>
+      <c r="C4" t="n">
+        <v>1622.592444608669</v>
+      </c>
       <c r="D4" t="n">
         <v>2.06951e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>1065.158</v>
       </c>
+      <c r="C5" t="n">
+        <v>1598.401910760441</v>
+      </c>
       <c r="D5" t="n">
         <v>2.07057e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>1038.614</v>
       </c>
+      <c r="C6" t="n">
+        <v>1572.961836703589</v>
+      </c>
       <c r="D6" t="n">
         <v>2.07355e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>1023.88</v>
       </c>
+      <c r="C7" t="n">
+        <v>1558.659745854895</v>
+      </c>
       <c r="D7" t="n">
         <v>2.07609e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>1003.1</v>
       </c>
+      <c r="C8" t="n">
+        <v>1535.748760360578</v>
+      </c>
       <c r="D8" t="n">
         <v>2.078e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>978.5730000000001</v>
       </c>
+      <c r="C9" t="n">
+        <v>1519.441347946964</v>
+      </c>
       <c r="D9" t="n">
         <v>2.07998e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>966.352</v>
       </c>
+      <c r="C10" t="n">
+        <v>1508.59743027234</v>
+      </c>
       <c r="D10" t="n">
         <v>2.08297e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>940.7620000000001</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1483.020945823115</v>
       </c>
       <c r="D11" t="n">
         <v>2.0844e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
@@ -565,7 +565,7 @@
         <v>2319.272</v>
       </c>
       <c r="C2" t="n">
-        <v>2765.25339923485</v>
+        <v>23844.27806002394</v>
       </c>
       <c r="D2" t="n">
         <v>1.79726e-07</v>
@@ -598,10 +598,7 @@
         <v>-29914.98110711802</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.57799203963456e-11</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3162.623821967788</v>
+        <v>-20329.69385283679</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000012e-08</v>
@@ -618,7 +615,7 @@
         <v>2218.411</v>
       </c>
       <c r="C3" t="n">
-        <v>2650.622563497349</v>
+        <v>1041.781633257731</v>
       </c>
       <c r="D3" t="n">
         <v>1.79278e-07</v>
@@ -651,16 +648,13 @@
         <v>-34761.02860804056</v>
       </c>
       <c r="Y3" t="n">
-        <v>169.2984843203908</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3196.958776527149</v>
+        <v>400.2417148268166</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.449986721646182e-08</v>
+        <v>7.037587496269356e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7991918328057676</v>
+        <v>0.9947606154262012</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +665,7 @@
         <v>2150.1</v>
       </c>
       <c r="C4" t="n">
-        <v>2586.037259708128</v>
+        <v>1004.262517849752</v>
       </c>
       <c r="D4" t="n">
         <v>1.79373e-07</v>
@@ -704,16 +698,13 @@
         <v>-33591.47731365899</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.156849441056458e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2970.216919520805</v>
+        <v>425.5564239757688</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000201e-08</v>
+        <v>7.470883090811317e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8171991454006072</v>
+        <v>0.9971730408241137</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +715,7 @@
         <v>2094.711</v>
       </c>
       <c r="C5" t="n">
-        <v>2535.159229752001</v>
+        <v>976.0361372716853</v>
       </c>
       <c r="D5" t="n">
         <v>1.79765e-07</v>
@@ -757,16 +748,13 @@
         <v>-32031.92196320686</v>
       </c>
       <c r="Y5" t="n">
-        <v>174.5331168529545</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3043.918106517487</v>
+        <v>442.8013555432655</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.432291297293793e-08</v>
+        <v>1.023113065572e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8012758228254919</v>
+        <v>0.9807764032430547</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +765,7 @@
         <v>2051.908</v>
       </c>
       <c r="C6" t="n">
-        <v>2497.098894081099</v>
+        <v>952.3570730543887</v>
       </c>
       <c r="D6" t="n">
         <v>1.80066e-07</v>
@@ -810,16 +798,13 @@
         <v>-31913.06618704371</v>
       </c>
       <c r="Y6" t="n">
-        <v>170.9042396417636</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2966.506574842459</v>
+        <v>456.5165582953535</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.428577322949221e-08</v>
+        <v>9.285355003542521e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8013860969554942</v>
+        <v>0.9897748592953416</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +815,7 @@
         <v>2025.09</v>
       </c>
       <c r="C7" t="n">
-        <v>2466.804762772409</v>
+        <v>930.2178653349423</v>
       </c>
       <c r="D7" t="n">
         <v>1.8041e-07</v>
@@ -863,16 +848,13 @@
         <v>-33633.35851403059</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.703271881903417e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2822.798465620636</v>
+        <v>443.8938498376136</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000050927e-08</v>
+        <v>7.778231396964356e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8177443413666805</v>
+        <v>0.9988189711697365</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +865,7 @@
         <v>1982.399</v>
       </c>
       <c r="C8" t="n">
-        <v>2429.809241504423</v>
+        <v>913.5032947087027</v>
       </c>
       <c r="D8" t="n">
         <v>1.80841e-07</v>
@@ -916,16 +898,13 @@
         <v>-31559.41778611071</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.229611816513598e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2780.688961265309</v>
+        <v>473.8273649522764</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000083773e-08</v>
+        <v>1.030269065896219e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8179917421367228</v>
+        <v>0.985151377449523</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +915,7 @@
         <v>1952.526</v>
       </c>
       <c r="C9" t="n">
-        <v>2398.159385734003</v>
+        <v>898.1224396727329</v>
       </c>
       <c r="D9" t="n">
         <v>1.81234e-07</v>
@@ -969,16 +948,13 @@
         <v>-31152.41284712239</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.282739444726501e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2741.026458025862</v>
+        <v>466.888686083195</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000168214e-08</v>
+        <v>8.369667679291777e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8182273988864641</v>
+        <v>0.9983042093822891</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +965,7 @@
         <v>1920.287</v>
       </c>
       <c r="C10" t="n">
-        <v>2366.659126029585</v>
+        <v>883.4011610673389</v>
       </c>
       <c r="D10" t="n">
         <v>1.81622e-07</v>
@@ -1022,16 +998,13 @@
         <v>-31221.48532913067</v>
       </c>
       <c r="Y10" t="n">
-        <v>171.0881415868463</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2789.254748204574</v>
+        <v>496.2926537291119</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.459199413072242e-08</v>
+        <v>1.281674088096457e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8012792039769343</v>
+        <v>0.9680636018055756</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1015,7 @@
         <v>1877.408</v>
       </c>
       <c r="C11" t="n">
-        <v>2329.062851415299</v>
+        <v>868.9198513396524</v>
       </c>
       <c r="D11" t="n">
         <v>1.82048e-07</v>
@@ -1075,16 +1048,13 @@
         <v>-27995.56745854828</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.809456445001685e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2670.130623209288</v>
+        <v>493.6093206729718</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000014896e-08</v>
+        <v>9.51236020932271e-10</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8186774839590578</v>
+        <v>0.9939049943049999</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1211,7 @@
         <v>2049.569</v>
       </c>
       <c r="C2" t="n">
-        <v>2502.457019276659</v>
+        <v>934.3702432678879</v>
       </c>
       <c r="D2" t="n">
         <v>1.89568e-07</v>
@@ -1274,16 +1244,13 @@
         <v>-32276.24153380185</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.062713675080443e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2817.482606988762</v>
+        <v>481.8949383597537</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000009562e-08</v>
+        <v>1.775206457464767e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8197788815018751</v>
+        <v>0.9492854241750405</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1261,7 @@
         <v>1921.625</v>
       </c>
       <c r="C3" t="n">
-        <v>2353.262974834514</v>
+        <v>880.9408768100415</v>
       </c>
       <c r="D3" t="n">
         <v>1.92475e-07</v>
@@ -1327,16 +1294,13 @@
         <v>-30869.33157610318</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.199384125382961e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2696.651472895748</v>
+        <v>456.3986705762126</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000047e-08</v>
+        <v>1.06907588732117e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8202425632635399</v>
+        <v>0.9830353947588316</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1311,7 @@
         <v>1896.133</v>
       </c>
       <c r="C4" t="n">
-        <v>2319.334081953533</v>
+        <v>861.9961825194481</v>
       </c>
       <c r="D4" t="n">
         <v>1.93395e-07</v>
@@ -1380,16 +1344,13 @@
         <v>-34249.29508316806</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.977309999750351e-11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2651.245768338757</v>
+        <v>468.8820659495628</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.00000000000035e-08</v>
+        <v>1.219170985048648e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8203774656077029</v>
+        <v>0.9807194675397339</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1361,7 @@
         <v>1858.729</v>
       </c>
       <c r="C5" t="n">
-        <v>2285.841974392742</v>
+        <v>848.19041876762</v>
       </c>
       <c r="D5" t="n">
         <v>1.94005e-07</v>
@@ -1433,16 +1394,13 @@
         <v>-32210.21361267188</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.412983682853059e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2617.722928009755</v>
+        <v>474.4113344212401</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000002194e-08</v>
+        <v>9.372355743042681e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8204699467478979</v>
+        <v>0.9979380963848797</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1411,7 @@
         <v>1829.222</v>
       </c>
       <c r="C6" t="n">
-        <v>2261.227465319625</v>
+        <v>837.0617626335777</v>
       </c>
       <c r="D6" t="n">
         <v>1.94399e-07</v>
@@ -1486,16 +1444,13 @@
         <v>-30819.6149635234</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.754991111739672e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2586.391296198517</v>
+        <v>479.1281354904103</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.00000000000004e-08</v>
+        <v>1.009199592786755e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8206270444170378</v>
+        <v>0.9960057718775555</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1461,7 @@
         <v>1799.899</v>
       </c>
       <c r="C7" t="n">
-        <v>2232.109885448911</v>
+        <v>824.1581325575819</v>
       </c>
       <c r="D7" t="n">
         <v>1.95007e-07</v>
@@ -1539,16 +1494,13 @@
         <v>-30711.9201904497</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.754305017899591e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2552.541169396459</v>
+        <v>480.4778831147132</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000005444e-08</v>
+        <v>9.302652497455268e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8208245912413163</v>
+        <v>0.9970848126815218</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1511,7 @@
         <v>1778.92</v>
       </c>
       <c r="C8" t="n">
-        <v>2210.12024384711</v>
+        <v>811.944984627101</v>
       </c>
       <c r="D8" t="n">
         <v>1.95551e-07</v>
@@ -1592,16 +1544,13 @@
         <v>-31356.98386594918</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.503501385785679e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2520.051021445846</v>
+        <v>470.4126698604636</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000103e-08</v>
+        <v>9.045038175323504e-10</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8210531653555203</v>
+        <v>0.9990130293528993</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1561,7 @@
         <v>1747.645</v>
       </c>
       <c r="C9" t="n">
-        <v>2180.05996833487</v>
+        <v>801.0763437655667</v>
       </c>
       <c r="D9" t="n">
         <v>1.96055e-07</v>
@@ -1645,16 +1594,13 @@
         <v>-29651.04948460772</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.103607156150456e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2488.499623189355</v>
+        <v>494.0252919680036</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000004e-08</v>
+        <v>9.977889302581655e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8213020873958177</v>
+        <v>0.9986795038717666</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1611,7 @@
         <v>1715.609</v>
       </c>
       <c r="C10" t="n">
-        <v>2154.481310829325</v>
+        <v>791.3193184998842</v>
       </c>
       <c r="D10" t="n">
         <v>1.96625e-07</v>
@@ -1698,16 +1644,13 @@
         <v>-28365.29311611508</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.69315635028907e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2458.740340453454</v>
+        <v>477.717809182793</v>
       </c>
       <c r="AA10" t="n">
-        <v>1e-08</v>
+        <v>9.519306478774155e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8215601878843636</v>
+        <v>0.99778149147419</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1661,7 @@
         <v>1700.874</v>
       </c>
       <c r="C11" t="n">
-        <v>2135.370643899865</v>
+        <v>781.3965894313219</v>
       </c>
       <c r="D11" t="n">
         <v>1.9695e-07</v>
@@ -1751,16 +1694,13 @@
         <v>-29499.88895770364</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.469416570882947e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2430.19508284942</v>
+        <v>495.4270263084382</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000012e-08</v>
+        <v>9.975510602701784e-10</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8218355076552178</v>
+        <v>0.9970172195316503</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1711,7 @@
         <v>1684.541</v>
       </c>
       <c r="C12" t="n">
-        <v>2116.652863858062</v>
+        <v>771.7689737625005</v>
       </c>
       <c r="D12" t="n">
         <v>1.97248e-07</v>
@@ -1804,16 +1744,13 @@
         <v>-30652.09157851015</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.227592549317984e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2402.334189525924</v>
+        <v>493.0677308699052</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000003668e-08</v>
+        <v>1.15820557836235e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8221100891259403</v>
+        <v>0.9900647092971634</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1761,7 @@
         <v>1664.2</v>
       </c>
       <c r="C13" t="n">
-        <v>2093.313739543561</v>
+        <v>762.3546074561652</v>
       </c>
       <c r="D13" t="n">
         <v>1.9763e-07</v>
@@ -1857,16 +1794,13 @@
         <v>-30985.04205280727</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.068240441306971e-07</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2375.18471007619</v>
+        <v>490.8370265534811</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000007576e-08</v>
+        <v>1.06709471749455e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8224020485155823</v>
+        <v>0.997985760891249</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1811,7 @@
         <v>1637.12</v>
       </c>
       <c r="C14" t="n">
-        <v>2068.743970203242</v>
+        <v>753.9224321379037</v>
       </c>
       <c r="D14" t="n">
         <v>1.98164e-07</v>
@@ -1910,16 +1844,13 @@
         <v>-28104.00107703159</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.264119972202835e-10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2347.983299388562</v>
+        <v>496.2342403110572</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000001325e-08</v>
+        <v>1.142350356178741e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8227032451695064</v>
+        <v>0.9968221818899595</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1861,7 @@
         <v>1614.806</v>
       </c>
       <c r="C15" t="n">
-        <v>2046.403633786304</v>
+        <v>745.059849415867</v>
       </c>
       <c r="D15" t="n">
         <v>1.9857e-07</v>
@@ -1963,16 +1894,13 @@
         <v>-28294.57574853358</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.648564380359053e-09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2321.447823498657</v>
+        <v>463.0922168385183</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000003e-08</v>
+        <v>1.132747186789178e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8230266146558169</v>
+        <v>0.9976112858513351</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1911,7 @@
         <v>1590.964</v>
       </c>
       <c r="C16" t="n">
-        <v>2023.749407709066</v>
+        <v>737.1740815295241</v>
       </c>
       <c r="D16" t="n">
         <v>1.98769e-07</v>
@@ -2016,16 +1944,13 @@
         <v>-26179.97634280716</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.444975292971956e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2295.454333830792</v>
+        <v>490.9773476758306</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000037474e-08</v>
+        <v>1.152966396587042e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.823351715766147</v>
+        <v>0.9945913870258327</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1961,7 @@
         <v>1575.338</v>
       </c>
       <c r="C17" t="n">
-        <v>2005.738477473314</v>
+        <v>728.5942545514757</v>
       </c>
       <c r="D17" t="n">
         <v>1.99302e-07</v>
@@ -2069,16 +1994,13 @@
         <v>-26857.77674374761</v>
       </c>
       <c r="Y17" t="n">
-        <v>7.284878717459521e-10</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2269.520303373984</v>
+        <v>490.3702926103192</v>
       </c>
       <c r="AA17" t="n">
-        <v>1e-08</v>
+        <v>1.16921370205845e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8236752203402323</v>
+        <v>0.9946691144636098</v>
       </c>
     </row>
     <row r="18">
@@ -2089,7 +2011,7 @@
         <v>1542.203</v>
       </c>
       <c r="C18" t="n">
-        <v>1979.022110820506</v>
+        <v>720.4329978498675</v>
       </c>
       <c r="D18" t="n">
         <v>1.99637e-07</v>
@@ -2122,16 +2044,13 @@
         <v>-24813.23486023556</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.122146396175027e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2244.281534153596</v>
+        <v>489.1844276572866</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000082565e-08</v>
+        <v>1.183201348950048e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8240364476399836</v>
+        <v>0.9947346148360996</v>
       </c>
     </row>
     <row r="19">
@@ -2142,7 +2061,7 @@
         <v>1538.817</v>
       </c>
       <c r="C19" t="n">
-        <v>1967.140914746095</v>
+        <v>712.8161426129523</v>
       </c>
       <c r="D19" t="n">
         <v>1.99729e-07</v>
@@ -2175,16 +2094,13 @@
         <v>-26751.19685487385</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.153696038650151e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2220.052834556127</v>
+        <v>479.0083591633943</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000071e-08</v>
+        <v>1.074340610865071e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8243669625812434</v>
+        <v>0.9975256481747612</v>
       </c>
     </row>
     <row r="20">
@@ -2195,7 +2111,7 @@
         <v>1514.049</v>
       </c>
       <c r="C20" t="n">
-        <v>1943.173117955198</v>
+        <v>707.7180914104667</v>
       </c>
       <c r="D20" t="n">
         <v>2.00154e-07</v>
@@ -2228,16 +2144,13 @@
         <v>-25046.5227868827</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.228405024624928e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2195.472264591197</v>
+        <v>469.1170590699004</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000292e-08</v>
+        <v>1.035239210861627e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8247232020220793</v>
+        <v>0.9987502165511425</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2161,7 @@
         <v>1496.498</v>
       </c>
       <c r="C21" t="n">
-        <v>1925.721806707736</v>
+        <v>702.566688746025</v>
       </c>
       <c r="D21" t="n">
         <v>2.00368e-07</v>
@@ -2281,16 +2194,13 @@
         <v>-24639.74399748924</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.819276857280407e-10</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2171.634071564724</v>
+        <v>475.8470030449392</v>
       </c>
       <c r="AA21" t="n">
-        <v>1e-08</v>
+        <v>1.468726159629952e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8250811738977637</v>
+        <v>0.9823936226828802</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2211,7 @@
         <v>1488.396</v>
       </c>
       <c r="C22" t="n">
-        <v>1915.514230814465</v>
+        <v>695.1464190357742</v>
       </c>
       <c r="D22" t="n">
         <v>2.00741e-07</v>
@@ -2334,16 +2244,13 @@
         <v>-24133.75447069373</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.578424228709979e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2147.228739683565</v>
+        <v>485.5655870547551</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000655e-08</v>
+        <v>1.230657342208007e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8254542221389155</v>
+        <v>0.9965610670459207</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2407,7 @@
         <v>2296.259</v>
       </c>
       <c r="C2" t="n">
-        <v>2767.481619554566</v>
+        <v>1073.40534604551</v>
       </c>
       <c r="D2" t="n">
         <v>1.76371e-07</v>
@@ -2533,16 +2440,13 @@
         <v>-33423.4216940086</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.098250106241304e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3120.664929391704</v>
+        <v>414.7867723529997</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000042e-08</v>
+        <v>1.706618578314526e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8167512048500183</v>
+        <v>0.9346277901766484</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2457,7 @@
         <v>2135.695</v>
       </c>
       <c r="C3" t="n">
-        <v>2582.399292919124</v>
+        <v>988.3023816061969</v>
       </c>
       <c r="D3" t="n">
         <v>1.78267e-07</v>
@@ -2586,16 +2490,13 @@
         <v>-32428.9839919529</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.31867104258221e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2965.022094740954</v>
+        <v>436.9855463690911</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000151e-08</v>
+        <v>7.804688817888568e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8171428854042595</v>
+        <v>0.999313683724131</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2507,7 @@
         <v>2095.379</v>
       </c>
       <c r="C4" t="n">
-        <v>2535.981933143532</v>
+        <v>961.9247789629018</v>
       </c>
       <c r="D4" t="n">
         <v>1.78277e-07</v>
@@ -2639,16 +2540,13 @@
         <v>-34518.214625006</v>
       </c>
       <c r="Y4" t="n">
-        <v>177.1211480723434</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3039.279138324308</v>
+        <v>458.5322142392272</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.408723919991782e-08</v>
+        <v>7.959930740303336e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8024963177946208</v>
+        <v>0.9985660965179871</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2557,7 @@
         <v>2056.981</v>
       </c>
       <c r="C5" t="n">
-        <v>2499.49506100792</v>
+        <v>947.0759641780558</v>
       </c>
       <c r="D5" t="n">
         <v>1.78542e-07</v>
@@ -2692,16 +2590,13 @@
         <v>-31987.10972683296</v>
       </c>
       <c r="Y5" t="n">
-        <v>176.2029875329841</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2981.14356315627</v>
+        <v>453.3257374394822</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.429785062539998e-08</v>
+        <v>8.275453320673954e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8015259960473308</v>
+        <v>0.9955407669864429</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2607,7 @@
         <v>2028.168</v>
       </c>
       <c r="C6" t="n">
-        <v>2472.089158229961</v>
+        <v>932.2545448720582</v>
       </c>
       <c r="D6" t="n">
         <v>1.78356e-07</v>
@@ -2745,16 +2640,13 @@
         <v>-32674.38718010858</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.582852024490997e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2837.911472723138</v>
+        <v>470.7812520360396</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>8.657484471179962e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8173622034734879</v>
+        <v>0.9957726722992544</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2657,7 @@
         <v>1997.313</v>
       </c>
       <c r="C7" t="n">
-        <v>2444.476983435881</v>
+        <v>917.8814178077185</v>
       </c>
       <c r="D7" t="n">
         <v>1.78514e-07</v>
@@ -2798,16 +2690,13 @@
         <v>-31411.49473469492</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.027052330947454e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2802.796779623428</v>
+        <v>472.4670647178955</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.00000000000002e-08</v>
+        <v>9.191658203968552e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.81748602223323</v>
+        <v>0.9927043052815471</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2707,7 @@
         <v>1970.152</v>
       </c>
       <c r="C8" t="n">
-        <v>2417.530860315659</v>
+        <v>904.8570563446985</v>
       </c>
       <c r="D8" t="n">
         <v>1.78715e-07</v>
@@ -2851,16 +2740,13 @@
         <v>-31723.44635492421</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.015787469702198e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2768.876023266081</v>
+        <v>496.963288323957</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000159084e-08</v>
+        <v>1.535092629099535e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8176430666296741</v>
+        <v>0.961851136384682</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2757,7 @@
         <v>1933.798</v>
       </c>
       <c r="C9" t="n">
-        <v>2387.038078666194</v>
+        <v>891.5756779459318</v>
       </c>
       <c r="D9" t="n">
         <v>1.78614e-07</v>
@@ -2904,16 +2790,13 @@
         <v>-30185.32181046786</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.414841070470384e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2735.507623836769</v>
+        <v>489.960303925632</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000099752e-08</v>
+        <v>9.139999054633082e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8178295304769163</v>
+        <v>0.9995483004492919</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2807,7 @@
         <v>1916.056</v>
       </c>
       <c r="C10" t="n">
-        <v>2366.946448651923</v>
+        <v>879.9501903330357</v>
       </c>
       <c r="D10" t="n">
         <v>1.78607e-07</v>
@@ -2957,16 +2840,13 @@
         <v>-31338.04713138255</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.117614611909924e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2703.72269973288</v>
+        <v>498.3669069567079</v>
       </c>
       <c r="AA10" t="n">
-        <v>1e-08</v>
+        <v>9.50696644871315e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8180467454064364</v>
+        <v>0.994897321577752</v>
       </c>
     </row>
     <row r="11">
@@ -2977,7 +2857,7 @@
         <v>1882.6</v>
       </c>
       <c r="C11" t="n">
-        <v>2334.931188423901</v>
+        <v>868.1633884631713</v>
       </c>
       <c r="D11" t="n">
         <v>1.78627e-07</v>
@@ -3010,16 +2890,13 @@
         <v>-29864.52036155956</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.363843093238253e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2671.904036300058</v>
+        <v>488.5211456016545</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000042e-08</v>
+        <v>9.152758151364134e-10</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8182950314756228</v>
+        <v>0.9977572213791279</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2907,7 @@
         <v>1863.725</v>
       </c>
       <c r="C12" t="n">
-        <v>2316.328382264959</v>
+        <v>855.8403076634685</v>
       </c>
       <c r="D12" t="n">
         <v>1.78455e-07</v>
@@ -3063,16 +2940,13 @@
         <v>-30800.82457272207</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.803671400167015e-10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2641.506310427568</v>
+        <v>484.3095201487728</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000000008e-08</v>
+        <v>9.913819330696896e-10</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.818551472836228</v>
+        <v>0.9991673594313064</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2957,7 @@
         <v>1834.568</v>
       </c>
       <c r="C13" t="n">
-        <v>2288.008128823943</v>
+        <v>845.6593016682713</v>
       </c>
       <c r="D13" t="n">
         <v>1.78432e-07</v>
@@ -3116,16 +2990,13 @@
         <v>-28701.88478166432</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.552840944951873e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2611.438701930438</v>
+        <v>483.6164780133429</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000001204e-08</v>
+        <v>8.983611613713931e-10</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8188384935621639</v>
+        <v>0.9998926637862544</v>
       </c>
     </row>
     <row r="14">
@@ -3136,7 +3007,7 @@
         <v>1806.722</v>
       </c>
       <c r="C14" t="n">
-        <v>2261.961931595813</v>
+        <v>834.1876899495143</v>
       </c>
       <c r="D14" t="n">
         <v>1.78076e-07</v>
@@ -3169,16 +3040,13 @@
         <v>-28685.03259873531</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.488659556647301e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2582.519623882753</v>
+        <v>492.0642865437497</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000183e-08</v>
+        <v>9.189909003738091e-10</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8191308488972497</v>
+        <v>0.9991281114595457</v>
       </c>
     </row>
     <row r="15">
@@ -3189,7 +3057,7 @@
         <v>1782.123</v>
       </c>
       <c r="C15" t="n">
-        <v>2236.594265495209</v>
+        <v>824.0309141702162</v>
       </c>
       <c r="D15" t="n">
         <v>1.77901e-07</v>
@@ -3222,16 +3090,13 @@
         <v>-28394.66167818223</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.3046240432988e-09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2553.871728548393</v>
+        <v>492.762584991062</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000013776e-08</v>
+        <v>9.724593187273653e-10</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8194319463068017</v>
+        <v>0.9989825623698</v>
       </c>
     </row>
     <row r="16">
@@ -3242,7 +3107,7 @@
         <v>1766.725</v>
       </c>
       <c r="C16" t="n">
-        <v>2222.257767649715</v>
+        <v>814.0894417752774</v>
       </c>
       <c r="D16" t="n">
         <v>1.77859e-07</v>
@@ -3275,16 +3140,13 @@
         <v>-28461.83541249934</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.282230997996266e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2526.138178742537</v>
+        <v>505.519430225513</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000003142e-08</v>
+        <v>9.541805293903058e-10</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8197395374908334</v>
+        <v>0.9950199699935445</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3157,7 @@
         <v>1739.261</v>
       </c>
       <c r="C17" t="n">
-        <v>2195.071520239685</v>
+        <v>803.9405140503578</v>
       </c>
       <c r="D17" t="n">
         <v>1.77748e-07</v>
@@ -3328,16 +3190,13 @@
         <v>-26483.93509906495</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.574439715375114e-11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2499.201143920776</v>
+        <v>500.3563515978099</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>9.74376774294991e-10</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8200444774305483</v>
+        <v>0.9986079440920036</v>
       </c>
     </row>
     <row r="18">
@@ -3348,7 +3207,7 @@
         <v>1719.156</v>
       </c>
       <c r="C18" t="n">
-        <v>2173.805933216641</v>
+        <v>795.5458290979096</v>
       </c>
       <c r="D18" t="n">
         <v>1.77596e-07</v>
@@ -3381,16 +3240,13 @@
         <v>-27191.33839576717</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.634196782120349e-10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2472.918314070274</v>
+        <v>504.5159586046943</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000825e-08</v>
+        <v>1.054997913097945e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8203547809949402</v>
+        <v>0.9989483960702272</v>
       </c>
     </row>
     <row r="19">
@@ -3401,7 +3257,7 @@
         <v>1697.681</v>
       </c>
       <c r="C19" t="n">
-        <v>2153.698610262876</v>
+        <v>785.4843101320695</v>
       </c>
       <c r="D19" t="n">
         <v>1.77453e-07</v>
@@ -3434,16 +3290,13 @@
         <v>-25897.57203092706</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.82262901452101e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2446.808083731452</v>
+        <v>514.5864863845248</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000741e-08</v>
+        <v>1.120920744634509e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.820672922691858</v>
+        <v>0.9933665434847897</v>
       </c>
     </row>
     <row r="20">
@@ -3454,7 +3307,7 @@
         <v>1683.348</v>
       </c>
       <c r="C20" t="n">
-        <v>2137.701149432174</v>
+        <v>777.1910350543145</v>
       </c>
       <c r="D20" t="n">
         <v>1.77162e-07</v>
@@ -3487,16 +3340,13 @@
         <v>-26556.73841351583</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.361737835006235e-10</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2421.562315616129</v>
+        <v>502.5209222264857</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000005e-08</v>
+        <v>1.00624582207808e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8209825486897392</v>
+        <v>0.9996614793346088</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3357,7 @@
         <v>1659.877</v>
       </c>
       <c r="C21" t="n">
-        <v>2113.079460492747</v>
+        <v>768.3120162478648</v>
       </c>
       <c r="D21" t="n">
         <v>1.77016e-07</v>
@@ -3540,16 +3390,13 @@
         <v>-25706.5580828153</v>
       </c>
       <c r="Y21" t="n">
-        <v>7.639996898130592e-12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2396.115690016146</v>
+        <v>499.3789423116834</v>
       </c>
       <c r="AA21" t="n">
-        <v>1e-08</v>
+        <v>1.096810954589e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.821309181071586</v>
+        <v>0.9947734719409419</v>
       </c>
     </row>
     <row r="22">
@@ -3560,7 +3407,7 @@
         <v>1635.382</v>
       </c>
       <c r="C22" t="n">
-        <v>2089.876805188434</v>
+        <v>759.9351601260066</v>
       </c>
       <c r="D22" t="n">
         <v>1.77114e-07</v>
@@ -3593,16 +3440,13 @@
         <v>-23581.44735841637</v>
       </c>
       <c r="Y22" t="n">
-        <v>9.386260832158776e-10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2370.972297857967</v>
+        <v>500.9359488944419</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000001279e-08</v>
+        <v>1.059564561331236e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8216299238500708</v>
+        <v>0.9966617291995471</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3603,7 @@
         <v>2055.368</v>
       </c>
       <c r="C2" t="n">
-        <v>2652.611683478858</v>
+        <v>1083.464418427791</v>
       </c>
       <c r="D2" t="n">
         <v>1.79691e-07</v>
@@ -3792,16 +3636,13 @@
         <v>-22726.48146502904</v>
       </c>
       <c r="Y2" t="n">
-        <v>161.2417281774964</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2997.753554063162</v>
+        <v>369.1923300782354</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.988846993442448e-08</v>
+        <v>1.247870500450246e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7747497912492826</v>
+        <v>0.9539053425965391</v>
       </c>
     </row>
     <row r="3">
@@ -3812,7 +3653,7 @@
         <v>1749.25</v>
       </c>
       <c r="C3" t="n">
-        <v>2264.066556795311</v>
+        <v>850.8264910612854</v>
       </c>
       <c r="D3" t="n">
         <v>1.86279e-07</v>
@@ -3845,16 +3686,13 @@
         <v>-27597.76330893855</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.944598466089181e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2541.080020887905</v>
+        <v>519.0554920990119</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000079e-08</v>
+        <v>1.56524409785152e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8157461941399734</v>
+        <v>0.9610959813285405</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3703,7 @@
         <v>1674.421</v>
       </c>
       <c r="C4" t="n">
-        <v>2179.190813969196</v>
+        <v>801.356394716214</v>
       </c>
       <c r="D4" t="n">
         <v>1.8711e-07</v>
@@ -3898,16 +3736,13 @@
         <v>-30499.42147381005</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.339634416928426e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2457.190193690232</v>
+        <v>529.9998724173651</v>
       </c>
       <c r="AA4" t="n">
-        <v>1e-08</v>
+        <v>1.03451720797111e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8158701634296962</v>
+        <v>0.995013013187198</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3753,7 @@
         <v>1620.014</v>
       </c>
       <c r="C5" t="n">
-        <v>2127.643999852218</v>
+        <v>779.760146134113</v>
       </c>
       <c r="D5" t="n">
         <v>1.8701e-07</v>
@@ -3951,16 +3786,13 @@
         <v>-28740.96151745195</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.141607515479345e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2411.008026712254</v>
+        <v>542.6303957002762</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000068516e-08</v>
+        <v>1.005775268091941e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.815882302457436</v>
+        <v>0.9999776065645677</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3803,7 @@
         <v>1592.746</v>
       </c>
       <c r="C6" t="n">
-        <v>2103.036253573521</v>
+        <v>763.1452967129345</v>
       </c>
       <c r="D6" t="n">
         <v>1.87345e-07</v>
@@ -4004,16 +3836,13 @@
         <v>-30139.68816408904</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.784582872436847e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2370.845084032311</v>
+        <v>563.4363545917554</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000003383e-08</v>
+        <v>1.715076157547092e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8158760916433044</v>
+        <v>0.9669391330060609</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3853,7 @@
         <v>1560.177</v>
       </c>
       <c r="C7" t="n">
-        <v>2073.687472824779</v>
+        <v>748.6748501195227</v>
       </c>
       <c r="D7" t="n">
         <v>1.87595e-07</v>
@@ -4057,16 +3886,13 @@
         <v>-30131.40489930597</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.78173516126112e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2335.636458354546</v>
+        <v>588.7189550490334</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000749e-08</v>
+        <v>2.354091844186129e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8159179511372353</v>
+        <v>0.9501344682944294</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3903,7 @@
         <v>1527.535</v>
       </c>
       <c r="C8" t="n">
-        <v>2044.473473153196</v>
+        <v>737.2003234005493</v>
       </c>
       <c r="D8" t="n">
         <v>1.87763e-07</v>
@@ -4110,16 +3936,13 @@
         <v>-29114.33606285213</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.493521025855163e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2303.725336890074</v>
+        <v>550.4960953629287</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000021807e-08</v>
+        <v>1.027954665271354e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8159718830446999</v>
+        <v>0.9996032029083252</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3953,7 @@
         <v>1503.321</v>
       </c>
       <c r="C9" t="n">
-        <v>2020.465082799839</v>
+        <v>727.5099698213635</v>
       </c>
       <c r="D9" t="n">
         <v>1.87885e-07</v>
@@ -4163,16 +3986,13 @@
         <v>-29316.09885609434</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.349852838923336e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2273.865132145196</v>
+        <v>566.3730969931272</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>1.173518205974143e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8160623225976936</v>
+        <v>0.9992195353921139</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4003,7 @@
         <v>1479.373</v>
       </c>
       <c r="C10" t="n">
-        <v>1999.617652474425</v>
+        <v>719.5004176453912</v>
       </c>
       <c r="D10" t="n">
         <v>1.88043e-07</v>
@@ -4216,16 +4036,13 @@
         <v>-29292.31176746068</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.415840859719032e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2246.633628514866</v>
+        <v>567.8474214033062</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000001037e-08</v>
+        <v>1.285283992421158e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8161684121207439</v>
+        <v>0.9885985685750636</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4053,7 @@
         <v>1458.328</v>
       </c>
       <c r="C11" t="n">
-        <v>1978.833045984886</v>
+        <v>1333.215844395835</v>
       </c>
       <c r="D11" t="n">
         <v>1.88263e-07</v>
@@ -4269,16 +4086,13 @@
         <v>-29049.92704982174</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.662693213914232e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2221.753564947094</v>
+        <v>3.083474990054915</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000021e-08</v>
+        <v>2.478840718154098e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8163150548366694</v>
+        <v>0.8747089699165976</v>
       </c>
     </row>
   </sheetData>
@@ -4435,7 +4249,7 @@
         <v>2109.609</v>
       </c>
       <c r="C2" t="n">
-        <v>2566.457828555054</v>
+        <v>992.2807324956339</v>
       </c>
       <c r="D2" t="n">
         <v>1.80582e-07</v>
@@ -4468,16 +4282,13 @@
         <v>-31764.89629019741</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.747300497441216e-11</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2907.479074605734</v>
+        <v>474.3905656292795</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000113e-08</v>
+        <v>2.102718807900267e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8187223477313514</v>
+        <v>0.9365321090384376</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4299,7 @@
         <v>2004.165</v>
       </c>
       <c r="C3" t="n">
-        <v>2441.970338644355</v>
+        <v>925.0412703011408</v>
       </c>
       <c r="D3" t="n">
         <v>1.82804e-07</v>
@@ -4521,16 +4332,13 @@
         <v>-32504.48179644905</v>
       </c>
       <c r="Y3" t="n">
-        <v>168.5195265035647</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2889.556619265637</v>
+        <v>450.4354794864075</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.445891583989431e-08</v>
+        <v>8.876154214053475e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8020592143047403</v>
+        <v>0.995607431160708</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4349,7 @@
         <v>1954.573</v>
       </c>
       <c r="C4" t="n">
-        <v>2393.271221472365</v>
+        <v>897.3442830647947</v>
       </c>
       <c r="D4" t="n">
         <v>1.83893e-07</v>
@@ -4574,16 +4382,13 @@
         <v>-31977.71335055447</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.555493351899843e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2740.841542456011</v>
+        <v>477.6770039491474</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000084496e-08</v>
+        <v>9.756658805441304e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.819043599687526</v>
+        <v>0.9865097717688528</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4399,7 @@
         <v>1932.932</v>
       </c>
       <c r="C5" t="n">
-        <v>2368.29517136367</v>
+        <v>881.6152809051744</v>
       </c>
       <c r="D5" t="n">
         <v>1.8475e-07</v>
@@ -4627,16 +4432,13 @@
         <v>-33338.50338005289</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.342753719515469e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2703.782377099914</v>
+        <v>473.3116404831158</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000074021e-08</v>
+        <v>1.113736445601003e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8190909559437562</v>
+        <v>0.9814608765254016</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4449,7 @@
         <v>1894.38</v>
       </c>
       <c r="C6" t="n">
-        <v>2337.283902193636</v>
+        <v>868.6752232809606</v>
       </c>
       <c r="D6" t="n">
         <v>1.85466e-07</v>
@@ -4680,16 +4482,13 @@
         <v>-31008.47685392185</v>
       </c>
       <c r="Y6" t="n">
-        <v>176.4817727525122</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2746.685211094529</v>
+        <v>482.7472470129874</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.41996735244995e-08</v>
+        <v>8.91200637706705e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8046711866808292</v>
+        <v>0.99258922594298</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4499,7 @@
         <v>1862.599</v>
       </c>
       <c r="C7" t="n">
-        <v>2306.377750178047</v>
+        <v>857.7040084603435</v>
       </c>
       <c r="D7" t="n">
         <v>1.85812e-07</v>
@@ -4733,16 +4532,13 @@
         <v>-29947.1649625958</v>
       </c>
       <c r="Y7" t="n">
-        <v>178.0211361878237</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2726.024493861719</v>
+        <v>483.1837490394695</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.458498066863573e-08</v>
+        <v>9.75612433339423e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8031980694926291</v>
+        <v>0.9965756794204902</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4549,7 @@
         <v>1829.782</v>
       </c>
       <c r="C8" t="n">
-        <v>2276.92218542719</v>
+        <v>845.1361783986555</v>
       </c>
       <c r="D8" t="n">
         <v>1.86224e-07</v>
@@ -4786,16 +4582,13 @@
         <v>-27979.73269080841</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.779085770779615e-11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2608.177857410929</v>
+        <v>490.4294537801966</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000017e-08</v>
+        <v>9.23897873976043e-10</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8196074959740213</v>
+        <v>0.9950119404215859</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4599,7 @@
         <v>1813.049</v>
       </c>
       <c r="C9" t="n">
-        <v>2258.937578484088</v>
+        <v>835.483797656498</v>
       </c>
       <c r="D9" t="n">
         <v>1.86793e-07</v>
@@ -4839,16 +4632,13 @@
         <v>-28766.31773061886</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.655100104717447e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2578.616719393352</v>
+        <v>470.7316203150272</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000029e-08</v>
+        <v>8.516097487796143e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8198317936240599</v>
+        <v>0.9995019273375015</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4649,7 @@
         <v>1791.775</v>
       </c>
       <c r="C10" t="n">
-        <v>2236.002473812734</v>
+        <v>824.9337916569077</v>
       </c>
       <c r="D10" t="n">
         <v>1.87002e-07</v>
@@ -4892,16 +4682,13 @@
         <v>-28756.07535024081</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.091953517026953e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2550.114354591583</v>
+        <v>478.0098049067686</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000534e-08</v>
+        <v>9.592721296744305e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8201092857635204</v>
+        <v>0.9983112427676485</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4699,7 @@
         <v>1771.164</v>
       </c>
       <c r="C11" t="n">
-        <v>2212.324578166099</v>
+        <v>815.0013031270754</v>
       </c>
       <c r="D11" t="n">
         <v>1.87396e-07</v>
@@ -4945,16 +4732,13 @@
         <v>-27684.93709289018</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.62909506396634e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2522.540919444169</v>
+        <v>491.5411591865667</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>1.043183085002276e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8204279121052407</v>
+        <v>0.9936505581309362</v>
       </c>
     </row>
     <row r="12">
@@ -4965,7 +4749,7 @@
         <v>1747.663</v>
       </c>
       <c r="C12" t="n">
-        <v>2191.949889980789</v>
+        <v>804.4853866395422</v>
       </c>
       <c r="D12" t="n">
         <v>1.87648e-07</v>
@@ -4998,16 +4782,13 @@
         <v>-28123.70963899793</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.987472430098682e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2493.047171116554</v>
+        <v>497.319804350214</v>
       </c>
       <c r="AA12" t="n">
-        <v>1e-08</v>
+        <v>1.07448798747022e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8208081807839711</v>
+        <v>0.9958038723141945</v>
       </c>
     </row>
     <row r="13">
@@ -5018,7 +4799,7 @@
         <v>1724.264</v>
       </c>
       <c r="C13" t="n">
-        <v>2166.857486197992</v>
+        <v>794.9755907980704</v>
       </c>
       <c r="D13" t="n">
         <v>1.88127e-07</v>
@@ -5051,16 +4832,13 @@
         <v>-26980.1496763315</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.393343331997727e-10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2463.337570982736</v>
+        <v>481.7744703270318</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000125e-08</v>
+        <v>9.483993504108736e-10</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8211641342548746</v>
+        <v>0.9989832453723658</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4849,7 @@
         <v>1700.635</v>
       </c>
       <c r="C14" t="n">
-        <v>2146.104086115552</v>
+        <v>783.2349961809293</v>
       </c>
       <c r="D14" t="n">
         <v>1.88564e-07</v>
@@ -5104,16 +4882,13 @@
         <v>-26126.30703645421</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.434777164258078e-11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2434.584296388062</v>
+        <v>490.1333063996733</v>
       </c>
       <c r="AA14" t="n">
-        <v>1e-08</v>
+        <v>1.028238578149965e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8215384419511169</v>
+        <v>0.9986138956611496</v>
       </c>
     </row>
     <row r="15">
@@ -5124,7 +4899,7 @@
         <v>1679.72</v>
       </c>
       <c r="C15" t="n">
-        <v>2121.846854622285</v>
+        <v>773.7227101007618</v>
       </c>
       <c r="D15" t="n">
         <v>1.88678e-07</v>
@@ -5157,16 +4932,13 @@
         <v>-26558.86995910022</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.684336146384152e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2405.335203949656</v>
+        <v>495.3371826510996</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000027e-08</v>
+        <v>1.097370789250814e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8219147047866441</v>
+        <v>0.9995868171463097</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4949,7 @@
         <v>1659.648</v>
       </c>
       <c r="C16" t="n">
-        <v>2098.258564823981</v>
+        <v>764.4005413079014</v>
       </c>
       <c r="D16" t="n">
         <v>1.88925e-07</v>
@@ -5210,16 +4982,13 @@
         <v>-26767.35432003055</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.807164635943636e-12</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2377.324128530602</v>
+        <v>479.7855726426115</v>
       </c>
       <c r="AA16" t="n">
-        <v>1e-08</v>
+        <v>9.513279771430987e-10</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8222964029961314</v>
+        <v>0.9999604488560495</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +4999,7 @@
         <v>1637.082</v>
       </c>
       <c r="C17" t="n">
-        <v>2076.771142898563</v>
+        <v>754.8488624207514</v>
       </c>
       <c r="D17" t="n">
         <v>1.89484e-07</v>
@@ -5263,16 +5032,13 @@
         <v>-25383.43886330936</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.054322738713438e-12</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2348.931582503353</v>
+        <v>492.9826480438506</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000006e-08</v>
+        <v>1.22315207790207e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8226889203609115</v>
+        <v>0.9881151163277533</v>
       </c>
     </row>
     <row r="18">
@@ -5283,7 +5049,7 @@
         <v>1615.956</v>
       </c>
       <c r="C18" t="n">
-        <v>2055.027266979027</v>
+        <v>746.6767782824048</v>
       </c>
       <c r="D18" t="n">
         <v>1.89727e-07</v>
@@ -5316,16 +5082,13 @@
         <v>-24497.48739716551</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.866706578933825e-09</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2320.472602728526</v>
+        <v>491.8464540898343</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000008e-08</v>
+        <v>1.130597033468783e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8231048157835914</v>
+        <v>0.9964607473523918</v>
       </c>
     </row>
     <row r="19">
@@ -5336,7 +5099,7 @@
         <v>1587.141</v>
       </c>
       <c r="C19" t="n">
-        <v>2028.656706785446</v>
+        <v>737.1221781987973</v>
       </c>
       <c r="D19" t="n">
         <v>1.89987e-07</v>
@@ -5369,16 +5132,13 @@
         <v>-23498.40669568294</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.70225681349418e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2293.723643250007</v>
+        <v>497.410548604123</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000010132e-08</v>
+        <v>1.222505182753026e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8234896453865895</v>
+        <v>0.99154592641759</v>
       </c>
     </row>
     <row r="20">
@@ -5389,7 +5149,7 @@
         <v>1565.966</v>
       </c>
       <c r="C20" t="n">
-        <v>2005.845559730371</v>
+        <v>728.2906693587209</v>
       </c>
       <c r="D20" t="n">
         <v>1.90312e-07</v>
@@ -5422,16 +5182,13 @@
         <v>-22083.13348589925</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.210396138398304e-09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2265.475399808963</v>
+        <v>498.6468089265232</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000019e-08</v>
+        <v>1.164906390693688e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8238958024119492</v>
+        <v>0.9964536824744427</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5199,7 @@
         <v>1552.813</v>
       </c>
       <c r="C21" t="n">
-        <v>1989.903047368714</v>
+        <v>719.96280303111</v>
       </c>
       <c r="D21" t="n">
         <v>1.9041e-07</v>
@@ -5475,16 +5232,13 @@
         <v>-23353.09673975293</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.33699942704002e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2237.606985131801</v>
+        <v>497.4132294404153</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000001356e-08</v>
+        <v>1.245810443995778e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8243226703090486</v>
+        <v>0.9914854871326636</v>
       </c>
     </row>
     <row r="22">
@@ -5495,7 +5249,7 @@
         <v>1529.684</v>
       </c>
       <c r="C22" t="n">
-        <v>1966.252372203238</v>
+        <v>710.6772414580184</v>
       </c>
       <c r="D22" t="n">
         <v>1.90786e-07</v>
@@ -5528,16 +5282,13 @@
         <v>-22753.88532271128</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.239735727126652e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2209.97942875963</v>
+        <v>488.6569871166131</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000001243e-08</v>
+        <v>1.188033603485214e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8247433108567596</v>
+        <v>0.994133601140668</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5445,7 @@
         <v>2145.244</v>
       </c>
       <c r="C2" t="n">
-        <v>2717.564994895205</v>
+        <v>1471.272118811122</v>
       </c>
       <c r="D2" t="n">
         <v>1.76943e-07</v>
@@ -5727,16 +5478,13 @@
         <v>-22565.89730244199</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.669308107439065e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2898.531356320102</v>
+        <v>7.16568196666651</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000001478e-08</v>
+        <v>1.871234641773068e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8190025675869466</v>
+        <v>0.8922821697453025</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5495,7 @@
         <v>1804.357</v>
       </c>
       <c r="C3" t="n">
-        <v>2283.147365066457</v>
+        <v>859.6517774101522</v>
       </c>
       <c r="D3" t="n">
         <v>1.84077e-07</v>
@@ -5780,16 +5528,13 @@
         <v>-29408.65401258625</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.03126867934202e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2556.597060659346</v>
+        <v>464.3506271814567</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000111e-08</v>
+        <v>1.013466997112486e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8199216917217894</v>
+        <v>0.9863750849994375</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5545,7 @@
         <v>1710.582</v>
       </c>
       <c r="C4" t="n">
-        <v>2177.390011964691</v>
+        <v>810.4746069223406</v>
       </c>
       <c r="D4" t="n">
         <v>1.85184e-07</v>
@@ -5833,16 +5578,13 @@
         <v>-29583.93365675751</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.061974822504213e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2467.008602312186</v>
+        <v>485.1730571685194</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000025e-08</v>
+        <v>1.302283282822179e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8200960150288892</v>
+        <v>0.9850504367103818</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5595,7 @@
         <v>1671.218</v>
       </c>
       <c r="C5" t="n">
-        <v>2138.222782543589</v>
+        <v>790.1232126097572</v>
       </c>
       <c r="D5" t="n">
         <v>1.85759e-07</v>
@@ -5886,16 +5628,13 @@
         <v>-29678.09452322549</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.629535078081057e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2422.043207017894</v>
+        <v>496.7567135220285</v>
       </c>
       <c r="AA5" t="n">
-        <v>1e-08</v>
+        <v>9.512205541820202e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8201782845207977</v>
+        <v>0.9998744779148099</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5645,7 @@
         <v>1648.205</v>
       </c>
       <c r="C6" t="n">
-        <v>2112.526259575811</v>
+        <v>772.9993961476116</v>
       </c>
       <c r="D6" t="n">
         <v>1.85986e-07</v>
@@ -5939,16 +5678,13 @@
         <v>-31154.37288865895</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.990938932229572e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2385.792369250469</v>
+        <v>510.2414840859927</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000008783e-08</v>
+        <v>1.095789939240374e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8203024432975681</v>
+        <v>0.9951860277066019</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5695,7 @@
         <v>1600.842</v>
       </c>
       <c r="C7" t="n">
-        <v>2073.77550909039</v>
+        <v>760.7164526635735</v>
       </c>
       <c r="D7" t="n">
         <v>1.86409e-07</v>
@@ -5992,16 +5728,13 @@
         <v>-27596.06716754378</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.129356743279167e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2351.902489905589</v>
+        <v>508.9502650626966</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000007e-08</v>
+        <v>1.123482896407329e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8204542884825974</v>
+        <v>0.9939302068312214</v>
       </c>
     </row>
     <row r="8">
@@ -6012,7 +5745,7 @@
         <v>1586.441</v>
       </c>
       <c r="C8" t="n">
-        <v>2055.369711888345</v>
+        <v>749.3414205927178</v>
       </c>
       <c r="D8" t="n">
         <v>1.86455e-07</v>
@@ -6045,16 +5778,13 @@
         <v>-30018.07600164873</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.382791105745357e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2318.745722138486</v>
+        <v>505.8507784235541</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000131e-08</v>
+        <v>1.040224690945059e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8206460909902948</v>
+        <v>0.999700431303531</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5795,7 @@
         <v>1557.725</v>
       </c>
       <c r="C9" t="n">
-        <v>2029.460098808713</v>
+        <v>736.143716079899</v>
       </c>
       <c r="D9" t="n">
         <v>1.86925e-07</v>
@@ -6098,16 +5828,13 @@
         <v>-29550.90375437156</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.719626855767721e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2286.064416655111</v>
+        <v>522.3438842023299</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>1.183794077282299e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8208424885399236</v>
+        <v>0.9952444736271645</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5845,7 @@
         <v>1522.092</v>
       </c>
       <c r="C10" t="n">
-        <v>1996.123038045879</v>
+        <v>726.0133274980298</v>
       </c>
       <c r="D10" t="n">
         <v>1.87132e-07</v>
@@ -6151,16 +5878,13 @@
         <v>-27340.36124166657</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.08760428912035e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2254.315818047912</v>
+        <v>508.2807544589886</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000032e-08</v>
+        <v>1.361800178378256e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8210697152121067</v>
+        <v>0.9873796559068413</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5895,7 @@
         <v>1502.414</v>
       </c>
       <c r="C11" t="n">
-        <v>1977.252821410763</v>
+        <v>716.822077507831</v>
       </c>
       <c r="D11" t="n">
         <v>1.87239e-07</v>
@@ -6204,16 +5928,13 @@
         <v>-28871.0837201775</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.166191682446323e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2224.310126700585</v>
+        <v>517.0460445827583</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000001448e-08</v>
+        <v>1.123379114871775e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8213032005508728</v>
+        <v>0.998682405248852</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6091,7 @@
         <v>2164.259</v>
       </c>
       <c r="C2" t="n">
-        <v>2615.042423759553</v>
+        <v>1037.219665721289</v>
       </c>
       <c r="D2" t="n">
         <v>1.79463e-07</v>
@@ -6403,16 +6124,13 @@
         <v>-30621.82678766628</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.297076168366234e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2968.891507117198</v>
+        <v>395.6403830934048</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000048e-08</v>
+        <v>1.135681110777725e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.818931396280973</v>
+        <v>0.9703139843213445</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6141,7 @@
         <v>2069.956</v>
       </c>
       <c r="C3" t="n">
-        <v>2500.482359148224</v>
+        <v>965.38898852733</v>
       </c>
       <c r="D3" t="n">
         <v>1.80846e-07</v>
@@ -6456,16 +6174,13 @@
         <v>-34279.09277141315</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.568459738348793e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2861.859134141609</v>
+        <v>401.8666025669112</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000018728e-08</v>
+        <v>9.612684961935492e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8192054736333529</v>
+        <v>0.9884728625095356</v>
       </c>
     </row>
     <row r="4">
@@ -6476,7 +6191,7 @@
         <v>2029.286</v>
       </c>
       <c r="C4" t="n">
-        <v>2455.973236641828</v>
+        <v>939.2291287874627</v>
       </c>
       <c r="D4" t="n">
         <v>1.81489e-07</v>
@@ -6509,16 +6224,13 @@
         <v>-34513.32611334425</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.875781802845816e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2814.340182505431</v>
+        <v>432.9550887826145</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>9.883339460564109e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8193239749030816</v>
+        <v>0.9829692669503133</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6241,7 @@
         <v>1988.22</v>
       </c>
       <c r="C5" t="n">
-        <v>2420.142799335162</v>
+        <v>920.4909657080984</v>
       </c>
       <c r="D5" t="n">
         <v>1.82214e-07</v>
@@ -6562,16 +6274,13 @@
         <v>-32476.83126192831</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.447210733315941e-12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2777.40156528471</v>
+        <v>451.1623308189176</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000003147e-08</v>
+        <v>1.168651215416865e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8193876311862822</v>
+        <v>0.9829921611997852</v>
       </c>
     </row>
     <row r="6">
@@ -6582,7 +6291,7 @@
         <v>1961.517</v>
       </c>
       <c r="C6" t="n">
-        <v>2394.114206196847</v>
+        <v>902.8152496646982</v>
       </c>
       <c r="D6" t="n">
         <v>1.82776e-07</v>
@@ -6615,16 +6324,13 @@
         <v>-32186.55168588873</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.433992573529441e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2743.957567616646</v>
+        <v>457.1496139777062</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000005e-08</v>
+        <v>9.932477506330386e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8194662589336773</v>
+        <v>0.9873494551183715</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6341,7 @@
         <v>1934.235</v>
       </c>
       <c r="C7" t="n">
-        <v>2369.692124176571</v>
+        <v>890.0950875845809</v>
       </c>
       <c r="D7" t="n">
         <v>1.83007e-07</v>
@@ -6668,16 +6374,13 @@
         <v>-32270.01974311587</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.579990235952119e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2713.596310572661</v>
+        <v>464.367760552249</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000156968e-08</v>
+        <v>9.530886508143908e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8195668929104341</v>
+        <v>0.9856667084531565</v>
       </c>
     </row>
     <row r="8">
@@ -6688,7 +6391,7 @@
         <v>1902.703</v>
       </c>
       <c r="C8" t="n">
-        <v>2344.196598059812</v>
+        <v>878.5017073696847</v>
       </c>
       <c r="D8" t="n">
         <v>1.83257e-07</v>
@@ -6721,16 +6424,13 @@
         <v>-30808.79912314165</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.218697654527602e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2685.741271748901</v>
+        <v>469.259579878555</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000116112e-08</v>
+        <v>9.024272323948269e-10</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8196825558247631</v>
+        <v>0.9985709411300788</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6441,7 @@
         <v>1881.206</v>
       </c>
       <c r="C9" t="n">
-        <v>2320.817710551393</v>
+        <v>867.3882604464</v>
       </c>
       <c r="D9" t="n">
         <v>1.83615e-07</v>
@@ -6774,16 +6474,13 @@
         <v>-30546.62388083949</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.479441224105351e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2658.180877920011</v>
+        <v>478.3197583662477</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.00000000000071e-08</v>
+        <v>9.062844031079818e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8198505988660719</v>
+        <v>0.9985062689887372</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6491,7 @@
         <v>1854.214</v>
       </c>
       <c r="C10" t="n">
-        <v>2296.210351620853</v>
+        <v>857.2699073283629</v>
       </c>
       <c r="D10" t="n">
         <v>1.83892e-07</v>
@@ -6827,16 +6524,13 @@
         <v>-28941.91113499524</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.380012355386828e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2631.183480824692</v>
+        <v>472.3044120652549</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000012889e-08</v>
+        <v>9.529152858851178e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8200813779813744</v>
+        <v>0.9994459870008403</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6541,7 @@
         <v>1841.019</v>
       </c>
       <c r="C11" t="n">
-        <v>2277.764147138912</v>
+        <v>847.4883979769094</v>
       </c>
       <c r="D11" t="n">
         <v>1.84195e-07</v>
@@ -6880,16 +6574,13 @@
         <v>-30427.58664542211</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.303005940359943e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2603.979594122613</v>
+        <v>480.0016692225964</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000039895e-08</v>
+        <v>1.117462720488432e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.82035353547412</v>
+        <v>0.9860721529925507</v>
       </c>
     </row>
     <row r="12">
@@ -6900,7 +6591,7 @@
         <v>1813.612</v>
       </c>
       <c r="C12" t="n">
-        <v>2252.857224841983</v>
+        <v>837.8679688455234</v>
       </c>
       <c r="D12" t="n">
         <v>1.84343e-07</v>
@@ -6933,16 +6624,13 @@
         <v>-29298.80621146221</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.344160738297588e-12</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2577.717880925443</v>
+        <v>479.316832728725</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000002961e-08</v>
+        <v>9.817601515611863e-10</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8206536807278236</v>
+        <v>0.9963285398216245</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6641,7 @@
         <v>1791.995</v>
       </c>
       <c r="C13" t="n">
-        <v>2232.85959785229</v>
+        <v>828.1408286950661</v>
       </c>
       <c r="D13" t="n">
         <v>1.84847e-07</v>
@@ -6986,16 +6674,13 @@
         <v>-29107.36544144287</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.60985710614627e-18</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2550.833724812115</v>
+        <v>476.0515666586744</v>
       </c>
       <c r="AA13" t="n">
-        <v>1e-08</v>
+        <v>9.594315446787119e-10</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8209732842270187</v>
+        <v>0.9994660109295094</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6691,7 @@
         <v>1779.061</v>
       </c>
       <c r="C14" t="n">
-        <v>2215.694125556464</v>
+        <v>818.3059429984502</v>
       </c>
       <c r="D14" t="n">
         <v>1.8497e-07</v>
@@ -7039,16 +6724,13 @@
         <v>-29948.80514446605</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.883939939052494e-10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2523.973641391239</v>
+        <v>475.9551862848365</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000010549e-08</v>
+        <v>9.764072085670752e-10</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8212867731213296</v>
+        <v>0.9961932260315317</v>
       </c>
     </row>
     <row r="15">
@@ -7059,7 +6741,7 @@
         <v>1763.477</v>
       </c>
       <c r="C15" t="n">
-        <v>2199.651920674664</v>
+        <v>809.3445739526372</v>
       </c>
       <c r="D15" t="n">
         <v>1.85395e-07</v>
@@ -7092,16 +6774,13 @@
         <v>-30744.11453532423</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.502981915748685e-08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2497.596764095284</v>
+        <v>475.3040212293569</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000210954e-08</v>
+        <v>1.016773329343467e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8216267671235367</v>
+        <v>0.9961618596326339</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6791,7 @@
         <v>1743.803</v>
       </c>
       <c r="C16" t="n">
-        <v>2178.858437222986</v>
+        <v>800.051740287213</v>
       </c>
       <c r="D16" t="n">
         <v>1.85489e-07</v>
@@ -7145,16 +6824,13 @@
         <v>-30783.16612355501</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.583345736296063e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2472.138018937787</v>
+        <v>474.9936055235584</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000263e-08</v>
+        <v>1.006433885883926e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8219592530084373</v>
+        <v>0.9965962401742681</v>
       </c>
     </row>
     <row r="17">
@@ -7165,7 +6841,7 @@
         <v>1708.144</v>
       </c>
       <c r="C17" t="n">
-        <v>2149.082797839986</v>
+        <v>790.5991278235053</v>
       </c>
       <c r="D17" t="n">
         <v>1.85835e-07</v>
@@ -7198,16 +6874,13 @@
         <v>-27650.59457274326</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.076491277200882e-10</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2446.151413445513</v>
+        <v>471.7898225230245</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000042e-08</v>
+        <v>9.793906394411779e-10</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8222949768213919</v>
+        <v>0.9999325502958565</v>
       </c>
     </row>
     <row r="18">
@@ -7218,7 +6891,7 @@
         <v>1697.884</v>
       </c>
       <c r="C18" t="n">
-        <v>2133.928302754755</v>
+        <v>782.040353676026</v>
       </c>
       <c r="D18" t="n">
         <v>1.8599e-07</v>
@@ -7251,16 +6924,13 @@
         <v>-28482.02510896072</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.786965320502517e-09</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2420.467735693825</v>
+        <v>492.0848874918357</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000001139e-08</v>
+        <v>1.107174064805114e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8226282779471028</v>
+        <v>0.9926166035968373</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +6941,7 @@
         <v>1670.326</v>
       </c>
       <c r="C19" t="n">
-        <v>2109.304827429291</v>
+        <v>773.4594493520667</v>
       </c>
       <c r="D19" t="n">
         <v>1.8624e-07</v>
@@ -7304,16 +6974,13 @@
         <v>-27841.27747218926</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.728071149661126e-11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2395.345596222047</v>
+        <v>467.9890286639154</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000271e-08</v>
+        <v>9.52735643163163e-10</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8229619698113428</v>
+        <v>0.9987436026187907</v>
       </c>
     </row>
     <row r="20">
@@ -7324,7 +6991,7 @@
         <v>1662.175</v>
       </c>
       <c r="C20" t="n">
-        <v>2097.502806155587</v>
+        <v>764.3689632986157</v>
       </c>
       <c r="D20" t="n">
         <v>1.86512e-07</v>
@@ -7357,16 +7024,13 @@
         <v>-29578.20759198589</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.151201381785353e-09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2369.931667734592</v>
+        <v>494.3273651918614</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000026403e-08</v>
+        <v>1.27660601977224e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8233047208738283</v>
+        <v>0.9902311141755294</v>
       </c>
     </row>
     <row r="21">
@@ -7377,7 +7041,7 @@
         <v>1626.797</v>
       </c>
       <c r="C21" t="n">
-        <v>2067.010977353736</v>
+        <v>756.183788072409</v>
       </c>
       <c r="D21" t="n">
         <v>1.86723e-07</v>
@@ -7410,16 +7074,13 @@
         <v>-26252.44812079285</v>
       </c>
       <c r="Y21" t="n">
-        <v>90.94930141049421</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2331.396859334923</v>
+        <v>487.3514238797298</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.277275645378917e-08</v>
+        <v>1.609032414265062e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8104542054928779</v>
+        <v>0.976172392182437</v>
       </c>
     </row>
     <row r="22">
@@ -7430,7 +7091,7 @@
         <v>1619.644</v>
       </c>
       <c r="C22" t="n">
-        <v>2053.956968870594</v>
+        <v>748.1948918892848</v>
       </c>
       <c r="D22" t="n">
         <v>1.87046e-07</v>
@@ -7463,16 +7124,13 @@
         <v>-28367.55741277962</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.338455413330206e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2319.952965833445</v>
+        <v>476.7366515127636</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000194e-08</v>
+        <v>1.081790800867693e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8239873823820093</v>
+        <v>0.9990400747314945</v>
       </c>
     </row>
   </sheetData>
@@ -7629,7 +7287,7 @@
         <v>1988.348</v>
       </c>
       <c r="C2" t="n">
-        <v>2573.669666254917</v>
+        <v>1041.28711958872</v>
       </c>
       <c r="D2" t="n">
         <v>1.85436e-07</v>
@@ -7662,16 +7320,13 @@
         <v>-21553.65571513454</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.039085601399273e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2726.946789323578</v>
+        <v>310.8126898559482</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.00000000000027e-08</v>
+        <v>8.701387369644992e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8179473813783887</v>
+        <v>0.98469109092106</v>
       </c>
     </row>
     <row r="3">
@@ -7682,7 +7337,7 @@
         <v>1682.077</v>
       </c>
       <c r="C3" t="n">
-        <v>2180.447701705977</v>
+        <v>808.8186380456679</v>
       </c>
       <c r="D3" t="n">
         <v>1.90819e-07</v>
@@ -7715,16 +7370,13 @@
         <v>-27564.70733631978</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.810395849991254e-11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2434.128637667324</v>
+        <v>504.385778543593</v>
       </c>
       <c r="AA3" t="n">
-        <v>1e-08</v>
+        <v>1.417979261976193e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8187164122258088</v>
+        <v>0.9770625226712014</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7387,7 @@
         <v>1611.404</v>
       </c>
       <c r="C4" t="n">
-        <v>2097.904199290637</v>
+        <v>768.5138715973017</v>
       </c>
       <c r="D4" t="n">
         <v>1.9192e-07</v>
@@ -7768,16 +7420,13 @@
         <v>-30393.90042377313</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.372927700212982e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2356.440625562518</v>
+        <v>521.963042228945</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000119e-08</v>
+        <v>1.063183657035857e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8187829017704485</v>
+        <v>0.993438699080441</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7437,7 @@
         <v>1575.579</v>
       </c>
       <c r="C5" t="n">
-        <v>2060.821523868785</v>
+        <v>751.4776934369452</v>
       </c>
       <c r="D5" t="n">
         <v>1.92239e-07</v>
@@ -7821,16 +7470,13 @@
         <v>-31037.18969553097</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.55874122150104e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2317.316779300467</v>
+        <v>543.2347738504272</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000024045e-08</v>
+        <v>1.680255530403506e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8187899596608714</v>
+        <v>0.9704710681108566</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7487,7 @@
         <v>1536.597</v>
       </c>
       <c r="C6" t="n">
-        <v>2026.643513510091</v>
+        <v>737.4196365364904</v>
       </c>
       <c r="D6" t="n">
         <v>1.92703e-07</v>
@@ -7874,16 +7520,13 @@
         <v>-28738.03201182807</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.165904168561833e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2286.119522464697</v>
+        <v>537.5826119047181</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000247e-08</v>
+        <v>1.129332978288151e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8188216991037657</v>
+        <v>0.9958854442047181</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7537,7 @@
         <v>1512.392</v>
       </c>
       <c r="C7" t="n">
-        <v>2002.8456779642</v>
+        <v>726.8487704495742</v>
       </c>
       <c r="D7" t="n">
         <v>1.93103e-07</v>
@@ -7927,16 +7570,13 @@
         <v>-28895.87027455024</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.74042746161858e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2256.056384785873</v>
+        <v>549.8060351895209</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000002347e-08</v>
+        <v>1.998004787952333e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8189129950193168</v>
+        <v>0.9614593258700866</v>
       </c>
     </row>
     <row r="8">
@@ -7947,7 +7587,7 @@
         <v>1492.181</v>
       </c>
       <c r="C8" t="n">
-        <v>1982.807418110533</v>
+        <v>716.2463474861688</v>
       </c>
       <c r="D8" t="n">
         <v>1.93365e-07</v>
@@ -7980,16 +7620,13 @@
         <v>-30076.5926785157</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.72685249777086e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2225.900919931732</v>
+        <v>551.8322507773022</v>
       </c>
       <c r="AA8" t="n">
-        <v>1e-08</v>
+        <v>2.021418135931122e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.819045124068046</v>
+        <v>0.9628068376161149</v>
       </c>
     </row>
     <row r="9">
@@ -8000,7 +7637,7 @@
         <v>1461.894</v>
       </c>
       <c r="C9" t="n">
-        <v>1954.761999520421</v>
+        <v>706.4534293796548</v>
       </c>
       <c r="D9" t="n">
         <v>1.93899e-07</v>
@@ -8033,16 +7670,13 @@
         <v>-28852.46110564734</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.536564702534079e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2196.0039154832</v>
+        <v>522.9255353886826</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000428e-08</v>
+        <v>1.085823304193121e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8192257747855003</v>
+        <v>0.9994793656084063</v>
       </c>
     </row>
     <row r="10">
@@ -8053,7 +7687,7 @@
         <v>1439.08</v>
       </c>
       <c r="C10" t="n">
-        <v>1932.488133411392</v>
+        <v>697.6081060645184</v>
       </c>
       <c r="D10" t="n">
         <v>1.94223e-07</v>
@@ -8086,16 +7720,13 @@
         <v>-28908.51322135519</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.760263210525344e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2167.425630607172</v>
+        <v>564.0270504069305</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000014e-08</v>
+        <v>2.505954595012503e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8194058511994442</v>
+        <v>0.9507114841695963</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7737,7 @@
         <v>1414.254</v>
       </c>
       <c r="C11" t="n">
-        <v>1911.035482429834</v>
+        <v>689.9758543420246</v>
       </c>
       <c r="D11" t="n">
         <v>1.94502e-07</v>
@@ -8139,16 +7770,13 @@
         <v>-29159.12776337244</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.14325529618481e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2139.909577629029</v>
+        <v>522.618379710839</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000067e-08</v>
+        <v>1.095231734451851e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8195966819580668</v>
+        <v>0.999478008033385</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +7933,7 @@
         <v>2111.898</v>
       </c>
       <c r="C2" t="n">
-        <v>2552.961407012211</v>
+        <v>989.7244969277142</v>
       </c>
       <c r="D2" t="n">
         <v>1.86901e-07</v>
@@ -8338,16 +7966,13 @@
         <v>-33774.86298556774</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.846913323843916e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2877.138759700751</v>
+        <v>420.8958014666176</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000052073e-08</v>
+        <v>1.40443543226381e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8195915288991009</v>
+        <v>0.9558332450383024</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +7983,7 @@
         <v>1997.472</v>
       </c>
       <c r="C3" t="n">
-        <v>2422.94721975489</v>
+        <v>920.3795442397592</v>
       </c>
       <c r="D3" t="n">
         <v>1.88328e-07</v>
@@ -8391,16 +8016,13 @@
         <v>-33888.87326767434</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.405528003712421e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2768.959440272427</v>
+        <v>439.0008021187908</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000016458e-08</v>
+        <v>8.721793404055378e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8198919491967519</v>
+        <v>0.9974517457607575</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8033,7 @@
         <v>1954.439</v>
       </c>
       <c r="C4" t="n">
-        <v>2379.479700091805</v>
+        <v>897.0830112071153</v>
       </c>
       <c r="D4" t="n">
         <v>1.89304e-07</v>
@@ -8444,16 +8066,13 @@
         <v>-34009.82532537974</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.964427138879586e-12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2720.638480053613</v>
+        <v>420.424927598168</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000001424e-08</v>
+        <v>7.260883717032543e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8199472184299055</v>
+        <v>0.9999099651688204</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8083,7 @@
         <v>1925.279</v>
       </c>
       <c r="C5" t="n">
-        <v>2352.812711962656</v>
+        <v>879.9171650191694</v>
       </c>
       <c r="D5" t="n">
         <v>1.90045e-07</v>
@@ -8497,16 +8116,13 @@
         <v>-34167.61706204643</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.281344064035811e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2687.522056680972</v>
+        <v>458.9170443290848</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>9.396375109162503e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8199585031018202</v>
+        <v>0.9881745974499329</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8133,7 @@
         <v>1893.883</v>
       </c>
       <c r="C6" t="n">
-        <v>2322.693735038906</v>
+        <v>866.55627871502</v>
       </c>
       <c r="D6" t="n">
         <v>1.90706e-07</v>
@@ -8550,16 +8166,13 @@
         <v>-32371.817969048</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.77543492875132e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2657.029005892974</v>
+        <v>445.536878261337</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000001452e-08</v>
+        <v>1.092649822997671e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8201147448924281</v>
+        <v>0.992798973192511</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8183,7 @@
         <v>1868.608</v>
       </c>
       <c r="C7" t="n">
-        <v>2299.839082145288</v>
+        <v>854.1945369985701</v>
       </c>
       <c r="D7" t="n">
         <v>1.91195e-07</v>
@@ -8603,16 +8216,13 @@
         <v>-32071.22779888786</v>
       </c>
       <c r="Y7" t="n">
-        <v>178.7874322610375</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2685.114667925638</v>
+        <v>480.9278706241053</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.393666145335805e-08</v>
+        <v>9.500059489792207e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.807392366587996</v>
+        <v>0.9950136500054982</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8233,7 @@
         <v>1845.438</v>
       </c>
       <c r="C8" t="n">
-        <v>2276.625361202926</v>
+        <v>843.8008237636673</v>
       </c>
       <c r="D8" t="n">
         <v>1.91644e-07</v>
@@ -8656,16 +8266,13 @@
         <v>-31831.51642262445</v>
       </c>
       <c r="Y8" t="n">
-        <v>180.7099134671621</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2664.709232403846</v>
+        <v>477.6288742082194</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.423279139325497e-08</v>
+        <v>9.165886073026498e-10</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8063722578768966</v>
+        <v>0.9937373693650601</v>
       </c>
     </row>
     <row r="9">
@@ -8676,7 +8283,7 @@
         <v>1825.197</v>
       </c>
       <c r="C9" t="n">
-        <v>2256.442935487167</v>
+        <v>833.9121311039995</v>
       </c>
       <c r="D9" t="n">
         <v>1.91903e-07</v>
@@ -8709,16 +8316,13 @@
         <v>-31951.22384277095</v>
       </c>
       <c r="Y9" t="n">
-        <v>181.480830455624</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2646.651785233375</v>
+        <v>477.4813937834729</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.456808227389621e-08</v>
+        <v>1.25443665398941e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8050510101565322</v>
+        <v>0.9866787205314802</v>
       </c>
     </row>
     <row r="10">
@@ -8729,7 +8333,7 @@
         <v>1794.576</v>
       </c>
       <c r="C10" t="n">
-        <v>2230.130208420808</v>
+        <v>824.5974081040865</v>
       </c>
       <c r="D10" t="n">
         <v>1.92277e-07</v>
@@ -8762,16 +8366,13 @@
         <v>-30365.85402702303</v>
       </c>
       <c r="Y10" t="n">
-        <v>174.5742779311235</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2600.622594587256</v>
+        <v>476.1250701541922</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.390978337262408e-08</v>
+        <v>9.831969526959145e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8083431445395306</v>
+        <v>0.9961605017985001</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8383,7 @@
         <v>1784.815</v>
       </c>
       <c r="C11" t="n">
-        <v>2213.006685241706</v>
+        <v>814.854130303017</v>
       </c>
       <c r="D11" t="n">
         <v>1.92693e-07</v>
@@ -8815,16 +8416,13 @@
         <v>-31778.10502104715</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.872746667149741e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2519.116916451603</v>
+        <v>468.8749203198464</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000306e-08</v>
+        <v>9.498104747024292e-10</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8213885168837558</v>
+        <v>0.9981052734289519</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +8433,7 @@
         <v>1762.292</v>
       </c>
       <c r="C12" t="n">
-        <v>2192.234469119241</v>
+        <v>805.271109924242</v>
       </c>
       <c r="D12" t="n">
         <v>1.92978e-07</v>
@@ -8868,16 +8466,13 @@
         <v>-31683.216587006</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.581051058942064e-12</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2491.604678133055</v>
+        <v>474.3756085497394</v>
       </c>
       <c r="AA12" t="n">
-        <v>1e-08</v>
+        <v>1.006905085411733e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.821746400329142</v>
+        <v>0.9963914154782264</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8483,7 @@
         <v>1738.861</v>
       </c>
       <c r="C13" t="n">
-        <v>2168.935354564524</v>
+        <v>795.8369966279637</v>
       </c>
       <c r="D13" t="n">
         <v>1.93443e-07</v>
@@ -8921,16 +8516,13 @@
         <v>-31062.92627946116</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.067583795970227e-12</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2464.038823681705</v>
+        <v>473.6946504043707</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>9.880153763069584e-10</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8220720767545914</v>
+        <v>0.9968624548113522</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8533,7 @@
         <v>1708.564</v>
       </c>
       <c r="C14" t="n">
-        <v>2139.255264570246</v>
+        <v>786.8360520315147</v>
       </c>
       <c r="D14" t="n">
         <v>1.93696e-07</v>
@@ -8974,16 +8566,13 @@
         <v>-28115.63359985818</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.667103645306754e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2437.282706316727</v>
+        <v>482.2775030893397</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000007e-08</v>
+        <v>1.064996177639174e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8224168114902716</v>
+        <v>0.9927086156479861</v>
       </c>
     </row>
     <row r="15">
@@ -8994,7 +8583,7 @@
         <v>1684.266</v>
       </c>
       <c r="C15" t="n">
-        <v>2117.327598724976</v>
+        <v>777.4667883495354</v>
       </c>
       <c r="D15" t="n">
         <v>1.93967e-07</v>
@@ -9027,16 +8616,13 @@
         <v>-27958.58111479407</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.156250906290475e-12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2410.525587010599</v>
+        <v>480.1244194673075</v>
       </c>
       <c r="AA15" t="n">
-        <v>1e-08</v>
+        <v>1.050781242984815e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8227550837375864</v>
+        <v>0.9941448856849502</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8633,7 @@
         <v>1676.935</v>
       </c>
       <c r="C16" t="n">
-        <v>2105.778789208036</v>
+        <v>768.8097686636022</v>
       </c>
       <c r="D16" t="n">
         <v>1.94321e-07</v>
@@ -9080,16 +8666,13 @@
         <v>-30875.33796739028</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.470728801220286e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2384.055225509795</v>
+        <v>472.0833154775811</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000001024e-08</v>
+        <v>1.007630074066663e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.823102309757364</v>
+        <v>0.9969217255298839</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8683,7 @@
         <v>1649.18</v>
       </c>
       <c r="C17" t="n">
-        <v>2080.932645665826</v>
+        <v>758.6707474537743</v>
       </c>
       <c r="D17" t="n">
         <v>1.9469e-07</v>
@@ -9133,16 +8716,13 @@
         <v>-28487.34318003853</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.230705697416968e-08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2357.918282023292</v>
+        <v>490.3046952197239</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000016e-08</v>
+        <v>1.633708896865645e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8234458384755483</v>
+        <v>0.974489239634417</v>
       </c>
     </row>
     <row r="18">
@@ -9153,7 +8733,7 @@
         <v>1637.094</v>
       </c>
       <c r="C18" t="n">
-        <v>2065.938413596574</v>
+        <v>751.2482022643965</v>
       </c>
       <c r="D18" t="n">
         <v>1.95083e-07</v>
@@ -9186,16 +8766,13 @@
         <v>-28816.33325317343</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.194129678660083e-10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2331.314977939496</v>
+        <v>538.9370323942348</v>
       </c>
       <c r="AA18" t="n">
-        <v>1e-08</v>
+        <v>3.752600099942933e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8238081950896849</v>
+        <v>0.9176043732058954</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8783,7 @@
         <v>1609.313</v>
       </c>
       <c r="C19" t="n">
-        <v>2037.999750898706</v>
+        <v>742.0275435969953</v>
       </c>
       <c r="D19" t="n">
         <v>1.95229e-07</v>
@@ -9239,16 +8816,13 @@
         <v>-28409.74441714353</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19045633652048e-11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2306.018635037247</v>
+        <v>488.8391207764041</v>
       </c>
       <c r="AA19" t="n">
-        <v>1e-08</v>
+        <v>1.146780469981836e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8241829784722229</v>
+        <v>0.9966698469331974</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8833,7 @@
         <v>1592</v>
       </c>
       <c r="C20" t="n">
-        <v>2020.000788266332</v>
+        <v>733.9622324648541</v>
       </c>
       <c r="D20" t="n">
         <v>1.95609e-07</v>
@@ -9292,16 +8866,13 @@
         <v>-27664.71148502776</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.042093175659922e-11</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2280.661471813982</v>
+        <v>487.6946410225327</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000146e-08</v>
+        <v>1.169888228308794e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8245403951689554</v>
+        <v>0.9955956100684711</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8883,7 @@
         <v>1567.873</v>
       </c>
       <c r="C21" t="n">
-        <v>1997.820756043844</v>
+        <v>725.8288973553539</v>
       </c>
       <c r="D21" t="n">
         <v>1.95864e-07</v>
@@ -9345,16 +8916,13 @@
         <v>-27659.80082951646</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.610994835102721e-08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2255.78639408294</v>
+        <v>480.9637297520925</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000015152e-08</v>
+        <v>1.119629911330296e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8249258958499351</v>
+        <v>0.9987280094941122</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +8933,7 @@
         <v>1556.609</v>
       </c>
       <c r="C22" t="n">
-        <v>1979.764543724677</v>
+        <v>723.3337542501687</v>
       </c>
       <c r="D22" t="n">
         <v>1.96232e-07</v>
@@ -9398,16 +8966,13 @@
         <v>-27152.2559054583</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.641316762978337e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2230.140017103029</v>
+        <v>473.3298510581602</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000507e-08</v>
+        <v>1.154516377805409e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8253150783533207</v>
+        <v>0.9967664148191202</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9129,7 @@
         <v>1325.072</v>
       </c>
       <c r="C2" t="n">
-        <v>1956.931832287007</v>
+        <v>843.8003724452159</v>
       </c>
       <c r="D2" t="n">
         <v>2.08623e-07</v>
@@ -9597,16 +9162,13 @@
         <v>-16149.2406227118</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.18963506839997e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2000.054434608405</v>
+        <v>307.6394213103982</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000051e-08</v>
+        <v>7.526724388980683e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8198449945424701</v>
+        <v>0.996357747075158</v>
       </c>
     </row>
     <row r="3">
@@ -9617,7 +9179,7 @@
         <v>1141.581</v>
       </c>
       <c r="C3" t="n">
-        <v>1685.654169874066</v>
+        <v>581.5702368085556</v>
       </c>
       <c r="D3" t="n">
         <v>2.06994e-07</v>
@@ -9650,16 +9212,13 @@
         <v>-24860.58184285437</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.899639652387902e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1828.839227429705</v>
+        <v>544.1005835499863</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000072e-08</v>
+        <v>1.403402698344825e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8203893547553976</v>
+        <v>0.9978541852076358</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9229,7 @@
         <v>1090.47</v>
       </c>
       <c r="C4" t="n">
-        <v>1622.592444608669</v>
+        <v>1200.224455460131</v>
       </c>
       <c r="D4" t="n">
         <v>2.06951e-07</v>
@@ -9703,16 +9262,13 @@
         <v>-25272.2961287095</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.295643239239275e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1778.897592392325</v>
+        <v>0.2620115934518824</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000046e-08</v>
+        <v>4.255470027466449e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8205170933880845</v>
+        <v>0.8408656515116577</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9279,7 @@
         <v>1065.158</v>
       </c>
       <c r="C5" t="n">
-        <v>1598.401910760441</v>
+        <v>1016.707102402086</v>
       </c>
       <c r="D5" t="n">
         <v>2.07057e-07</v>
@@ -9756,16 +9312,13 @@
         <v>-26428.63204935795</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.339943731119014e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1748.353368977718</v>
+        <v>107.8045529630894</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000076e-08</v>
+        <v>1.826786052755414e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8206349145994807</v>
+        <v>0.9136829835148477</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9329,7 @@
         <v>1038.614</v>
       </c>
       <c r="C6" t="n">
-        <v>1572.961836703589</v>
+        <v>1001.18707685841</v>
       </c>
       <c r="D6" t="n">
         <v>2.07355e-07</v>
@@ -9809,16 +9362,13 @@
         <v>-25695.89624876585</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.06089984688109e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1720.612338470688</v>
+        <v>111.8751318607431</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000351e-08</v>
+        <v>1.857036407222256e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8208233706467746</v>
+        <v>0.91227041279604</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9379,7 @@
         <v>1023.88</v>
       </c>
       <c r="C7" t="n">
-        <v>1558.659745854895</v>
+        <v>987.1174182601842</v>
       </c>
       <c r="D7" t="n">
         <v>2.07609e-07</v>
@@ -9862,16 +9412,13 @@
         <v>-26403.05827183233</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.37158877233294e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1693.155492008821</v>
+        <v>116.0754757575176</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000022e-08</v>
+        <v>1.898441507964229e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8210912061231181</v>
+        <v>0.9148753749745114</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9429,7 @@
         <v>1003.1</v>
       </c>
       <c r="C8" t="n">
-        <v>1535.748760360578</v>
+        <v>1001.13698285028</v>
       </c>
       <c r="D8" t="n">
         <v>2.078e-07</v>
@@ -9915,16 +9462,13 @@
         <v>-25876.91593827373</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.830612224195562e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1666.728511405334</v>
+        <v>94.69012487638874</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000001403e-08</v>
+        <v>2.007547798056529e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8213970356642882</v>
+        <v>0.9075850600420277</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9479,7 @@
         <v>978.5730000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>1519.441347946964</v>
+        <v>989.0411443149591</v>
       </c>
       <c r="D9" t="n">
         <v>2.07998e-07</v>
@@ -9968,16 +9512,13 @@
         <v>-25678.13215329937</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.284306897986913e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1640.36726593241</v>
+        <v>94.56177980974037</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>1.999707737563698e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8217390669474903</v>
+        <v>0.9061091230833974</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9529,7 @@
         <v>966.352</v>
       </c>
       <c r="C10" t="n">
-        <v>1508.59743027234</v>
+        <v>966.352</v>
       </c>
       <c r="D10" t="n">
         <v>2.08297e-07</v>
@@ -10020,11 +9561,10 @@
       <c r="X10" t="n">
         <v>-27710.36230917755</v>
       </c>
-      <c r="Y10" t="n">
-        <v>140.6764401548427</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1567.082173047818</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>1.280368087482346e-08</v>
@@ -10041,7 +9581,7 @@
         <v>940.7620000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>1483.020945823115</v>
+        <v>958.3643644410558</v>
       </c>
       <c r="D11" t="n">
         <v>2.0844e-07</v>
@@ -10074,16 +9614,13 @@
         <v>-25053.07583818535</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.253218068662767e-07</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1593.111746086915</v>
+        <v>108.0598360862729</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.00000000000105e-08</v>
+        <v>2.178899680009048e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8223684639019326</v>
+        <v>0.9064638427848911</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 55.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>1.000000000014896e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8186774839590578</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2319.272</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2754.780557891642</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.79726e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-66.955</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1585747846515243</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4599211563732</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.535480161012092</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.224837074583673</v>
+      </c>
+      <c r="L12" t="n">
+        <v>19.9540243556174</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.81640921430224</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11.02312575118854</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-29914.98110711802</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.2296241170370195</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.00000000000012e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8167896763566419</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2218.411</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9565117847324506</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2614.043260519291</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.948911612226542</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.79278e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-69.04600000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3583572110792922</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.027572347266845</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.013596491228113</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.850155763239886</v>
+      </c>
+      <c r="L13" t="n">
+        <v>38.06553223342664</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.69713293948777</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.29067903633629</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-34761.02860804056</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>11.84678701661142</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.449986721646182e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.7991918328057676</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2150.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.927058145831968</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2552.178791949505</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9264544809706377</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.79373e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-69.812</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.02467248908296248</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.668285431119922</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.490639269406358</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.321809488782561</v>
+      </c>
+      <c r="L14" t="n">
+        <v>28.71178445525151</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.66424764890175</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.18949202404524</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-33591.47731365899</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>12.92666714526786</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000201e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8171991454006072</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2094.711</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9031760828397878</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2501.220723448591</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9079564309699092</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.79765e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-70.333</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.06178861788617579</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.3865384615384614</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.310533610533601</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.830832570905755</v>
+      </c>
+      <c r="L15" t="n">
+        <v>24.39693656956412</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.54943589274184</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12.84792135780487</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-32031.92196320686</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>14.99573403278259</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.432291297293793e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8012758228254919</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2051.908</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8847207227095398</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2460.856911233248</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.893304152370181</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.80066e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-70.762</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1614345114345062</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5868978805394516</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.204821958456928</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.005304792926931</v>
+      </c>
+      <c r="L16" t="n">
+        <v>24.90652750674552</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.60411717932806</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>13.00837999458543</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-31913.06618704371</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>14.38818673183755</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.428577322949221e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8013860969554942</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2025.09</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8731576115263756</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2539.67354458536</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9219150096402186</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.8041e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-71.145</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8531630170316488</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9704063604239835</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.629460847240028</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.579338505512531</v>
+      </c>
+      <c r="L17" t="n">
+        <v>31.67584235481791</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.87504135878514</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13.86601887606812</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-33633.35851403059</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-35.77321594088289</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000050927e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8177443413666805</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1982.399</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8547505424115843</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2509.625540345625</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9110074242234214</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.80841e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-71.486</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.09480519480518121</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.326387009472066</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.170400000000106</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.937499999999986</v>
+      </c>
+      <c r="L18" t="n">
+        <v>25.09660724327303</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.68327670184654</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>13.2478562366808</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-31559.41778611071</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-38.7660026238143</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000083773e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8179917421367228</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1952.526</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8418702075478859</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2354.921415181982</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8548490036477933</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.81234e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-71.818</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3952029520295419</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4692307692307645</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.085580389329531</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.429180695847357</v>
+      </c>
+      <c r="L19" t="n">
+        <v>24.38145561030451</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.68809269322692</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>13.26270894555962</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-31152.41284712239</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>14.10923572587603</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000168214e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8182273988864641</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1920.287</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.8279697249826671</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2454.664884014609</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8910564135436162</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.81622e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-72.07299999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5299310344827709</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5725067385444794</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.29827823691461</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.041313868613145</v>
+      </c>
+      <c r="L20" t="n">
+        <v>24.49086342097672</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.75111752662106</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13.46017764347877</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-31221.48532913067</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-43.20599074457459</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.459199413072242e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8012792039769343</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1877.408</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.8094815959490737</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2424.826318795009</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8802248556054997</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.82048e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-72.35599999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1320736434108495</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.7016742763137747</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.774792760313141</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.050101132663364</v>
+      </c>
+      <c r="L21" t="n">
+        <v>20.90216401282332</v>
+      </c>
+      <c r="M21" t="n">
+        <v>85.35115376309354</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>12.29767327067961</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-27995.56745854828</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-43.01697511598991</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000014896e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8186774839590578</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>1.000000000000655e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8254542221389155</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2049.569</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2470.533733084454</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.89568e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-69.714</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.03984375000001497</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5672707889126211</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.284543125533713</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.780857009781086</v>
+      </c>
+      <c r="L23" t="n">
+        <v>25.28013104938837</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.67769190834748</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.23067387865224</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-32276.24153380185</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.869575485474343</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000009562e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8197788815018751</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1921.625</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9375751682426888</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2323.578116936281</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9405166526648885</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.92475e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-70.724</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.02307692307692821</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.4259562841530169</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.7268243243243059</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.796038151137158</v>
+      </c>
+      <c r="L24" t="n">
+        <v>22.9483826203297</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.71322709819221</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.34076500332833</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-30869.33157610318</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>17.04732393665859</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000047e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8202425632635399</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1896.133</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9251374313331241</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2278.206327751814</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.922151475708644</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.93395e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-71.063</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2838084378563289</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.033136792452822</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.841335131490256</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.479505872822919</v>
+      </c>
+      <c r="L25" t="n">
+        <v>33.65585865354063</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.17691980166539</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14.96456239221126</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-34249.29508316806</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>19.02075272404295</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.00000000000035e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8203774656077029</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1858.729</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9068877407884292</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2248.501046823279</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9101276443677747</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.94005e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-71.324</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2180272108843628</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5796391752577996</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.37511032656668</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.992538915727219</v>
+      </c>
+      <c r="L26" t="n">
+        <v>26.78809752431617</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.99839542539505</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>14.29491325704733</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-32210.21361267188</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>19.71402526116367</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000002194e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8204699467478979</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1829.222</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8924910554365331</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2226.436056516214</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9011963798351036</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.94399e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-71.554</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2295081967213187</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.458184143222505</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.141674249317539</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.103157894736873</v>
+      </c>
+      <c r="L27" t="n">
+        <v>23.59409525852557</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.87587358970984</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>13.86882667000138</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-30819.6149635234</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>17.47031369191018</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.00000000000004e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8206270444170378</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1799.899</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8781841450568385</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2194.736842931273</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8883654627096108</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.95007e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-71.795</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.09674418604650938</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9625835189311763</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.025788900979394</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.008090844570724</v>
+      </c>
+      <c r="L28" t="n">
+        <v>23.9431557052806</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.91292744449579</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>13.99499638884589</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-30711.9201904497</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>18.97836176493956</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000005444e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8208245912413163</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1778.92</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.867948334503498</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2167.443402869748</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8773178742083809</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.95551e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-72.07899999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3966819221968448</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7014734774066812</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.634000000000123</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.331633272616938</v>
+      </c>
+      <c r="L29" t="n">
+        <v>26.34623474102023</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.03553267229474</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>14.42925563003187</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-31356.98386594918</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>19.18767025792636</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000103e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8210531653555203</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1747.645</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8526890287665356</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2141.850038777641</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.866958426875454</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.96055e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-72.32299999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1770631067961296</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.4623873873873711</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.9205223880596185</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.228667225481966</v>
+      </c>
+      <c r="L30" t="n">
+        <v>22.70337924811805</v>
+      </c>
+      <c r="M30" t="n">
+        <v>85.87061031206963</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>13.85108836176732</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-29651.04948460772</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>19.14217524041419</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8213020873958177</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1715.609</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8370584254543271</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2119.189773049523</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8577862122140392</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.96625e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-72.483</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.07826289950623208</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9801000711540685</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.847263413633432</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.189965525357663</v>
+      </c>
+      <c r="L31" t="n">
+        <v>25.06692690148411</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85.74332769620638</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>13.43545451619287</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-28365.29311611508</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>17.46053973308108</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8215601878843636</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1700.874</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8298691090663451</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2096.267547372246</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8485079638054821</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.9695e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-72.70699999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.03505402160863317</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5470223325061931</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.787132352941141</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.148451151707752</v>
+      </c>
+      <c r="L32" t="n">
+        <v>23.20462053068555</v>
+      </c>
+      <c r="M32" t="n">
+        <v>85.94015713521885</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>14.08918005742417</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-29499.88895770364</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>17.10509584710235</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8218355076552178</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1684.541</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8219001165610914</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2182.558795134385</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.883436144144232</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.97248e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-72.90300000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2993224932249284</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.197248968363107</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.703867924528241</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.335793357933519</v>
+      </c>
+      <c r="L33" t="n">
+        <v>25.60634371002162</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.12324255767194</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>14.75674375911331</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-30652.09157851015</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-32.64327562281369</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000003668e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8221100891259403</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1664.2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8119755909657103</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2047.864885337117</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8289159779171944</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.9763e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-73.08799999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.4406885758998715</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7168107588857473</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.182897862232749</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.562611073137339</v>
+      </c>
+      <c r="L34" t="n">
+        <v>25.87733918991289</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.20355099496464</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>15.06984640200759</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-30985.04205280727</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>18.82428020678105</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000007576e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8224020485155823</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1637.12</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7987630570134501</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2027.762357948757</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8207790611371666</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.98164e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-73.343</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.08323917137476962</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.121194029850707</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.175358422939039</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.782348993288685</v>
+      </c>
+      <c r="L35" t="n">
+        <v>21.16879016516664</v>
+      </c>
+      <c r="M35" t="n">
+        <v>85.87991980962975</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>13.88249400714191</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-28104.00107703159</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>17.504144146096</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000001325e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8227032451695064</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1614.806</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.787875890004191</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2120.673827830157</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8583869143055588</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.9857e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-73.51000000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.5629906542055639</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.6908163265305866</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.655577299412764</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.052464228934735</v>
+      </c>
+      <c r="L36" t="n">
+        <v>21.57941320890608</v>
+      </c>
+      <c r="M36" t="n">
+        <v>85.94789243767886</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>14.11616585849287</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-28294.57574853358</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-35.51865036752702</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8230266146558169</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1590.964</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7762432003996937</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1983.588399173991</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8028987309950578</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.98769e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-73.767</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.07173978882687217</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.058668705439521</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.967504523694704</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.319502330522582</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>85.68494044969964</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>13.25298355993706</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-26179.97634280716</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>17.62280585060364</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000037474e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.823351715766147</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1575.338</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.768619158466975</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1961.190321431433</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7938326423832688</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.99302e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-73.93899999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2994915254237248</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9693840579710565</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.020228671943679</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.754954321855337</v>
+      </c>
+      <c r="L38" t="n">
+        <v>18.44634920546769</v>
+      </c>
+      <c r="M38" t="n">
+        <v>85.83022020495159</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>13.716453327074</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-26857.77674374761</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>18.19523216400103</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8236752203402323</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1542.203</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7524523448588458</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1942.128110800467</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7861168154849382</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.99637e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-74.099</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.07430476998689227</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.548035304556388</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.741602887747425</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.772421530108343</v>
+      </c>
+      <c r="L39" t="n">
+        <v>6.325006490058035</v>
+      </c>
+      <c r="M39" t="n">
+        <v>85.55474785019742</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>12.86333617437917</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-24813.23486023556</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>17.16268393543351</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000082565e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8240364476399836</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1538.817</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7508002902073556</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2053.234118051917</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.831089286722048</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.99729e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-74.298</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.5791304347824622</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.4662079510703839</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.067057761732905</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.14161237785019</v>
+      </c>
+      <c r="L40" t="n">
+        <v>18.10624525057016</v>
+      </c>
+      <c r="M40" t="n">
+        <v>85.89717706372096</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>13.94108777677551</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-26751.19685487385</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-44.21213974574061</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000071e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8243669625812434</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1514.049</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7387157982971052</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2033.609761316801</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8231459194762121</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.00154e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-74.486</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1789824072844176</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9901773652783236</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.107320483577281</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.53429407337965</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>85.67983918752189</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>13.23727502118751</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-25046.5227868827</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-44.66586097092568</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000292e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8247232020220793</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1496.498</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7301525345084746</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1885.956979899564</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7633803799735827</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.00368e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-74.666</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3152446066921513</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8143617244498197</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.037116929129906</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.531062556991498</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>85.65409604666891</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>13.15856460221548</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-24639.74399748924</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>14.80288385152255</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8250811738977637</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1488.396</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7261995082868641</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1863.571592254525</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7543194279431519</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.00741e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-74.914</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.102791878172398</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.687196467991009</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.624079320113237</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.724205544286647</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.651683256211446</v>
+      </c>
+      <c r="M43" t="n">
+        <v>85.60819168391087</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>13.02049600043847</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-24133.75447069373</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>16.04289970281843</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000655e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8254542221389155</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>1.000000000001279e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8216299238500708</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2296.259</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2744.034640509481</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.76371e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-68.654</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.005752636625114716</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.643380109823051</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.375000000000025</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.381972149040257</v>
+      </c>
+      <c r="L23" t="n">
+        <v>27.04477161163654</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.39177638401414</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.40655543791352</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-33423.4216940086</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-8.642976989741555</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8167512048500183</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2135.695</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9300758320381105</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2552.077088440973</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9300455069937209</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.78267e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-70.33</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1473871733966776</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.3840292275574305</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.20766283524897</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.817417556897355</v>
+      </c>
+      <c r="L24" t="n">
+        <v>24.45472526078392</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.53496643231591</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.80611795201077</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-32428.9839919529</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>10.91775006733042</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000151e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8171428854042595</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2095.379</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9125185791324062</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2617.35175200011</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9538333493902794</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.78277e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-70.899</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2782363977485984</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.041071428571386</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.655418719211857</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.335013162843247</v>
+      </c>
+      <c r="L25" t="n">
+        <v>30.63640717090059</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.86922017233529</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>13.84641084333695</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-34518.214625006</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-37.89739010306153</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.408723919991782e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8024963177946208</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2056.981</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.895796597857646</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2571.307384037253</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9370535437409209</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.78542e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-71.29300000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1542452830188647</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.3028279654359785</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.086224821312543</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.772313865358907</v>
+      </c>
+      <c r="L26" t="n">
+        <v>23.8411350464324</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.61970620755656</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>13.05485737165704</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-31987.10972683296</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-31.66822249554457</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.429785062539998e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8015259960473308</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2028.168</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8832487972828849</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2547.91433454718</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.928528487553682</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.78356e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-71.545</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2835514018691813</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4578194816800418</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.412489795918334</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.250242587601068</v>
+      </c>
+      <c r="L27" t="n">
+        <v>25.26808171004656</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.75675250055059</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>13.4781182305421</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-32674.38718010858</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-34.91383982736261</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8173622034734879</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1997.313</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8698117242001011</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2523.584061093342</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9196618817555421</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.78514e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-71.94199999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.007309941520472623</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7834932821497109</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.346691449814127</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.093251859723683</v>
+      </c>
+      <c r="L28" t="n">
+        <v>22.60055077831586</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.64471569966712</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>13.13011476847629</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-31411.49473469492</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-37.51044605070342</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.81748602223323</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1970.152</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8579833546651314</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2375.994285211792</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8658761992780983</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.78715e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-72.16800000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5727735368956673</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.6934306569342773</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.306414219474502</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.362458654906276</v>
+      </c>
+      <c r="L29" t="n">
+        <v>22.88644387318298</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.7339394940268</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>13.40577828343277</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-31723.44635492421</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>14.45120130453802</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000159084e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8176430666296741</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1933.798</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8421515168802822</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2477.208175300881</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9027612620957808</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.78614e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-72.40600000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2122302158273307</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8129737609328568</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.198596491228048</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.588855602156974</v>
+      </c>
+      <c r="L30" t="n">
+        <v>20.86297303891655</v>
+      </c>
+      <c r="M30" t="n">
+        <v>85.58268283310457</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>12.94500985761681</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-30185.32181046786</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-42.43474713368164</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000099752e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8178295304769163</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1916.056</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8344250365485774</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2452.342579097106</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8936995702947043</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.78607e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-72.679</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.08494117647058347</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.203337306317007</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.133040078201236</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.468657599053973</v>
+      </c>
+      <c r="L31" t="n">
+        <v>22.12878298131901</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85.77806666185957</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>13.54641045978506</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-31338.04713138255</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-43.63041217698446</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8180467454064364</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1882.6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8198552515199723</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2293.375868080778</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8357678267702079</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.78627e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-72.91200000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.02690677966101727</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5146216768916433</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.000484652665529</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.329708431836253</v>
+      </c>
+      <c r="L32" t="n">
+        <v>20.4161222957007</v>
+      </c>
+      <c r="M32" t="n">
+        <v>85.63242873926892</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>13.09303392757421</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-29864.52036155956</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>15.18938125170371</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8182950314756228</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1863.725</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8116353599485076</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2409.929422912116</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8782430758471286</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.78455e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-73.172</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4276595744681494</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.067128712871187</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.82804659498199</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.061922714420343</v>
+      </c>
+      <c r="L33" t="n">
+        <v>21.07389383620736</v>
+      </c>
+      <c r="M33" t="n">
+        <v>85.80004939311935</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>13.61756961916917</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-30800.82457272207</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-47.96846112052344</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.818551472836228</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1834.568</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7989377504889476</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2245.813255801179</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8184347320718234</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.78432e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-73.468</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2334498834498945</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8906143344709286</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.324122807017519</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.743734491315224</v>
+      </c>
+      <c r="L34" t="n">
+        <v>18.08763919586585</v>
+      </c>
+      <c r="M34" t="n">
+        <v>85.56015391330622</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>12.87906187229454</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-28701.88478166432</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>14.10293100628883</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000001204e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8188384935621639</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1806.722</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7868110696572121</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2369.558219134694</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8635307237574602</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.78076e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-73.649</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.03001813298686253</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.7603460783619607</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.857296409695922</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.309749567866873</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>85.60673631577249</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>13.01616572166703</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-28685.03259873531</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-52.44038145094623</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000183e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8191308488972497</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1782.123</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7760984279212406</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2344.770381236439</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8544973691735499</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.77901e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-73.889</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.08614955853766434</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.7966535833294411</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.939720866532336</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.200588164529912</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>85.610437234266</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>13.02718299671588</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-28394.66167818223</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-52.04452360920436</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000013776e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8194319463068017</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1766.725</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7693927383627021</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2296.4798096192</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.83689898652038</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.77859e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-74.16</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1218475073313849</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.4649819494584939</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.209105560032239</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.74607754734008</v>
+      </c>
+      <c r="L37" t="n">
+        <v>17.64475831034795</v>
+      </c>
+      <c r="M37" t="n">
+        <v>85.66205234667723</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>13.18279167020717</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-28461.83541249934</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-40.76679783296731</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000003142e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8197395374908334</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1739.261</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7574324150716448</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2310.436420408376</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8419851507338846</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.77748e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-74.419</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.242802325464425</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.040044628347885</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.32352018960071</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.295937500013407</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>85.40347199469859</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>12.43825960549582</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-26483.93509906495</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-57.30982195680758</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8200444774305483</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1719.156</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7486768696388343</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2258.395910894607</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8230201898891824</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.77596e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-74.56699999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.08028936669875121</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.9018566444196355</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.891749737951876</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.479688990495477</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>85.5609320108414</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>12.8813284272303</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-27191.33839576717</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-43.52466376248435</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000825e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8203547809949402</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1697.681</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7393247016124923</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2236.564069506659</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.815064079909501</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.77453e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-74.846</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2958323106436052</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8641788302522365</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.870715502156409</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.474297553205317</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>85.39634455312655</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>12.41891958525885</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-25897.57203092706</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-43.60965390863612</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000741e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.820672922691858</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1683.348</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7330828099095094</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2222.231883477982</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8098410459808858</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.77162e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-75.05500000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3272425249169544</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.037594799566578</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.32446280991732</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.954877192982371</v>
+      </c>
+      <c r="L41" t="n">
+        <v>12.3728283624158</v>
+      </c>
+      <c r="M41" t="n">
+        <v>85.5448689275364</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>12.83469776916752</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-26556.73841351583</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-46.66397774311781</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8209825486897392</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1659.877</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7228614019585768</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2202.347073420655</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.802594486566594</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.77016e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-75.252</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3755122626338965</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.882693415982002</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.971470568481517</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.576407675697975</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>85.45268774548107</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>12.57345564903139</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-25706.5580828153</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-47.36598267038767</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.821309181071586</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1635.382</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7121940512808007</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2187.841817311047</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7973083812472692</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.77114e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-75.474</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.2581038217365134</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.7534271268454416</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.857111363532125</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.033373210900836</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>85.11598921882953</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>11.70286889378427</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-23581.44735841637</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-50.37435097683328</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000001279e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8216299238500708</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>1.000000000000021e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8163150548366694</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2055.368</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2587.599603449325</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.79691e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-66.895</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2493913043478221</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.636128048780512</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.097439024390271</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.673099662162126</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.09334511765336</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.72014836631793</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.087183331123452</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-22726.48146502904</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-42.70350506888008</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.988846993442448e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.7747497912492826</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1749.25</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.851064140338859</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2211.267460707486</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8545632244493391</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.86279e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-71.098</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1537557943148126</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8639157227665247</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.760311059520085</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.887455335491913</v>
+      </c>
+      <c r="L13" t="n">
+        <v>30.43281780639558</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.43516227096887</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.5249795278522</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-27597.76330893855</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.804180770034009</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000079e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8157461941399734</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1674.421</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8146575211835546</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2118.706358999411</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8187921949652223</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.8711e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-72.34999999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2670658682634868</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9895588235294286</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.571052631579055</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.878855218855212</v>
+      </c>
+      <c r="L14" t="n">
+        <v>23.49926292227236</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.00043112084253</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.30221277152701</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-30499.42147381005</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>9.54219944399415</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8158701634296962</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1620.014</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7881868356420846</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2075.609880022294</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8021371920352217</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.8701e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-72.92400000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.03813582830797662</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7716069131985591</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.809111047127211</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.518590983728823</v>
+      </c>
+      <c r="L15" t="n">
+        <v>36.55652458681441</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.85690537485016</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.80511105378638</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-28740.96151745195</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>11.61768338671413</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000068516e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.815882302457436</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1592.746</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7749201116296449</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2045.77477314963</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7906071597872288</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.87345e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-73.312</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5155109513330233</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.174309192244147</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.071469324360639</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.246148210642394</v>
+      </c>
+      <c r="L16" t="n">
+        <v>56.56221116205242</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.10034161816279</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.66981819561738</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-30139.68816408904</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>9.022326505947831</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000003383e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8158760916433044</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1560.177</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7590742874268745</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2015.051992497905</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7787340784145268</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.87595e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-73.68300000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5608120391205057</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.385744385124258</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.162864571541563</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.360447897224332</v>
+      </c>
+      <c r="L17" t="n">
+        <v>62.5869942657136</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.15477108984886</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>14.87810863730701</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-30131.40489930597</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>9.519408343214309</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000749e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8159179511372353</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1527.535</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7431929464699266</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1986.307044837295</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7676253475187993</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.87763e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-73.95699999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2277167335536202</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9674059784539646</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.888286174759087</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.85972035173991</v>
+      </c>
+      <c r="L18" t="n">
+        <v>43.05335073456732</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.08138355222933</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14.59862617537217</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-29114.33606285213</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>10.35081676214043</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000021807e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8159718830446999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1503.321</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7314120877623861</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2114.859733746477</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8173056337337988</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.87885e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-74.217</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5093014485010308</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.193291769396836</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.878421192391944</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.753185971985134</v>
+      </c>
+      <c r="L19" t="n">
+        <v>43.79316668483327</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.15446570425812</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14.876923566069</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-29316.09885609434</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-65.68178262600179</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8160623225976936</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1479.373</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7197606462686973</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2086.515076305124</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8063515984172187</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.88043e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-74.425</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2047546648799991</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9014897860428804</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.022458593118618</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.887040077883444</v>
+      </c>
+      <c r="L20" t="n">
+        <v>45.01037156074624</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.19490023385163</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>15.03548503297851</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-29292.31176746068</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-63.89206655467581</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000001037e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8161684121207439</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1458.328</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7095216039171575</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2150.04905467549</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8309048478015799</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.88263e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-74.681</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3755920250787826</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.114197939153625</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.880712433186532</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.872744652156764</v>
+      </c>
+      <c r="L21" t="n">
+        <v>45.65998810141355</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.20519091257219</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>15.07637789644078</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-29049.92704982174</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-107.2673983948982</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000021e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8163150548366694</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>1.000000000001243e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8247433108567596</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2109.609</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2535.532549741141</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.80582e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-69.59</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1264993026499297</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.3980237154150182</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.283583267561235</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.712387483926287</v>
+      </c>
+      <c r="L23" t="n">
+        <v>22.9206481399476</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.48563307455248</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.66560033411639</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-31764.89629019741</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.53717794806721</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000113e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8187223477313514</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2004.165</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9500172780832847</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2407.557586797167</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9495273831302069</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.82804e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-70.908</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.05467914438501859</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.4101302460202806</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.165629139072955</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.16544959128066</v>
+      </c>
+      <c r="L24" t="n">
+        <v>25.86213396851568</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.77726979360258</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.54384484897848</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-32504.48179644905</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>13.21544964386089</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.445891583989431e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8020592143047403</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1954.573</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9265096043864053</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2469.229454176645</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9738504261870883</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.83893e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-71.398</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4491686460807748</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6135817307692117</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.560422163588374</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.95633251833736</v>
+      </c>
+      <c r="L25" t="n">
+        <v>25.61951024273065</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.79496131596672</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>13.60103321445857</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-31977.71335055447</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-33.55290732914659</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000084496e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.819043599687526</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1932.932</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9162513053366763</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2445.214707916281</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9643791432162524</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.8475e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-71.702</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6595848595848331</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8671729957805677</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.824917817225479</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.584933222036676</v>
+      </c>
+      <c r="L26" t="n">
+        <v>31.08212197469907</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.00473210617741</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>14.31765949167264</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-33338.50338005289</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-37.58776784390329</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000074021e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8190909559437562</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1894.38</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8979768288815605</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2295.240868079738</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9052302910937056</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.85466e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-71.956</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2981707317073275</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8932079414838812</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.68899613899624</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.345792222867111</v>
+      </c>
+      <c r="L27" t="n">
+        <v>24.8488470947256</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.77433236462277</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>13.53439579442333</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-31008.47685392185</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>15.52483349307477</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.41996735244995e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8046711866808292</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1862.599</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8829119519304287</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2394.352901291099</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9443195282724905</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.85812e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-72.122</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.01997663551402849</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.5232771822358158</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.7831899921814075</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.347557003257347</v>
+      </c>
+      <c r="L28" t="n">
+        <v>22.49218713525085</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.68211348543718</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>13.24427378930981</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-29947.1649625958</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-39.94137875718434</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.458498066863573e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8031980694926291</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1829.782</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8673559887163924</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2347.558761196173</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9258641784882002</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.86224e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-72.40600000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1241647301518033</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.5780800559709286</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.924408686613661</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.920031018385956</v>
+      </c>
+      <c r="L29" t="n">
+        <v>19.77818342140005</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.4484269107667</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>12.56163574566255</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-27979.73269080841</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-30.72317194015545</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8196074959740213</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1813.049</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8594241871360997</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2325.859419700727</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9173060783377364</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.86793e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-72.616</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2288065843621437</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8352389878162678</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.176658860265418</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.426105810927893</v>
+      </c>
+      <c r="L30" t="n">
+        <v>20.8435048573684</v>
+      </c>
+      <c r="M30" t="n">
+        <v>85.60896831082496</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>13.02280793584823</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-28766.31773061886</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-32.42872095442931</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000029e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8198317936240599</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1791.775</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8493398539729401</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2301.593614205202</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9077357789945065</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.87002e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-72.83799999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2748043818466299</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.019710906701625</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.012768031189103</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.967671809256684</v>
+      </c>
+      <c r="L31" t="n">
+        <v>20.71546828223053</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85.65303013752521</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>13.15532561448664</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-28756.07535024081</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-32.30918691496527</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000534e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8201092857635204</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1771.164</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8395697970571797</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2281.47415429457</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8998007753943019</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.87396e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-73.09699999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.08384527872582639</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4034090909090997</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.288996763754067</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.002663622526548</v>
+      </c>
+      <c r="L32" t="n">
+        <v>18.8579425993542</v>
+      </c>
+      <c r="M32" t="n">
+        <v>85.536689265056</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>12.81108116479109</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-27684.93709289018</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-33.09512471011658</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8204279121052407</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1747.663</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8284298180373708</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2146.211079817501</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8464537676854565</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.87648e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-73.24299999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5698811096433439</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.5894862604539836</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.181950384944372</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.16427432216905</v>
+      </c>
+      <c r="L33" t="n">
+        <v>19.72323614897519</v>
+      </c>
+      <c r="M33" t="n">
+        <v>85.64876452444132</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>13.14237950920491</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-28123.70963899793</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>16.53355039929488</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8208081807839711</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1724.264</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8173381892094697</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2240.833032392601</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8837721419199976</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.88127e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-73.48999999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1976578411405386</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6303303303303726</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.209066427289134</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.942250673854441</v>
+      </c>
+      <c r="L34" t="n">
+        <v>17.88599935950926</v>
+      </c>
+      <c r="M34" t="n">
+        <v>85.52395524815631</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>12.77448650817274</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-26980.1496763315</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-37.26859641980991</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000125e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8211641342548746</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1700.635</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8061375354390317</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2219.222955255829</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8752492471383952</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.88564e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-73.727</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1817958179581655</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9315989847716106</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.371781756180785</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.040674318507756</v>
+      </c>
+      <c r="L35" t="n">
+        <v>15.75115614220901</v>
+      </c>
+      <c r="M35" t="n">
+        <v>85.43447767524192</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>12.52309344730977</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-26126.30703645421</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-38.63115556770504</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8215384419511169</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1679.72</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7962233759905271</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2199.114110434666</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.867318430070708</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.88678e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-73.90300000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.07331730769230987</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.639267015706765</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.636890951276123</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.067287630402468</v>
+      </c>
+      <c r="L36" t="n">
+        <v>16.53200210997002</v>
+      </c>
+      <c r="M36" t="n">
+        <v>85.55302254198135</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>12.85832545716506</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-26558.86995910022</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-40.53915998633215</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000027e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8219147047866441</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1659.648</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7867088166574945</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2177.817748363521</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8589192627741499</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.88925e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-74.06</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.7193661971831671</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.593678160919536</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.664784394250493</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.42921253175273</v>
+      </c>
+      <c r="L37" t="n">
+        <v>17.54275273248681</v>
+      </c>
+      <c r="M37" t="n">
+        <v>85.63416318064937</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>13.09825567409449</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-26767.35432003055</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-41.28584363595792</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8222964029961314</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1637.082</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7760120477301717</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2159.781198106217</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8518057472094827</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.89484e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-74.298</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.450240384615369</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.6442043222003655</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.584868421052649</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.898097826086989</v>
+      </c>
+      <c r="L38" t="n">
+        <v>14.24045460836506</v>
+      </c>
+      <c r="M38" t="n">
+        <v>85.45889795763823</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>12.59072292520358</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-25383.43886330936</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-44.08365395288024</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8226889203609115</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1615.956</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7659978697474272</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2136.461285645054</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8426085028422019</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.89727e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-74.51900000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3767942583731618</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.041881443298995</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.9804347826086868</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.118482344102102</v>
+      </c>
+      <c r="L39" t="n">
+        <v>12.06014352843084</v>
+      </c>
+      <c r="M39" t="n">
+        <v>85.35343439223158</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>12.30373578560168</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-24497.48739716551</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-44.59176788116281</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8231048157835914</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1587.141</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7523389405335302</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1985.711064065359</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.783153450058484</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.89987e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-74.694</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2563781606098836</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9969441452217283</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.804196397967004</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.553055431392509</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>85.22137184686588</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>11.96219201794371</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-23498.40669568294</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>15.02140676588704</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000010132e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8234896453865895</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1565.966</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7423015354978103</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2097.686802803091</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8273160614787807</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.90312e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-74.93300000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2124016522732937</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8316712066353664</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.914456992646637</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.251959721728572</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>84.98757251495587</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>11.40156880999661</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-22083.13348589925</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-47.78575787740874</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000019e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8238958024119492</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1552.813</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7360667308491764</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1936.969658826233</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7639301096820797</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.9041e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-75.092</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.08507853403138531</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6179340028694011</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.316837782340924</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.586170212765991</v>
+      </c>
+      <c r="L42" t="n">
+        <v>9.096772206442481</v>
+      </c>
+      <c r="M42" t="n">
+        <v>85.29593044656765</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>12.15266566885281</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-23353.09673975293</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>15.92778277951504</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000001356e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8243226703090486</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1529.684</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7251030878233835</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2062.187448085079</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8133153125151611</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.90786e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-75.28</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.2592079207920942</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.355447154471579</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.513070539419135</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.417086330935393</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7.476094741698008</v>
+      </c>
+      <c r="M43" t="n">
+        <v>85.23316132345582</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>11.99191471404188</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-22753.88532271128</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-52.88080689529988</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000001243e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8247433108567596</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>1.000000000001448e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8213032005508728</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2145.244</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2682.362506876329</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.76943e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-66.64400000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.06619183285849521</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3431557653405256</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.9255657492354911</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.760035842293836</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.92354205133403</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.5391984418617</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.830596023209797</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-22565.89730244199</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-50.23269423969555</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000001478e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8190025675869466</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1804.357</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8410963974261202</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2234.604908011365</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.83307342027145</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.84077e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-71.477</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5417943107221553</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.908650875386144</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.306906614785914</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.807678018575794</v>
+      </c>
+      <c r="L13" t="n">
+        <v>20.93809919373094</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.67727164542526</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.22938267682432</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-29408.65401258625</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.790525530795776</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000111e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8199216917217894</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1710.582</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7973834211865877</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2132.152843077595</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7948787077107389</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.85184e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-72.633</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.07026064364732587</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9835590988326689</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.992073326552868</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.166481189186836</v>
+      </c>
+      <c r="L14" t="n">
+        <v>48.73356223004248</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.87851877562265</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.87775855706153</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-29583.93365675751</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>11.3242846436217</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000025e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8200960150288892</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1671.218</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.779033993335956</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2091.126579480674</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7795838832819943</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.85759e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-73.092</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2245057921206386</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8789611587162565</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.10430061842461</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.15284312343381</v>
+      </c>
+      <c r="L15" t="n">
+        <v>55.26537244303667</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.96601860262649</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.17980651531481</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-29678.09452322549</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>11.82721237302621</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8201782845207977</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1648.205</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7683065422860988</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2058.98900079777</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7676028111485604</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.85986e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-73.459</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4232217573221217</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7375951293759425</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.80771812080537</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.372549019607845</v>
+      </c>
+      <c r="L16" t="n">
+        <v>26.50465078239117</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.1994198164175</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15.05341761510953</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-31154.37288865895</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>12.70089329837924</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000008783e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8203024432975681</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1600.842</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.746228401058341</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2031.890762084078</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7575004336197123</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.86409e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-73.684</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.09798611861049893</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.4928599440369619</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.230224277024809</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.409641476584216</v>
+      </c>
+      <c r="L17" t="n">
+        <v>31.72474037547325</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.80287814285442</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13.62678045159084</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-27596.06716754378</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>12.07682019279912</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8204542884825974</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1586.441</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.73951541176668</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2172.882584621722</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8100629870315673</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.86455e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-73.949</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1530238873021293</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.886326692270619</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.231312423250098</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.317791200155269</v>
+      </c>
+      <c r="L18" t="n">
+        <v>63.18307913664914</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.16959384640222</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14.93585627042165</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-30018.07600164873</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-67.60627417656394</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000131e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8206460909902948</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1557.725</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7261295218632472</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1976.583911088414</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7368817249798907</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.86925e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-74.249</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4700819907729475</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.222272139091677</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.450071988481739</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.35708387435085</v>
+      </c>
+      <c r="L19" t="n">
+        <v>66.5235378490376</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.16231172024354</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14.90743034316741</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-29550.90375437156</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>11.96074584434029</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8208424885399236</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1522.092</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7095192901133855</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2133.507135831754</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7953835957527867</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.87132e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-74.467</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1082735514692771</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6130599531801963</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.216165621389492</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.212478445074232</v>
+      </c>
+      <c r="L20" t="n">
+        <v>33.15852937049793</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.92732160050741</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>14.04462710262912</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-27340.36124166657</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-75.70645345511878</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000032e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8210697152121067</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1502.414</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7003464407778324</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1924.37437542814</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7174177131148157</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.87239e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-74.64400000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1918080706282584</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9398742325789154</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.887368634406233</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.88722959658035</v>
+      </c>
+      <c r="L21" t="n">
+        <v>45.16543240586272</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.17786898249233</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>14.96828971563667</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-28871.0837201775</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>11.9930048128748</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000001448e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8213032005508728</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>1.000000000000194e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8239873823820093</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2164.259</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2592.587212839607</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.79463e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-68.84699999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.052718078381787</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2523162939297187</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9143913538111793</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.714469729497668</v>
+      </c>
+      <c r="L23" t="n">
+        <v>20.17003580839866</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.22988672510775</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11.9836443529929</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-30621.82678766628</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.4043944371976522</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000048e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.818931396280973</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2069.956</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9564271189353954</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2462.863129472509</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9499634640159262</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.80846e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-70.349</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.239685863874375</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8076923076923588</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.405833333333299</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.842429501084546</v>
+      </c>
+      <c r="L24" t="n">
+        <v>30.04711987395344</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.89089795448947</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.91971137817118</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-34279.09277141315</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>13.21742415271888</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000018728e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8192054736333529</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2029.286</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9376354678437285</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2535.251668225904</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9778848154732257</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.81489e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-70.836</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.358931698774072</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9531034482758434</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.9277498202732</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.713193851409006</v>
+      </c>
+      <c r="L25" t="n">
+        <v>31.82073888544717</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.98638690921051</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14.25200403193947</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-34513.32611334425</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-35.20759951698255</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8193239749030816</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1988.22</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9186608441965587</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2383.359150613063</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.919297579965543</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.82214e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-71.131</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.006313834726083744</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.09443961772372357</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.704746835443164</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.138008342022833</v>
+      </c>
+      <c r="L26" t="n">
+        <v>26.34472265192726</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.80482185543558</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>13.63311665764747</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-32476.83126192831</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>16.24956174251747</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000003147e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8193876311862822</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1961.517</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.9063226721016293</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2469.366181351267</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9524717892311985</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.82776e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-71.455</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.4205882352941485</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6770232558139498</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.184681460272017</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.542012195122005</v>
+      </c>
+      <c r="L27" t="n">
+        <v>26.09050407600991</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.81830792661792</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>13.67724111399948</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-32186.55168588873</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-33.32684482857167</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8194662589336773</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1934.235</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8937169719520631</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2448.606172608221</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9444643406716156</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.83007e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-71.66500000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5443089430894275</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7620017714791728</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.31134485349353</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.018765311122019</v>
+      </c>
+      <c r="L28" t="n">
+        <v>26.45935074543551</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.87163150708022</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>13.85452646480459</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-32270.01974311587</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-36.23517199833532</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000156968e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8195668929104341</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1902.703</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8791475511941962</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2307.342608568169</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8899768529063228</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.83257e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-71.86</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1043294614572391</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2450602409638383</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.9137601177336271</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.766666666666765</v>
+      </c>
+      <c r="L29" t="n">
+        <v>23.14263984714875</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.73117651278226</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>13.3970692776507</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-30808.79912314165</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>15.17468326055996</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000116112e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8196825558247631</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1881.206</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8692148213314579</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2283.051950829136</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8806075797652942</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.83615e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-72.123</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1341726618704952</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.5833657587549134</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.8235332043842873</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.072619047618872</v>
+      </c>
+      <c r="L30" t="n">
+        <v>23.24097922922099</v>
+      </c>
+      <c r="M30" t="n">
+        <v>85.73842902141354</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>13.41995345661399</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-30546.62388083949</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>15.74332020039151</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.00000000000071e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8198505988660719</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1854.214</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8567431162351641</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2389.654751804524</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9217258883211046</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.83892e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-72.348</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.04703866229295919</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.57822411788636</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.69014541144829</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.130955516489549</v>
+      </c>
+      <c r="L31" t="n">
+        <v>40.64421714725524</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85.55946921631539</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>12.8770680436661</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-28941.91113499524</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-41.42245384452826</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000012889e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8200813779813744</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1841.019</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8506463413112756</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2370.222669778126</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9142306411293567</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.84195e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-72.509</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1166023166023121</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4661702127659471</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.7657400972897708</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.706428138265575</v>
+      </c>
+      <c r="L32" t="n">
+        <v>23.50375382973382</v>
+      </c>
+      <c r="M32" t="n">
+        <v>85.80128589062012</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>13.62159431595203</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-30427.58664542211</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-42.89626943049529</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000039895e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.82035353547412</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1813.612</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.83798288467323</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2348.90724367556</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9060089597151297</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.84343e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-72.676</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.09966228016350101</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.6827350666408089</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.814473566357984</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.068136902502828</v>
+      </c>
+      <c r="L33" t="n">
+        <v>44.04898659981232</v>
+      </c>
+      <c r="M33" t="n">
+        <v>85.69226677238517</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>13.27560878633282</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-29298.80621146221</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-43.10596150066385</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000002961e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8206536807278236</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1791.995</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8279947085815514</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2194.702901662489</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8465300186598838</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.84847e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-72.854</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1988684457684855</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6901797817919918</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.817762949331802</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.114139569909911</v>
+      </c>
+      <c r="L34" t="n">
+        <v>38.83173767432984</v>
+      </c>
+      <c r="M34" t="n">
+        <v>85.70841168783397</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>13.3257398529347</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-29107.36544144287</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>15.58826951732044</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8209732842270187</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1779.061</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.822018529205608</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2172.697279877658</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8380421183586522</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.8497e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-73.113</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1670299727520248</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.6840175953079207</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.3696721311475</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.669221484610854</v>
+      </c>
+      <c r="L35" t="n">
+        <v>23.42724663160913</v>
+      </c>
+      <c r="M35" t="n">
+        <v>85.85919159752454</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>13.81275975747213</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-29948.80514446605</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>15.46004063429768</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000010549e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8212867731213296</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1763.477</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8148179122739008</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2152.037898862141</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8300734834316562</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.85395e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-73.31999999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.59573770491805</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.260698689956347</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.408502906976785</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.272149744753282</v>
+      </c>
+      <c r="L36" t="n">
+        <v>24.40595317391118</v>
+      </c>
+      <c r="M36" t="n">
+        <v>85.99574808611756</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>14.28543161867493</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-30744.11453532423</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>15.04643894154356</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000210954e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8216267671235367</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1743.803</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.8057275030391465</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2130.663440228387</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8218290322795797</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.85489e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-73.479</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.7989660265878692</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.107894736842106</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.118794098781233</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.396026490066222</v>
+      </c>
+      <c r="L37" t="n">
+        <v>25.13575999622183</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.03822384549272</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>14.43908854381331</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-30783.16612355501</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>15.24970944944562</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000263e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8219592530084373</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1708.144</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7892511940576428</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2108.465879574073</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.813267098260781</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.85835e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-73.68000000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.09642591881024945</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.6844444698887178</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.572339249421166</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.280361568212883</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.341780708683093</v>
+      </c>
+      <c r="M38" t="n">
+        <v>85.66248540855653</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>13.1841128965781</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-27650.59457274326</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>15.72870011027362</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8222949768213919</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1697.884</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7845105414832513</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2237.619748360914</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.86308369387894</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.8599e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-73.879</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1572799999999886</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.5832222222221741</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.723692992213523</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.044476534295995</v>
+      </c>
+      <c r="L39" t="n">
+        <v>21.33362090945453</v>
+      </c>
+      <c r="M39" t="n">
+        <v>85.81927658141153</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>13.68042134931388</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-28482.02510896072</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-52.52256674509908</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000001139e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8226282779471028</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1670.326</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7717773150071225</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2221.398168029673</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8568267856249362</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.8624e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-74.004</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1689432075045502</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8036175452845065</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.050087014551297</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.22571132296877</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>85.77189410797133</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>13.52656242009697</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-27841.27747218926</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-54.8516236759167</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000271e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8229619698113428</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1662.175</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7680111299063559</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2171.131992812326</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8374383635234897</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.86512e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-74.196</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.5481786133959914</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.346587926509128</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.408416220352049</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.270756756756702</v>
+      </c>
+      <c r="L41" t="n">
+        <v>22.66434483128718</v>
+      </c>
+      <c r="M41" t="n">
+        <v>86.04079009269893</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>14.44847743851758</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-29578.20759198589</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-41.313771859589</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000026403e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8233047208738283</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1626.797</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7516646575109541</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2153.635632300191</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.8306897533222647</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.86723e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-74.349</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.08731997254227876</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7459597266380356</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.679816162230556</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.617860072244097</v>
+      </c>
+      <c r="L42" t="n">
+        <v>20.823838663639</v>
+      </c>
+      <c r="M42" t="n">
+        <v>85.61859359939417</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>13.05152928534863</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-26252.44812079285</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-43.16124056549847</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.277275645378917e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8104542054928779</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1619.644</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7483596002142073</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2135.481382367067</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.823687385246384</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.87046e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-74.524</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.6484098939929802</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.225826446280989</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.121831869510793</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.450340136054421</v>
+      </c>
+      <c r="L43" t="n">
+        <v>21.57798976706174</v>
+      </c>
+      <c r="M43" t="n">
+        <v>85.96295309951256</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>14.16900350035914</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-28367.55741277962</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-44.20140310656393</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000194e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8239873823820093</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>1.000000000000067e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8195966819580668</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1988.348</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2506.729103921557</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.85436e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-66.83499999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1587344028520467</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.372055030094593</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.536466165413567</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.719089108910864</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.92425574979669</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.59616956072668</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.909823609083137</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-21553.65571513454</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-43.81054001893767</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.00000000000027e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8179473813783887</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1682.077</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8459671043499427</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2126.56562661029</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8483428158565143</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.90819e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-71.625</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2134415720757781</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9083313515617871</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.690312500235393</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.942211281016333</v>
+      </c>
+      <c r="L13" t="n">
+        <v>34.51062267380237</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.60455708824557</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.00968703455139</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-27564.70733631978</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.307982502426512</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8187164122258088</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1611.404</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8104235274710463</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2039.475037657868</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8136000952265999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.9192e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-72.696</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5256211180124327</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5336371923427402</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.232642916321428</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.043287671232912</v>
+      </c>
+      <c r="L14" t="n">
+        <v>24.6379385753511</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.13770616101534</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.81217384871999</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-30393.90042377313</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>8.634240648969694</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000119e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8187829017704485</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1575.579</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7924060576921141</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2185.785104256392</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.871967019027674</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.92239e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-73.131</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.893478260869606</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6667852906287209</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.093794964028785</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.69147627416535</v>
+      </c>
+      <c r="L15" t="n">
+        <v>26.13090271135829</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.27934440394502</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15.37772536549441</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-31037.18969553097</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-78.13039723049394</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000024045e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8187899596608714</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1536.597</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7728008376803255</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1974.453921387277</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7876614662104566</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.92703e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-73.474</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.256706660779095</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.783492099114218</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.896416443741846</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.612041911653753</v>
+      </c>
+      <c r="L16" t="n">
+        <v>40.49425355894642</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.05706977543211</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.5083226583154</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-28738.03201182807</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>10.98432657157525</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000247e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8188216991037657</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1512.392</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.760627415321664</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1950.948463342645</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7782845223644462</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.93103e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-73.74299999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1219316438417739</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9068713288654667</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.598494419119144</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.806322439044119</v>
+      </c>
+      <c r="L17" t="n">
+        <v>42.00928930268382</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.12476278051119</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>14.7625504079541</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-28895.87027455024</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>10.2215780033689</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000002347e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8189129950193168</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1492.181</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7504626956649439</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2054.106996537883</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8194371674723104</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.93365e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-74.008</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.569475682439224</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.100854321917947</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.229112833686433</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.32405448100505</v>
+      </c>
+      <c r="L18" t="n">
+        <v>65.72099417672497</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.31408704074593</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>15.52307893630385</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-30076.5926785157</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-52.20946176512643</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.819045124068046</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1461.894</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7352304526169464</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1898.636213825373</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.757415793695108</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.93899e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-74.246</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2948786390490279</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.439322231330101</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.772473864973404</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.792140412009485</v>
+      </c>
+      <c r="L19" t="n">
+        <v>44.71040105897736</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.21687968130527</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15.12309592243104</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-28852.46110564734</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>11.28007242884132</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000428e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8192257747855003</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1439.08</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7237566059864771</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1877.869356335257</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7491313494535552</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.94223e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-74.48699999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1554244740486372</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9036080809628981</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.82516860069548</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.909732626172684</v>
+      </c>
+      <c r="L20" t="n">
+        <v>45.22308275884836</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.27033952714685</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>15.34049274003198</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-28908.51322135519</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>9.93105393180349</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000014e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8194058511994442</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1414.254</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7112708640539783</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1995.141510642201</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7959142882735026</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.94502e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-74.619</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3150739563931069</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.230693413898665</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.83292160389022</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.859524294344061</v>
+      </c>
+      <c r="L21" t="n">
+        <v>47.58832023132853</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.34295633619254</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>15.64595805765012</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-29159.12776337244</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-59.9552624947712</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000067e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8195966819580668</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>1.000000000000507e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8253150783533207</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2111.898</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2510.5736219702</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.86901e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-68.756</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.8452688172042837</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.130451127819533</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.506652631578923</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.89554441659704</v>
+      </c>
+      <c r="L23" t="n">
+        <v>32.45630097322727</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.75811165242861</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.48245260975388</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-33774.86298556774</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.195183333353043</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000052073e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8195915288991009</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1997.472</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9458184060025626</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2383.439309101731</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9493604522265715</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.88328e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-70.313</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.08786359077231919</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8951197870453007</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.307405022537019</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.43805168986081</v>
+      </c>
+      <c r="L24" t="n">
+        <v>31.7470195809039</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.96653098710421</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14.18161378770432</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-33888.87326767434</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>15.89338098002031</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000016458e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8198919491967519</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1954.439</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9254419484274334</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2336.329760185212</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9305959959667509</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.89304e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-70.745</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5565594059405854</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8714859437751142</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.107765451663998</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.709658371995007</v>
+      </c>
+      <c r="L25" t="n">
+        <v>32.57799146563097</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.05187263551271</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14.48916407533497</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-34009.82532537974</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>17.40106677601671</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000001424e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8199472184299055</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1925.279</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9116344634068501</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2309.992637620188</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9201055158889928</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.90045e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-71.039</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4780487804878008</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.297677119628248</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.570656370656512</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.725529995489418</v>
+      </c>
+      <c r="L26" t="n">
+        <v>33.71145553372613</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.1169377044325</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>14.73271017374215</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-34167.61706204643</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>16.24382700616366</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8199585031018202</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1893.883</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8967682151316021</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2397.821990956405</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9550892951208052</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.90706e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-71.28100000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.376683087027949</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5844011142061518</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.320980707395444</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.977024793388388</v>
+      </c>
+      <c r="L27" t="n">
+        <v>27.14100763741779</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.95980606102954</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>14.15793017516788</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-32371.817969048</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-33.42682865344023</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000001452e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8201147448924281</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1868.608</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8848003075906128</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2354.472044603464</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9378223462555805</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.91195e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-71.50700000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.02975206611568673</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.6553666312433682</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.529008264462782</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.04872462259245</v>
+      </c>
+      <c r="L28" t="n">
+        <v>27.42504985033319</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.96482790941235</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>14.17560849540062</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-32071.22779888786</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-25.46690836718403</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.393666145335805e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.807392366587996</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1845.438</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8738291337933934</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2330.205774925035</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9281567186611243</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.91644e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-71.735</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.108153477218222</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7916395222583914</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.208626887131533</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.124903793293059</v>
+      </c>
+      <c r="L29" t="n">
+        <v>27.03386724380429</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.97733059189549</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>14.21981288039699</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-31831.51642262445</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-25.44225423232615</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.423279139325497e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8063722578768966</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1825.197</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8642448640985501</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2213.961785301704</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8818549537552589</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.91903e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-71.902</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.43898550724637</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9033542976940097</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.621252204585436</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.326309921962131</v>
+      </c>
+      <c r="L30" t="n">
+        <v>27.48694761056511</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.02870966900606</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>14.40438561075018</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-31951.22384277095</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>16.37252232144556</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.456808227389621e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8050510101565322</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1794.576</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8497455843037873</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2192.171422658318</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8731755179272486</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.92277e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-72.086</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.282306830907057</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.489424206815495</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.498723897911857</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.705124835742366</v>
+      </c>
+      <c r="L31" t="n">
+        <v>24.1670412655428</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85.87609696665561</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>13.8695804952709</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-30365.85402702303</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>16.00490132695495</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.390978337262408e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8083431445395306</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1784.815</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8451236754805392</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2168.762972724793</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8638515731009841</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.92693e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-72.29900000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4916387959865709</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9452571428571652</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.597463768115971</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.831385390428202</v>
+      </c>
+      <c r="L32" t="n">
+        <v>27.27324940408628</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.08516463464437</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>14.61277007336968</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-31778.10502104715</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>16.60752190411336</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000306e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8213885168837558</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1762.292</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8344588611760605</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2250.882894766661</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8965611982333566</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.92978e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-72.48099999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2713201820940587</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.4846534653465558</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.502354920100994</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.246371882086255</v>
+      </c>
+      <c r="L33" t="n">
+        <v>28.03717184987267</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.11355201084075</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>14.71983631726206</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-31683.216587006</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-30.13459896800623</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.821746400329142</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1738.861</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8233641018647682</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2230.52878885431</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8884538455016021</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.93443e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-72.721</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2613188976377858</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7026915113871813</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.775923970433069</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.111932479627581</v>
+      </c>
+      <c r="L34" t="n">
+        <v>26.67230853066723</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.08020508541409</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>14.59422345255162</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-31062.92627946116</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-31.40849825062446</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8220720767545914</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1708.564</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8090182385702338</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2100.520061340436</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.836669374265165</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.93696e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-72.91500000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1490725338935988</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8085133703354108</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.866272757836868</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.114479101282501</v>
+      </c>
+      <c r="L35" t="n">
+        <v>24.40922486503461</v>
+      </c>
+      <c r="M35" t="n">
+        <v>85.74036323023644</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>13.42606969415648</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-28115.63359985818</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>17.12964549756884</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8224168114902716</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1684.266</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7975129480685147</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2192.500880047453</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8733067458610768</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.93967e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-73.128</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.01518986744462819</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.678282385233173</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.973038757060784</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.22473815192653</v>
+      </c>
+      <c r="L36" t="n">
+        <v>15.55229104313778</v>
+      </c>
+      <c r="M36" t="n">
+        <v>85.76039479724962</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>13.48973987606593</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-27958.58111479407</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-34.39289928898665</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8227550837375864</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1676.935</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7940416629969818</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2174.465135238203</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8661228319334318</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.94321e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-73.27200000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.8020634920634637</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.6642659279778691</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.283890954151217</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.160100166944956</v>
+      </c>
+      <c r="L37" t="n">
+        <v>26.9927480182674</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.1750776523389</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>14.95733375595929</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-30875.33796739028</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-36.57821751423876</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000001024e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.823102309757364</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1649.18</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7808994563184396</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2152.742869241987</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8574705200449761</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.9469e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-73.51600000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3678275290215436</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.6925974025973791</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.779863013698621</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.184732214228679</v>
+      </c>
+      <c r="L38" t="n">
+        <v>22.38309758416112</v>
+      </c>
+      <c r="M38" t="n">
+        <v>85.91530846486062</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>14.00318198743088</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-28487.34318003853</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-36.53613261537976</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000016e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8234458384755483</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1637.094</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7751766420537355</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2135.712450721735</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8506870430056184</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.95083e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-73.755</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6151556156969546</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.826597938144306</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.099484536082316</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.103571428571493</v>
+      </c>
+      <c r="L39" t="n">
+        <v>20.59133403708775</v>
+      </c>
+      <c r="M39" t="n">
+        <v>85.99763930489898</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>14.29220387887353</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-28816.33325317343</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-39.19453140385258</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8238081950896849</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1609.313</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7620221241745576</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2111.014628987518</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8408495216048978</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.95229e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-73.89</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3168289290681517</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.769346733668362</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.045982142857129</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.159871244635255</v>
+      </c>
+      <c r="L40" t="n">
+        <v>22.3757781550994</v>
+      </c>
+      <c r="M40" t="n">
+        <v>85.9876950211288</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>14.25666577523855</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-28409.74441714353</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-37.20303993663993</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8241829784722229</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1592</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7538242850743738</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2096.210883345959</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8349529625428528</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.95609e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-74.08199999999999</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1795811518324265</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.92220795892163</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.072660098522167</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.230877483443701</v>
+      </c>
+      <c r="L41" t="n">
+        <v>20.90762961641318</v>
+      </c>
+      <c r="M41" t="n">
+        <v>85.92609497672279</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>14.04038408555592</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-27664.71148502776</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-40.43260228286306</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000146e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8245403951689554</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1567.873</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7423999643922197</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2076.544897375117</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.8271196985434451</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.95864e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-74.238</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1758677685950436</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.5471626733921927</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.832784810126508</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.898786653184994</v>
+      </c>
+      <c r="L42" t="n">
+        <v>21.33889786901714</v>
+      </c>
+      <c r="M42" t="n">
+        <v>85.96545586314856</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>14.17782215982208</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-27659.80082951646</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-40.74636713878181</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000015152e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8249258958499351</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1556.609</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7370663734706884</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2061.003242668581</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8209292189771299</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.96232e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-74.44199999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5528089887640059</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.7835550181378867</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.27936320754709</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.108732612055497</v>
+      </c>
+      <c r="L43" t="n">
+        <v>20.18094444421598</v>
+      </c>
+      <c r="M43" t="n">
+        <v>85.93625423983973</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>14.07560313162577</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-27152.2559054583</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-43.63085340890996</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000507e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8253150783533207</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.8223684639019326</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1325.072</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1867.816843577628</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.08623e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-70.033</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2292389459308818</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6365809500997687</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.260119733770537</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.180883309527025</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.77405098758756</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.64983059297444</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.985742616147581</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-16149.2406227118</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-44.69714813626831</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000051e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8198449945424701</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1141.581</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8615237511622008</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1630.20892877358</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.872788429111212</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.06994e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-75.041</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2092183721124184</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9281699756652059</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.50223840576859</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.613301752202911</v>
+      </c>
+      <c r="L13" t="n">
+        <v>27.31152456196506</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.27031403448062</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15.34038758989648</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-24860.58184285437</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-7.648184136553823</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000072e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8203893547553976</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1090.47</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8229515075407222</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1572.515755608066</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8419004042152549</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.06951e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-75.95399999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3964381117348948</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7304300968449365</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.403468600234386</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.99856370185541</v>
+      </c>
+      <c r="L14" t="n">
+        <v>29.28887231560023</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.44820967343497</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>16.1108520209959</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-25272.2961287095</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-1.041334171414292</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000046e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8205170933880845</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1065.158</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8038491493292439</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1754.381685368931</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9392685858901333</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.07057e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-76.327</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4494401787887425</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9066330683554946</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.947524955194195</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.709318763503869</v>
+      </c>
+      <c r="L15" t="n">
+        <v>35.2496118355776</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.65293236683763</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>17.09872501700414</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-26428.63204935795</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-120.121466765489</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000076e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8206349145994807</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1038.614</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7838170303198618</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1525.891980818296</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8169387625264118</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.07355e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-76.581</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3340135456659701</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7655314018124919</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.520592115291121</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.392265454942453</v>
+      </c>
+      <c r="L16" t="n">
+        <v>32.23071685783785</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.61506210747608</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16.90698825500108</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-25695.89624876585</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-2.704030519185494</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000351e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8208233706467746</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1023.88</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7726976345436324</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1508.746512380324</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8077593461950274</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.07609e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-76.857</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2901853472605054</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7902493135960845</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.64637931990596</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.880139346891258</v>
+      </c>
+      <c r="L17" t="n">
+        <v>38.47667886689877</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.74794040825911</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>17.59938175690651</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-26403.05827183233</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-6.6771196038884</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8210912061231181</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1003.1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7570154678387286</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1491.217405741959</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7983745359559301</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.078e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-77.038</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5605050105711572</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.10255738947121</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.510043112611268</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.655289930090377</v>
+      </c>
+      <c r="L18" t="n">
+        <v>34.38393257394949</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.73482270002181</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>17.52852461314235</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-25876.91593827373</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-9.57176411547573</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000001403e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8213970356642882</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>978.5730000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7385055302655252</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1478.224757375453</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7914184747065738</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.07998e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-77.306</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3681066542570877</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8223235490139518</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.660743489392434</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.335962776801288</v>
+      </c>
+      <c r="L19" t="n">
+        <v>35.35974646188302</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.7597429707979</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>17.66362474277963</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-25678.13215329937</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-16.08234724032479</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8217390669474903</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>966.352</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7292826352077472</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1460.19722635537</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7817668158289544</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.08297e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-77.503</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.7759056771935948</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.626484739626742</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.116182113421989</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.138261006813592</v>
+      </c>
+      <c r="L20" t="n">
+        <v>51.98874431911516</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.02495968943157</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>19.24151340323605</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-27710.36230917755</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-18.35040628536274</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.280368087482346e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8180991154307861</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>940.7620000000001</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7099704770759626</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1445.826894975041</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.774073164585932</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.0844e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-77.687</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3115963208114889</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.001607122153005</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.200321061395096</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.353283726153484</v>
+      </c>
+      <c r="L21" t="n">
+        <v>71.85621553432904</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.77386829314423</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>17.7411280920849</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-25053.07583818535</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-21.9060671962576</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.00000000000105e-08</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8223684639019326</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
